--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,34 +160,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>48.5 → 53.0</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>48.5</t>
-  </si>
-  <si>
-    <t>53.0</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +246,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -389,18 +362,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -911,10 +883,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>4080</v>
+        <v>4037.4</v>
       </c>
       <c r="D2">
-        <v>0.59</v>
+        <v>-1.04</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -923,46 +895,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-6.75</v>
+        <v>-7.72</v>
       </c>
       <c r="H2">
-        <v>23.26</v>
+        <v>21.97</v>
       </c>
       <c r="I2">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="J2">
-        <v>3.4</v>
+        <v>2.77</v>
       </c>
       <c r="K2">
-        <v>6.83</v>
+        <v>4.11</v>
       </c>
       <c r="L2">
-        <v>13.46</v>
+        <v>11.61</v>
       </c>
       <c r="M2">
-        <v>22</v>
+        <v>21.83</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="P2">
-        <v>4048.96</v>
+        <v>4058.44</v>
       </c>
       <c r="Q2">
-        <v>3900.96</v>
+        <v>3910.4</v>
       </c>
       <c r="R2">
-        <v>3987.98</v>
+        <v>3988.51</v>
       </c>
       <c r="S2">
-        <v>3947.16</v>
+        <v>3948.09</v>
       </c>
       <c r="T2">
-        <v>3.37</v>
+        <v>2.26</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -977,43 +949,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>63.73</v>
+        <v>57.99</v>
       </c>
       <c r="Z2">
-        <v>26.43</v>
+        <v>28.38</v>
       </c>
       <c r="AA2">
-        <v>-4.59</v>
+        <v>2</v>
       </c>
       <c r="AB2">
-        <v>31.03</v>
+        <v>26.38</v>
       </c>
       <c r="AC2">
-        <v>99.09</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="AD2">
-        <v>97.86</v>
+        <v>96.92</v>
       </c>
       <c r="AE2">
-        <v>64.05</v>
+        <v>63.15</v>
       </c>
       <c r="AF2">
-        <v>-42.13</v>
+        <v>-24.72</v>
       </c>
       <c r="AG2">
-        <v>4118.91</v>
+        <v>4135.06</v>
       </c>
       <c r="AH2">
-        <v>3683.02</v>
+        <v>3685.74</v>
       </c>
       <c r="AI2">
-        <v>3860.75</v>
+        <v>3862.54</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>41.86</v>
+        <v>42.23</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1024,10 +996,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>312.85</v>
+        <v>315.4</v>
       </c>
       <c r="D3">
-        <v>1.57</v>
+        <v>0.82</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1036,46 +1008,46 @@
         <v>193.76</v>
       </c>
       <c r="G3">
-        <v>-6.78</v>
+        <v>-6.02</v>
       </c>
       <c r="H3">
-        <v>61.46</v>
+        <v>62.78</v>
       </c>
       <c r="I3">
-        <v>-1.62</v>
+        <v>-0.79</v>
       </c>
       <c r="J3">
-        <v>-2.61</v>
+        <v>-2.86</v>
       </c>
       <c r="K3">
-        <v>12.62</v>
+        <v>13.03</v>
       </c>
       <c r="L3">
-        <v>54.92</v>
+        <v>55.99</v>
       </c>
       <c r="M3">
-        <v>31.02</v>
+        <v>31.88</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P3">
-        <v>314.76</v>
+        <v>314.26</v>
       </c>
       <c r="Q3">
         <v>310.75</v>
       </c>
       <c r="R3">
-        <v>300.44</v>
+        <v>301.32</v>
       </c>
       <c r="S3">
-        <v>288.27</v>
+        <v>288.52</v>
       </c>
       <c r="T3">
-        <v>8.529999999999999</v>
+        <v>9.32</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1090,31 +1062,31 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>52.95</v>
+        <v>55.14</v>
       </c>
       <c r="Z3">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AA3">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="AB3">
-        <v>-0.57</v>
+        <v>-0.43</v>
       </c>
       <c r="AC3">
-        <v>47.26</v>
+        <v>40.97</v>
       </c>
       <c r="AD3">
-        <v>68.79000000000001</v>
+        <v>51.06</v>
       </c>
       <c r="AE3">
-        <v>9.029999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="AF3">
-        <v>-60.84</v>
+        <v>-60.81</v>
       </c>
       <c r="AG3">
-        <v>320.21</v>
+        <v>320.23</v>
       </c>
       <c r="AH3">
         <v>301.28</v>
@@ -1126,7 +1098,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>20.46</v>
+        <v>18.55</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1137,10 +1109,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3583.4</v>
+        <v>3652.7</v>
       </c>
       <c r="D4">
-        <v>-0.43</v>
+        <v>1.93</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1149,46 +1121,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-22.84</v>
+        <v>-21.34</v>
       </c>
       <c r="H4">
-        <v>17.82</v>
+        <v>20.1</v>
       </c>
       <c r="I4">
-        <v>0.52</v>
+        <v>4.3</v>
       </c>
       <c r="J4">
-        <v>9.31</v>
+        <v>10.77</v>
       </c>
       <c r="K4">
-        <v>0.5600000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="L4">
-        <v>-14.69</v>
+        <v>-12.47</v>
       </c>
       <c r="M4">
-        <v>0.58</v>
+        <v>1.16</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="P4">
-        <v>3562.96</v>
+        <v>3593.1</v>
       </c>
       <c r="Q4">
-        <v>3482.8</v>
+        <v>3500.78</v>
       </c>
       <c r="R4">
-        <v>3365.06</v>
+        <v>3370.41</v>
       </c>
       <c r="S4">
-        <v>3698.56</v>
+        <v>3696.13</v>
       </c>
       <c r="T4">
-        <v>-3.11</v>
+        <v>-1.17</v>
       </c>
       <c r="U4" t="s">
         <v>42</v>
@@ -1203,43 +1175,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>60</v>
+        <v>64.06</v>
       </c>
       <c r="Z4">
-        <v>68.13</v>
+        <v>72.72</v>
       </c>
       <c r="AA4">
-        <v>59.29</v>
+        <v>61.98</v>
       </c>
       <c r="AB4">
-        <v>8.84</v>
+        <v>10.74</v>
       </c>
       <c r="AC4">
-        <v>69.52</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="AD4">
-        <v>67.36</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="AE4">
-        <v>111.7</v>
+        <v>112.62</v>
       </c>
       <c r="AF4">
-        <v>-68.83</v>
+        <v>-31.9</v>
       </c>
       <c r="AG4">
-        <v>3692.07</v>
+        <v>3703.1</v>
       </c>
       <c r="AH4">
-        <v>3273.52</v>
+        <v>3298.45</v>
       </c>
       <c r="AI4">
-        <v>3277.75</v>
+        <v>3316.13</v>
       </c>
       <c r="AJ4" t="s">
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>36.59</v>
+        <v>38.93</v>
       </c>
     </row>
   </sheetData>
@@ -1400,47 +1372,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1448,428 +1385,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="D7" s="5">
+        <v>2.77</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-2.61</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-2.86</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>9.31</v>
+      </c>
+      <c r="D9" s="5">
+        <v>10.77</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1.37</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1.19</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-1.62</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-0.79</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0.52</v>
+      </c>
+      <c r="D12" s="5">
+        <v>4.3</v>
+      </c>
+      <c r="E12" s="7">
+        <v>3.78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5">
+        <v>13.46</v>
+      </c>
+      <c r="D13" s="5">
+        <v>11.61</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-1.85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5">
+        <v>54.92</v>
+      </c>
+      <c r="D14" s="5">
+        <v>55.99</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-14.69</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-12.47</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2.22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>6.83</v>
+      </c>
+      <c r="D16" s="5">
+        <v>4.11</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-2.72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>12.62</v>
+      </c>
+      <c r="D17" s="5">
+        <v>13.03</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D18" s="5">
+        <v>5.6</v>
+      </c>
+      <c r="E18" s="7">
+        <v>5.04</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-6.75</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-7.72</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-6.78</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-6.02</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-22.84</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-21.34</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5">
+        <v>4080</v>
+      </c>
+      <c r="D22" s="5">
+        <v>4037.4</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-42.6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5">
+        <v>312.85</v>
+      </c>
+      <c r="D23" s="5">
+        <v>315.4</v>
+      </c>
+      <c r="E23" s="7">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5">
+        <v>3583.4</v>
+      </c>
+      <c r="D24" s="5">
+        <v>3652.7</v>
+      </c>
+      <c r="E24" s="7">
+        <v>69.3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="5">
+        <v>63.73</v>
+      </c>
+      <c r="D25" s="5">
+        <v>57.99</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-5.74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="5">
+        <v>52.95</v>
+      </c>
+      <c r="D26" s="5">
+        <v>55.14</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="D27" s="5">
+        <v>64.06</v>
+      </c>
+      <c r="E27" s="7">
+        <v>4.06</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>4.37</v>
-      </c>
-      <c r="D7" s="6">
-        <v>3.4</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-42.13</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-24.72</v>
+      </c>
+      <c r="E28" s="7">
+        <v>17.41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-4.08</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-2.61</v>
-      </c>
-      <c r="E8" s="8">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-60.84</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-60.81</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>11.84</v>
-      </c>
-      <c r="D9" s="6">
-        <v>9.31</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-2.53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="6">
-        <v>2.97</v>
-      </c>
-      <c r="D10" s="6">
-        <v>1.37</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-1.04</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-1.62</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="6">
-        <v>1.22</v>
-      </c>
-      <c r="D12" s="6">
-        <v>0.52</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="6">
-        <v>14.17</v>
-      </c>
-      <c r="D13" s="6">
-        <v>13.46</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="6">
-        <v>54.7</v>
-      </c>
-      <c r="D14" s="6">
-        <v>54.92</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-14.49</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-14.69</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="6">
-        <v>3.94</v>
-      </c>
-      <c r="D16" s="6">
-        <v>6.83</v>
-      </c>
-      <c r="E16" s="8">
-        <v>2.89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="6">
-        <v>5.48</v>
-      </c>
-      <c r="D17" s="6">
-        <v>12.62</v>
-      </c>
-      <c r="E17" s="8">
-        <v>7.14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-3.94</v>
-      </c>
-      <c r="D18" s="6">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E18" s="8">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-7.3</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-6.75</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-8.220000000000001</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-6.78</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-22.51</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-22.84</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="6">
-        <v>4056</v>
-      </c>
-      <c r="D22" s="6">
-        <v>4080</v>
-      </c>
-      <c r="E22" s="8">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6">
-        <v>308</v>
-      </c>
-      <c r="D23" s="6">
-        <v>312.85</v>
-      </c>
-      <c r="E23" s="8">
-        <v>4.85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="6">
-        <v>3598.7</v>
-      </c>
-      <c r="D24" s="6">
-        <v>3583.4</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-15.3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="6">
-        <v>61.75</v>
-      </c>
-      <c r="D25" s="6">
-        <v>63.73</v>
-      </c>
-      <c r="E25" s="8">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="6">
-        <v>48.52</v>
-      </c>
-      <c r="D26" s="6">
-        <v>52.95</v>
-      </c>
-      <c r="E26" s="8">
-        <v>4.43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="6">
-        <v>61.43</v>
-      </c>
-      <c r="D27" s="6">
-        <v>60</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-1.43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6">
-        <v>-56.52</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-42.13</v>
-      </c>
-      <c r="E28" s="8">
-        <v>14.39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-27.14</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-60.84</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-33.7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-66.59999999999999</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C30" s="5">
         <v>-68.83</v>
       </c>
+      <c r="D30" s="5">
+        <v>-31.9</v>
+      </c>
       <c r="E30" s="7">
-        <v>-2.23</v>
+        <v>36.93</v>
       </c>
     </row>
   </sheetData>
@@ -1895,60 +1832,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>68</v>
+      <c r="B1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>64.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>58.9</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>59.1</v>
+      </c>
+      <c r="E2" s="10">
         <v>70</v>
       </c>
-      <c r="F2" s="11">
-        <v>3.4</v>
-      </c>
-      <c r="G2" s="11">
-        <v>6.7</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>3.6</v>
+      </c>
+      <c r="G2" s="10">
+        <v>7.6</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>30</v>
       </c>
     </row>
@@ -2050,25 +1987,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.3102</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.22</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.0058</v>
+      <c r="A2" s="13">
+        <v>0.3188</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.2183</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.0116</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -246,14 +246,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,13 +286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -744,7 +744,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="17" width="8.7109375" customWidth="1"/>
+    <col min="18" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -883,10 +885,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>4037.4</v>
+        <v>4020</v>
       </c>
       <c r="D2">
-        <v>-1.04</v>
+        <v>-0.43</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -895,25 +897,25 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-7.72</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="H2">
-        <v>21.97</v>
+        <v>21.45</v>
       </c>
       <c r="I2">
-        <v>1.19</v>
+        <v>-0.91</v>
       </c>
       <c r="J2">
-        <v>2.77</v>
+        <v>4.45</v>
       </c>
       <c r="K2">
-        <v>4.11</v>
+        <v>3.02</v>
       </c>
       <c r="L2">
-        <v>11.61</v>
+        <v>11.87</v>
       </c>
       <c r="M2">
-        <v>21.83</v>
+        <v>21.11</v>
       </c>
       <c r="N2">
         <v>66</v>
@@ -922,19 +924,19 @@
         <v>65</v>
       </c>
       <c r="P2">
-        <v>4058.44</v>
+        <v>4051.04</v>
       </c>
       <c r="Q2">
-        <v>3910.4</v>
+        <v>3922.2</v>
       </c>
       <c r="R2">
-        <v>3988.51</v>
+        <v>3988.89</v>
       </c>
       <c r="S2">
-        <v>3948.09</v>
+        <v>3948.79</v>
       </c>
       <c r="T2">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -949,34 +951,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>57.99</v>
+        <v>55.78</v>
       </c>
       <c r="Z2">
-        <v>28.38</v>
+        <v>28.19</v>
       </c>
       <c r="AA2">
-        <v>2</v>
+        <v>7.24</v>
       </c>
       <c r="AB2">
-        <v>26.38</v>
+        <v>20.96</v>
       </c>
       <c r="AC2">
-        <v>92.56999999999999</v>
+        <v>84.45</v>
       </c>
       <c r="AD2">
-        <v>96.92</v>
+        <v>92.04000000000001</v>
       </c>
       <c r="AE2">
-        <v>63.15</v>
+        <v>62.51</v>
       </c>
       <c r="AF2">
-        <v>-24.72</v>
+        <v>20.64</v>
       </c>
       <c r="AG2">
-        <v>4135.06</v>
+        <v>4143.66</v>
       </c>
       <c r="AH2">
-        <v>3685.74</v>
+        <v>3700.75</v>
       </c>
       <c r="AI2">
         <v>3862.54</v>
@@ -985,7 +987,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>42.23</v>
+        <v>38.62</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -996,10 +998,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>315.4</v>
+        <v>317.2</v>
       </c>
       <c r="D3">
-        <v>0.82</v>
+        <v>0.57</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1008,46 +1010,46 @@
         <v>193.76</v>
       </c>
       <c r="G3">
-        <v>-6.02</v>
+        <v>-5.48</v>
       </c>
       <c r="H3">
-        <v>62.78</v>
+        <v>63.71</v>
       </c>
       <c r="I3">
-        <v>-0.79</v>
+        <v>-0.38</v>
       </c>
       <c r="J3">
-        <v>-2.86</v>
+        <v>0.6</v>
       </c>
       <c r="K3">
-        <v>13.03</v>
+        <v>13.92</v>
       </c>
       <c r="L3">
-        <v>55.99</v>
+        <v>58.91</v>
       </c>
       <c r="M3">
-        <v>31.88</v>
+        <v>31.67</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P3">
-        <v>314.26</v>
+        <v>314.02</v>
       </c>
       <c r="Q3">
-        <v>310.75</v>
+        <v>310.99</v>
       </c>
       <c r="R3">
-        <v>301.32</v>
+        <v>302.25</v>
       </c>
       <c r="S3">
-        <v>288.52</v>
+        <v>288.79</v>
       </c>
       <c r="T3">
-        <v>9.32</v>
+        <v>9.84</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1062,34 +1064,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>55.14</v>
+        <v>56.67</v>
       </c>
       <c r="Z3">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="AA3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AB3">
-        <v>-0.43</v>
+        <v>-0.23</v>
       </c>
       <c r="AC3">
-        <v>40.97</v>
+        <v>62.77</v>
       </c>
       <c r="AD3">
-        <v>51.06</v>
+        <v>50.34</v>
       </c>
       <c r="AE3">
-        <v>8.789999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="AF3">
-        <v>-60.81</v>
+        <v>-8.84</v>
       </c>
       <c r="AG3">
-        <v>320.23</v>
+        <v>320.88</v>
       </c>
       <c r="AH3">
-        <v>301.28</v>
+        <v>301.11</v>
       </c>
       <c r="AI3">
         <v>329.06</v>
@@ -1098,7 +1100,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>18.55</v>
+        <v>16.22</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1109,10 +1111,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3652.7</v>
+        <v>3578.9</v>
       </c>
       <c r="D4">
-        <v>1.93</v>
+        <v>-2.02</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1121,46 +1123,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-21.34</v>
+        <v>-22.93</v>
       </c>
       <c r="H4">
-        <v>20.1</v>
+        <v>17.68</v>
       </c>
       <c r="I4">
-        <v>4.3</v>
+        <v>0.1</v>
       </c>
       <c r="J4">
-        <v>10.77</v>
+        <v>8.68</v>
       </c>
       <c r="K4">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="L4">
-        <v>-12.47</v>
+        <v>-14.63</v>
       </c>
       <c r="M4">
-        <v>1.16</v>
+        <v>0.75</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="P4">
-        <v>3593.1</v>
+        <v>3593.82</v>
       </c>
       <c r="Q4">
-        <v>3500.78</v>
+        <v>3504.3</v>
       </c>
       <c r="R4">
-        <v>3370.41</v>
+        <v>3371.82</v>
       </c>
       <c r="S4">
-        <v>3696.13</v>
+        <v>3693.33</v>
       </c>
       <c r="T4">
-        <v>-1.17</v>
+        <v>-3.1</v>
       </c>
       <c r="U4" t="s">
         <v>42</v>
@@ -1175,34 +1177,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>64.06</v>
+        <v>57.38</v>
       </c>
       <c r="Z4">
-        <v>72.72</v>
+        <v>69.59</v>
       </c>
       <c r="AA4">
-        <v>61.98</v>
+        <v>63.5</v>
       </c>
       <c r="AB4">
-        <v>10.74</v>
+        <v>6.09</v>
       </c>
       <c r="AC4">
-        <v>80.34999999999999</v>
+        <v>60.01</v>
       </c>
       <c r="AD4">
-        <v>73.93000000000001</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="AE4">
-        <v>112.62</v>
+        <v>111.61</v>
       </c>
       <c r="AF4">
-        <v>-31.9</v>
+        <v>-74.73</v>
       </c>
       <c r="AG4">
-        <v>3703.1</v>
+        <v>3709.62</v>
       </c>
       <c r="AH4">
-        <v>3298.45</v>
+        <v>3298.99</v>
       </c>
       <c r="AI4">
         <v>3316.13</v>
@@ -1211,7 +1213,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>38.93</v>
+        <v>37.99</v>
       </c>
     </row>
   </sheetData>
@@ -1409,13 +1411,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>3.4</v>
+        <v>2.77</v>
       </c>
       <c r="D7" s="5">
-        <v>2.77</v>
+        <v>4.45</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.63</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1426,13 +1428,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-2.61</v>
+        <v>-2.86</v>
       </c>
       <c r="D8" s="5">
-        <v>-2.86</v>
+        <v>0.6</v>
       </c>
       <c r="E8" s="6">
-        <v>-0.25</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1443,13 +1445,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>9.31</v>
+        <v>10.77</v>
       </c>
       <c r="D9" s="5">
-        <v>10.77</v>
+        <v>8.68</v>
       </c>
       <c r="E9" s="7">
-        <v>1.46</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1460,13 +1462,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="D10" s="5">
-        <v>1.19</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-0.18</v>
+        <v>-0.91</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-2.1</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1477,13 +1479,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-1.62</v>
+        <v>-0.79</v>
       </c>
       <c r="D11" s="5">
-        <v>-0.79</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.83</v>
+        <v>-0.38</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.41</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1494,13 +1496,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>0.52</v>
+        <v>4.3</v>
       </c>
       <c r="D12" s="5">
-        <v>4.3</v>
+        <v>0.1</v>
       </c>
       <c r="E12" s="7">
-        <v>3.78</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1511,13 +1513,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>13.46</v>
+        <v>11.61</v>
       </c>
       <c r="D13" s="5">
-        <v>11.61</v>
+        <v>11.87</v>
       </c>
       <c r="E13" s="6">
-        <v>-1.85</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1528,13 +1530,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>54.92</v>
+        <v>55.99</v>
       </c>
       <c r="D14" s="5">
-        <v>55.99</v>
-      </c>
-      <c r="E14" s="7">
-        <v>1.07</v>
+        <v>58.91</v>
+      </c>
+      <c r="E14" s="6">
+        <v>2.92</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1545,13 +1547,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-14.69</v>
+        <v>-12.47</v>
       </c>
       <c r="D15" s="5">
-        <v>-12.47</v>
+        <v>-14.63</v>
       </c>
       <c r="E15" s="7">
-        <v>2.22</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1562,13 +1564,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>6.83</v>
+        <v>4.11</v>
       </c>
       <c r="D16" s="5">
-        <v>4.11</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-2.72</v>
+        <v>3.02</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1579,13 +1581,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>12.62</v>
+        <v>13.03</v>
       </c>
       <c r="D17" s="5">
-        <v>13.03</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.41</v>
+        <v>13.92</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.89</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1596,13 +1598,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>0.5600000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="D18" s="5">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="E18" s="7">
-        <v>5.04</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1613,13 +1615,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-6.75</v>
+        <v>-7.72</v>
       </c>
       <c r="D19" s="5">
-        <v>-7.72</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-0.97</v>
+        <v>-8.119999999999999</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1630,13 +1632,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-6.78</v>
+        <v>-6.02</v>
       </c>
       <c r="D20" s="5">
-        <v>-6.02</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.76</v>
+        <v>-5.48</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.54</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1647,13 +1649,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-22.84</v>
+        <v>-21.34</v>
       </c>
       <c r="D21" s="5">
-        <v>-21.34</v>
+        <v>-22.93</v>
       </c>
       <c r="E21" s="7">
-        <v>1.5</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1664,13 +1666,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>4080</v>
+        <v>4037.4</v>
       </c>
       <c r="D22" s="5">
-        <v>4037.4</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-42.6</v>
+        <v>4020</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-17.4</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1681,13 +1683,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>312.85</v>
+        <v>315.4</v>
       </c>
       <c r="D23" s="5">
-        <v>315.4</v>
-      </c>
-      <c r="E23" s="7">
-        <v>2.55</v>
+        <v>317.2</v>
+      </c>
+      <c r="E23" s="6">
+        <v>1.8</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1698,13 +1700,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>3583.4</v>
+        <v>3652.7</v>
       </c>
       <c r="D24" s="5">
-        <v>3652.7</v>
+        <v>3578.9</v>
       </c>
       <c r="E24" s="7">
-        <v>69.3</v>
+        <v>-73.8</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1715,13 +1717,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>63.73</v>
+        <v>57.99</v>
       </c>
       <c r="D25" s="5">
-        <v>57.99</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-5.74</v>
+        <v>55.78</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-2.21</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1732,13 +1734,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>52.95</v>
+        <v>55.14</v>
       </c>
       <c r="D26" s="5">
-        <v>55.14</v>
-      </c>
-      <c r="E26" s="7">
-        <v>2.19</v>
+        <v>56.67</v>
+      </c>
+      <c r="E26" s="6">
+        <v>1.53</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1749,13 +1751,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>60</v>
+        <v>64.06</v>
       </c>
       <c r="D27" s="5">
-        <v>64.06</v>
+        <v>57.38</v>
       </c>
       <c r="E27" s="7">
-        <v>4.06</v>
+        <v>-6.68</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1766,13 +1768,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>-42.13</v>
+        <v>-24.72</v>
       </c>
       <c r="D28" s="5">
-        <v>-24.72</v>
-      </c>
-      <c r="E28" s="7">
-        <v>17.41</v>
+        <v>20.64</v>
+      </c>
+      <c r="E28" s="6">
+        <v>45.36</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1783,13 +1785,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-60.84</v>
+        <v>-60.81</v>
       </c>
       <c r="D29" s="5">
-        <v>-60.81</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.03</v>
+        <v>-8.84</v>
+      </c>
+      <c r="E29" s="6">
+        <v>51.97</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1800,13 +1802,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-68.83</v>
+        <v>-31.9</v>
       </c>
       <c r="D30" s="5">
-        <v>-31.9</v>
+        <v>-74.73</v>
       </c>
       <c r="E30" s="7">
-        <v>36.93</v>
+        <v>-42.83</v>
       </c>
     </row>
   </sheetData>
@@ -1871,16 +1873,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>59.1</v>
+        <v>56.6</v>
       </c>
       <c r="E2" s="10">
         <v>70</v>
       </c>
       <c r="F2" s="10">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="G2" s="10">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -1999,13 +2001,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.3188</v>
+        <v>0.3167</v>
       </c>
       <c r="B2" s="13">
-        <v>0.2183</v>
+        <v>0.2111</v>
       </c>
       <c r="C2" s="13">
-        <v>0.0116</v>
+        <v>0.0075</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -744,9 +744,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="17" width="8.7109375" customWidth="1"/>
-    <col min="18" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -885,10 +883,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>4020</v>
+        <v>4070.7</v>
       </c>
       <c r="D2">
-        <v>-0.43</v>
+        <v>1.26</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -897,46 +895,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-8.119999999999999</v>
+        <v>-6.96</v>
       </c>
       <c r="H2">
-        <v>21.45</v>
+        <v>22.98</v>
       </c>
       <c r="I2">
-        <v>-0.91</v>
+        <v>0.22</v>
       </c>
       <c r="J2">
-        <v>4.45</v>
+        <v>7.58</v>
       </c>
       <c r="K2">
-        <v>3.02</v>
+        <v>5.15</v>
       </c>
       <c r="L2">
-        <v>11.87</v>
+        <v>12.87</v>
       </c>
       <c r="M2">
-        <v>21.11</v>
+        <v>20.75</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="P2">
-        <v>4051.04</v>
+        <v>4052.82</v>
       </c>
       <c r="Q2">
-        <v>3922.2</v>
+        <v>3936.96</v>
       </c>
       <c r="R2">
-        <v>3988.89</v>
+        <v>3991.24</v>
       </c>
       <c r="S2">
-        <v>3948.79</v>
+        <v>3949.81</v>
       </c>
       <c r="T2">
-        <v>1.8</v>
+        <v>3.06</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -951,34 +949,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>55.78</v>
+        <v>60.5</v>
       </c>
       <c r="Z2">
-        <v>28.19</v>
+        <v>31.77</v>
       </c>
       <c r="AA2">
-        <v>7.24</v>
+        <v>12.15</v>
       </c>
       <c r="AB2">
-        <v>20.96</v>
+        <v>19.63</v>
       </c>
       <c r="AC2">
-        <v>84.45</v>
+        <v>80.38</v>
       </c>
       <c r="AD2">
-        <v>92.04000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="AE2">
-        <v>62.51</v>
+        <v>63.81</v>
       </c>
       <c r="AF2">
-        <v>20.64</v>
+        <v>25.12</v>
       </c>
       <c r="AG2">
-        <v>4143.66</v>
+        <v>4156.61</v>
       </c>
       <c r="AH2">
-        <v>3700.75</v>
+        <v>3717.31</v>
       </c>
       <c r="AI2">
         <v>3862.54</v>
@@ -987,7 +985,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>38.62</v>
+        <v>37.07</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -998,10 +996,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>317.2</v>
+        <v>315.35</v>
       </c>
       <c r="D3">
-        <v>0.57</v>
+        <v>-0.58</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1010,25 +1008,25 @@
         <v>193.76</v>
       </c>
       <c r="G3">
-        <v>-5.48</v>
+        <v>-6.03</v>
       </c>
       <c r="H3">
-        <v>63.71</v>
+        <v>62.75</v>
       </c>
       <c r="I3">
-        <v>-0.38</v>
+        <v>-0.41</v>
       </c>
       <c r="J3">
-        <v>0.6</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K3">
-        <v>13.92</v>
+        <v>13.48</v>
       </c>
       <c r="L3">
-        <v>58.91</v>
+        <v>59.07</v>
       </c>
       <c r="M3">
-        <v>31.67</v>
+        <v>31.8</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1037,19 +1035,19 @@
         <v>87</v>
       </c>
       <c r="P3">
-        <v>314.02</v>
+        <v>313.76</v>
       </c>
       <c r="Q3">
-        <v>310.99</v>
+        <v>311.28</v>
       </c>
       <c r="R3">
-        <v>302.25</v>
+        <v>303.2</v>
       </c>
       <c r="S3">
-        <v>288.79</v>
+        <v>289.04</v>
       </c>
       <c r="T3">
-        <v>9.84</v>
+        <v>9.1</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1064,34 +1062,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>56.67</v>
+        <v>54.61</v>
       </c>
       <c r="Z3">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="AA3">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="AB3">
-        <v>-0.23</v>
+        <v>-0.24</v>
       </c>
       <c r="AC3">
-        <v>62.77</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="AD3">
-        <v>50.34</v>
+        <v>56.41</v>
       </c>
       <c r="AE3">
-        <v>8.69</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AF3">
-        <v>-8.84</v>
+        <v>-76.56999999999999</v>
       </c>
       <c r="AG3">
-        <v>320.88</v>
+        <v>321.33</v>
       </c>
       <c r="AH3">
-        <v>301.11</v>
+        <v>301.24</v>
       </c>
       <c r="AI3">
         <v>329.06</v>
@@ -1100,7 +1098,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>16.22</v>
+        <v>14.15</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1111,10 +1109,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3578.9</v>
+        <v>3604.7</v>
       </c>
       <c r="D4">
-        <v>-2.02</v>
+        <v>0.72</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1123,46 +1121,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-22.93</v>
+        <v>-22.38</v>
       </c>
       <c r="H4">
-        <v>17.68</v>
+        <v>18.52</v>
       </c>
       <c r="I4">
-        <v>0.1</v>
+        <v>1.39</v>
       </c>
       <c r="J4">
-        <v>8.68</v>
+        <v>2.75</v>
       </c>
       <c r="K4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L4">
-        <v>-14.63</v>
+        <v>-12.97</v>
       </c>
       <c r="M4">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="P4">
-        <v>3593.82</v>
+        <v>3603.68</v>
       </c>
       <c r="Q4">
-        <v>3504.3</v>
+        <v>3510.53</v>
       </c>
       <c r="R4">
-        <v>3371.82</v>
+        <v>3377.93</v>
       </c>
       <c r="S4">
-        <v>3693.33</v>
+        <v>3690.81</v>
       </c>
       <c r="T4">
-        <v>-3.1</v>
+        <v>-2.33</v>
       </c>
       <c r="U4" t="s">
         <v>42</v>
@@ -1177,34 +1175,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>57.38</v>
+        <v>58.99</v>
       </c>
       <c r="Z4">
-        <v>69.59</v>
+        <v>68.41</v>
       </c>
       <c r="AA4">
-        <v>63.5</v>
+        <v>64.48</v>
       </c>
       <c r="AB4">
-        <v>6.09</v>
+        <v>3.93</v>
       </c>
       <c r="AC4">
-        <v>60.01</v>
+        <v>48.85</v>
       </c>
       <c r="AD4">
-        <v>69.95999999999999</v>
+        <v>63.07</v>
       </c>
       <c r="AE4">
-        <v>111.61</v>
+        <v>110.06</v>
       </c>
       <c r="AF4">
-        <v>-74.73</v>
+        <v>-77.93000000000001</v>
       </c>
       <c r="AG4">
-        <v>3709.62</v>
+        <v>3720.27</v>
       </c>
       <c r="AH4">
-        <v>3298.99</v>
+        <v>3300.79</v>
       </c>
       <c r="AI4">
         <v>3316.13</v>
@@ -1213,7 +1211,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>37.99</v>
+        <v>36.8</v>
       </c>
     </row>
   </sheetData>
@@ -1411,13 +1409,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>2.77</v>
+        <v>4.45</v>
       </c>
       <c r="D7" s="5">
-        <v>4.45</v>
+        <v>7.58</v>
       </c>
       <c r="E7" s="6">
-        <v>1.68</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1428,13 +1426,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-2.86</v>
+        <v>0.6</v>
       </c>
       <c r="D8" s="5">
-        <v>0.6</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E8" s="6">
-        <v>3.46</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1445,13 +1443,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>10.77</v>
+        <v>8.68</v>
       </c>
       <c r="D9" s="5">
-        <v>8.68</v>
+        <v>2.75</v>
       </c>
       <c r="E9" s="7">
-        <v>-2.09</v>
+        <v>-5.93</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1462,13 +1460,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>1.19</v>
+        <v>-0.91</v>
       </c>
       <c r="D10" s="5">
-        <v>-0.91</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-2.1</v>
+        <v>0.22</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1.13</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1479,13 +1477,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-0.79</v>
+        <v>-0.38</v>
       </c>
       <c r="D11" s="5">
-        <v>-0.38</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0.41</v>
+        <v>-0.41</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1496,13 +1494,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>4.3</v>
+        <v>0.1</v>
       </c>
       <c r="D12" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-4.2</v>
+        <v>1.39</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1.29</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1513,13 +1511,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>11.61</v>
+        <v>11.87</v>
       </c>
       <c r="D13" s="5">
-        <v>11.87</v>
+        <v>12.87</v>
       </c>
       <c r="E13" s="6">
-        <v>0.26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1530,13 +1528,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>55.99</v>
+        <v>58.91</v>
       </c>
       <c r="D14" s="5">
-        <v>58.91</v>
+        <v>59.07</v>
       </c>
       <c r="E14" s="6">
-        <v>2.92</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1547,13 +1545,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-12.47</v>
+        <v>-14.63</v>
       </c>
       <c r="D15" s="5">
-        <v>-14.63</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-2.16</v>
+        <v>-12.97</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1.66</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1564,13 +1562,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>4.11</v>
+        <v>3.02</v>
       </c>
       <c r="D16" s="5">
-        <v>3.02</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-1.09</v>
+        <v>5.15</v>
+      </c>
+      <c r="E16" s="6">
+        <v>2.13</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1581,13 +1579,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>13.03</v>
+        <v>13.92</v>
       </c>
       <c r="D17" s="5">
-        <v>13.92</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0.89</v>
+        <v>13.48</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1598,13 +1596,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="D18" s="5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="E18" s="7">
-        <v>-1.2</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1615,13 +1613,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-7.72</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="D19" s="5">
-        <v>-8.119999999999999</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.4</v>
+        <v>-6.96</v>
+      </c>
+      <c r="E19" s="6">
+        <v>1.16</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1632,13 +1630,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-6.02</v>
+        <v>-5.48</v>
       </c>
       <c r="D20" s="5">
-        <v>-5.48</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0.54</v>
+        <v>-6.03</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1649,13 +1647,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-21.34</v>
+        <v>-22.93</v>
       </c>
       <c r="D21" s="5">
-        <v>-22.93</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-1.59</v>
+        <v>-22.38</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.55</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1666,13 +1664,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>4037.4</v>
+        <v>4020</v>
       </c>
       <c r="D22" s="5">
-        <v>4020</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-17.4</v>
+        <v>4070.7</v>
+      </c>
+      <c r="E22" s="6">
+        <v>50.7</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1683,13 +1681,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>315.4</v>
+        <v>317.2</v>
       </c>
       <c r="D23" s="5">
-        <v>317.2</v>
-      </c>
-      <c r="E23" s="6">
-        <v>1.8</v>
+        <v>315.35</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-1.85</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1700,13 +1698,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>3652.7</v>
+        <v>3578.9</v>
       </c>
       <c r="D24" s="5">
-        <v>3578.9</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-73.8</v>
+        <v>3604.7</v>
+      </c>
+      <c r="E24" s="6">
+        <v>25.8</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1717,13 +1715,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>57.99</v>
+        <v>55.78</v>
       </c>
       <c r="D25" s="5">
-        <v>55.78</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-2.21</v>
+        <v>60.5</v>
+      </c>
+      <c r="E25" s="6">
+        <v>4.72</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1734,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>55.14</v>
+        <v>56.67</v>
       </c>
       <c r="D26" s="5">
-        <v>56.67</v>
-      </c>
-      <c r="E26" s="6">
-        <v>1.53</v>
+        <v>54.61</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-2.06</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1751,13 +1749,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>64.06</v>
+        <v>57.38</v>
       </c>
       <c r="D27" s="5">
-        <v>57.38</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-6.68</v>
+        <v>58.99</v>
+      </c>
+      <c r="E27" s="6">
+        <v>1.61</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1768,13 +1766,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>-24.72</v>
+        <v>20.64</v>
       </c>
       <c r="D28" s="5">
-        <v>20.64</v>
+        <v>25.12</v>
       </c>
       <c r="E28" s="6">
-        <v>45.36</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1785,13 +1783,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-60.81</v>
+        <v>-8.84</v>
       </c>
       <c r="D29" s="5">
-        <v>-8.84</v>
-      </c>
-      <c r="E29" s="6">
-        <v>51.97</v>
+        <v>-76.56999999999999</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-67.73</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1802,13 +1800,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-31.9</v>
+        <v>-74.73</v>
       </c>
       <c r="D30" s="5">
-        <v>-74.73</v>
+        <v>-77.93000000000001</v>
       </c>
       <c r="E30" s="7">
-        <v>-42.83</v>
+        <v>-3.2</v>
       </c>
     </row>
   </sheetData>
@@ -1873,16 +1871,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>56.6</v>
+        <v>58</v>
       </c>
       <c r="E2" s="10">
         <v>70</v>
       </c>
       <c r="F2" s="10">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="G2" s="10">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -2001,13 +1999,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.3167</v>
+        <v>0.318</v>
       </c>
       <c r="B2" s="13">
-        <v>0.2111</v>
+        <v>0.2075</v>
       </c>
       <c r="C2" s="13">
-        <v>0.0075</v>
+        <v>0.0069</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,7 +160,43 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>54.6 → 45.8</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>54.6</t>
+  </si>
+  <si>
+    <t>45.8</t>
+  </si>
+  <si>
+    <t>59.0 → 49.1</t>
+  </si>
+  <si>
+    <t>59.0</t>
+  </si>
+  <si>
+    <t>49.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -246,14 +282,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,13 +322,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -362,14 +398,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -883,10 +920,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>4070.7</v>
+        <v>4057</v>
       </c>
       <c r="D2">
-        <v>1.26</v>
+        <v>-0.34</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -895,46 +932,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-6.96</v>
+        <v>-7.28</v>
       </c>
       <c r="H2">
-        <v>22.98</v>
+        <v>22.57</v>
       </c>
       <c r="I2">
-        <v>0.22</v>
+        <v>0.02</v>
       </c>
       <c r="J2">
-        <v>7.58</v>
+        <v>7.45</v>
       </c>
       <c r="K2">
-        <v>5.15</v>
+        <v>4.56</v>
       </c>
       <c r="L2">
-        <v>12.87</v>
+        <v>13.56</v>
       </c>
       <c r="M2">
-        <v>20.75</v>
+        <v>20.88</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="P2">
-        <v>4052.82</v>
+        <v>4053.02</v>
       </c>
       <c r="Q2">
-        <v>3936.96</v>
+        <v>3949.08</v>
       </c>
       <c r="R2">
-        <v>3991.24</v>
+        <v>3993.54</v>
       </c>
       <c r="S2">
-        <v>3949.81</v>
+        <v>3950.66</v>
       </c>
       <c r="T2">
-        <v>3.06</v>
+        <v>2.69</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -949,43 +986,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>60.5</v>
+        <v>58.68</v>
       </c>
       <c r="Z2">
-        <v>31.77</v>
+        <v>33.12</v>
       </c>
       <c r="AA2">
-        <v>12.15</v>
+        <v>16.34</v>
       </c>
       <c r="AB2">
-        <v>19.63</v>
+        <v>16.78</v>
       </c>
       <c r="AC2">
-        <v>80.38</v>
+        <v>79.52</v>
       </c>
       <c r="AD2">
-        <v>85.8</v>
+        <v>81.45</v>
       </c>
       <c r="AE2">
-        <v>63.81</v>
+        <v>62.06</v>
       </c>
       <c r="AF2">
-        <v>25.12</v>
+        <v>-47.36</v>
       </c>
       <c r="AG2">
-        <v>4156.61</v>
+        <v>4167.03</v>
       </c>
       <c r="AH2">
-        <v>3717.31</v>
+        <v>3731.14</v>
       </c>
       <c r="AI2">
-        <v>3862.54</v>
+        <v>3866.61</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>37.07</v>
+        <v>35.83</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -996,58 +1033,58 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>315.35</v>
+        <v>306.3</v>
       </c>
       <c r="D3">
-        <v>-0.58</v>
+        <v>-2.87</v>
       </c>
       <c r="E3">
         <v>335.6</v>
       </c>
       <c r="F3">
-        <v>193.76</v>
+        <v>195.76</v>
       </c>
       <c r="G3">
-        <v>-6.03</v>
+        <v>-8.73</v>
       </c>
       <c r="H3">
-        <v>62.75</v>
+        <v>56.47</v>
       </c>
       <c r="I3">
-        <v>-0.41</v>
+        <v>-0.55</v>
       </c>
       <c r="J3">
-        <v>0.9399999999999999</v>
+        <v>-1.05</v>
       </c>
       <c r="K3">
-        <v>13.48</v>
+        <v>11.01</v>
       </c>
       <c r="L3">
-        <v>59.07</v>
+        <v>58.08</v>
       </c>
       <c r="M3">
-        <v>31.8</v>
+        <v>31.32</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P3">
-        <v>313.76</v>
+        <v>313.42</v>
       </c>
       <c r="Q3">
-        <v>311.28</v>
+        <v>311.09</v>
       </c>
       <c r="R3">
-        <v>303.2</v>
+        <v>304</v>
       </c>
       <c r="S3">
-        <v>289.04</v>
+        <v>289.25</v>
       </c>
       <c r="T3">
-        <v>9.1</v>
+        <v>5.89</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1062,34 +1099,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>54.61</v>
+        <v>45.82</v>
       </c>
       <c r="Z3">
-        <v>2.69</v>
+        <v>1.88</v>
       </c>
       <c r="AA3">
-        <v>2.93</v>
+        <v>2.72</v>
       </c>
       <c r="AB3">
-        <v>-0.24</v>
+        <v>-0.84</v>
       </c>
       <c r="AC3">
-        <v>65.48999999999999</v>
+        <v>43.98</v>
       </c>
       <c r="AD3">
-        <v>56.41</v>
+        <v>57.42</v>
       </c>
       <c r="AE3">
-        <v>8.380000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AF3">
-        <v>-76.56999999999999</v>
+        <v>-21.62</v>
       </c>
       <c r="AG3">
-        <v>321.33</v>
+        <v>321.37</v>
       </c>
       <c r="AH3">
-        <v>301.24</v>
+        <v>300.82</v>
       </c>
       <c r="AI3">
         <v>329.06</v>
@@ -1098,7 +1135,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>14.15</v>
+        <v>15.88</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1109,10 +1146,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3604.7</v>
+        <v>3476.8</v>
       </c>
       <c r="D4">
-        <v>0.72</v>
+        <v>-3.55</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1121,46 +1158,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-22.38</v>
+        <v>-25.13</v>
       </c>
       <c r="H4">
-        <v>18.52</v>
+        <v>14.32</v>
       </c>
       <c r="I4">
-        <v>1.39</v>
+        <v>-3.39</v>
       </c>
       <c r="J4">
-        <v>2.75</v>
+        <v>-0.1</v>
       </c>
       <c r="K4">
-        <v>4.3</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L4">
-        <v>-12.97</v>
+        <v>-15.53</v>
       </c>
       <c r="M4">
-        <v>0.6899999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="P4">
-        <v>3603.68</v>
+        <v>3579.3</v>
       </c>
       <c r="Q4">
-        <v>3510.53</v>
+        <v>3513.6</v>
       </c>
       <c r="R4">
-        <v>3377.93</v>
+        <v>3382.02</v>
       </c>
       <c r="S4">
-        <v>3690.81</v>
+        <v>3687.45</v>
       </c>
       <c r="T4">
-        <v>-2.33</v>
+        <v>-5.71</v>
       </c>
       <c r="U4" t="s">
         <v>42</v>
@@ -1175,34 +1212,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>58.99</v>
+        <v>49.09</v>
       </c>
       <c r="Z4">
-        <v>68.41</v>
+        <v>56.5</v>
       </c>
       <c r="AA4">
-        <v>64.48</v>
+        <v>62.88</v>
       </c>
       <c r="AB4">
-        <v>3.93</v>
+        <v>-6.38</v>
       </c>
       <c r="AC4">
-        <v>48.85</v>
+        <v>17.14</v>
       </c>
       <c r="AD4">
-        <v>63.07</v>
+        <v>42</v>
       </c>
       <c r="AE4">
-        <v>110.06</v>
+        <v>112.53</v>
       </c>
       <c r="AF4">
-        <v>-77.93000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AG4">
-        <v>3720.27</v>
+        <v>3719.23</v>
       </c>
       <c r="AH4">
-        <v>3300.79</v>
+        <v>3307.98</v>
       </c>
       <c r="AI4">
         <v>3316.13</v>
@@ -1211,7 +1248,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>36.8</v>
+        <v>33.02</v>
       </c>
     </row>
   </sheetData>
@@ -1352,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1372,447 +1409,502 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>51</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>4.45</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="6">
         <v>7.58</v>
       </c>
-      <c r="E7" s="6">
-        <v>3.13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="6">
+        <v>7.45</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="6">
         <v>0.9399999999999999</v>
       </c>
-      <c r="E8" s="6">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="6">
+        <v>-1.05</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>8.68</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="6">
         <v>2.75</v>
       </c>
-      <c r="E9" s="7">
-        <v>-5.93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-2.85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>-0.91</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C11" s="6">
         <v>0.22</v>
       </c>
-      <c r="E10" s="6">
-        <v>1.13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D11" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>-0.38</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C12" s="6">
         <v>-0.41</v>
       </c>
-      <c r="E11" s="7">
-        <v>-0.03</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="6">
+        <v>-0.55</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C13" s="6">
         <v>1.39</v>
       </c>
-      <c r="E12" s="6">
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="6">
+        <v>-3.39</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-4.78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
-        <v>11.87</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C14" s="6">
         <v>12.87</v>
       </c>
-      <c r="E13" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D14" s="6">
+        <v>13.56</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5">
-        <v>58.91</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C15" s="6">
         <v>59.07</v>
       </c>
-      <c r="E14" s="6">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D15" s="6">
+        <v>58.08</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="5">
-        <v>-14.63</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C16" s="6">
         <v>-12.97</v>
       </c>
-      <c r="E15" s="6">
-        <v>1.66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D16" s="6">
+        <v>-15.53</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-2.56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="5">
-        <v>3.02</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C17" s="6">
         <v>5.15</v>
       </c>
-      <c r="E16" s="6">
-        <v>2.13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D17" s="6">
+        <v>4.56</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="5">
-        <v>13.92</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C18" s="6">
         <v>13.48</v>
       </c>
-      <c r="E17" s="7">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D18" s="6">
+        <v>11.01</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-2.47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="5">
-        <v>4.4</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C19" s="6">
         <v>4.3</v>
       </c>
-      <c r="E18" s="7">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D19" s="6">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-5.24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="5">
-        <v>-8.119999999999999</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C20" s="6">
         <v>-6.96</v>
       </c>
-      <c r="E19" s="6">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="D20" s="6">
+        <v>-7.28</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="5">
-        <v>-5.48</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C21" s="6">
         <v>-6.03</v>
       </c>
-      <c r="E20" s="7">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="D21" s="6">
+        <v>-8.73</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="5">
-        <v>-22.93</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C22" s="6">
         <v>-22.38</v>
       </c>
-      <c r="E21" s="6">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="D22" s="6">
+        <v>-25.13</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-2.75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="5">
-        <v>4020</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C23" s="6">
         <v>4070.7</v>
       </c>
-      <c r="E22" s="6">
-        <v>50.7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="D23" s="6">
+        <v>4057</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-13.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="5">
-        <v>317.2</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C24" s="6">
         <v>315.35</v>
       </c>
-      <c r="E23" s="7">
-        <v>-1.85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="D24" s="6">
+        <v>306.3</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-9.050000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="5">
-        <v>3578.9</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C25" s="6">
         <v>3604.7</v>
       </c>
-      <c r="E24" s="6">
-        <v>25.8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="D25" s="6">
+        <v>3476.8</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-127.9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="5">
-        <v>55.78</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C26" s="6">
         <v>60.5</v>
       </c>
-      <c r="E25" s="6">
-        <v>4.72</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="D26" s="6">
+        <v>58.68</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="5">
-        <v>56.67</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C27" s="6">
         <v>54.61</v>
       </c>
-      <c r="E26" s="7">
-        <v>-2.06</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="D27" s="6">
+        <v>45.82</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-8.789999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="5">
-        <v>57.38</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C28" s="6">
         <v>58.99</v>
       </c>
-      <c r="E27" s="6">
-        <v>1.61</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="D28" s="6">
+        <v>49.09</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-9.9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5">
-        <v>20.64</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C29" s="6">
         <v>25.12</v>
       </c>
-      <c r="E28" s="6">
-        <v>4.48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="D29" s="6">
+        <v>-47.36</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-72.48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="5">
-        <v>-8.84</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C30" s="6">
         <v>-76.56999999999999</v>
       </c>
-      <c r="E29" s="7">
-        <v>-67.73</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="D30" s="6">
+        <v>-21.62</v>
+      </c>
+      <c r="E30" s="8">
+        <v>54.95</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="5">
-        <v>-74.73</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C31" s="6">
         <v>-77.93000000000001</v>
       </c>
-      <c r="E30" s="7">
-        <v>-3.2</v>
+      <c r="D31" s="6">
+        <v>10.5</v>
+      </c>
+      <c r="E31" s="8">
+        <v>88.43000000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1832,60 +1924,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>59</v>
+      <c r="B1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>64.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>58</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>51.2</v>
+      </c>
+      <c r="E2" s="11">
         <v>70</v>
       </c>
-      <c r="F2" s="10">
-        <v>3.8</v>
-      </c>
-      <c r="G2" s="10">
-        <v>7.6</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>2.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>4.9</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>30</v>
       </c>
     </row>
@@ -1987,25 +2079,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.318</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.2075</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.0069</v>
+      <c r="A2" s="14">
+        <v>0.3132</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2088</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.0008</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,25 +178,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>54.6 → 45.8</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>54.6</t>
+    <t>45.8 → 53.6</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>45.8</t>
   </si>
   <si>
-    <t>59.0 → 49.1</t>
-  </si>
-  <si>
-    <t>59.0</t>
-  </si>
-  <si>
-    <t>49.1</t>
+    <t>53.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -282,14 +273,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -322,13 +313,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -408,8 +399,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -920,10 +911,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>4057</v>
+        <v>4086.7</v>
       </c>
       <c r="D2">
-        <v>-0.34</v>
+        <v>0.73</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -932,46 +923,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-7.28</v>
+        <v>-6.6</v>
       </c>
       <c r="H2">
-        <v>22.57</v>
+        <v>23.46</v>
       </c>
       <c r="I2">
-        <v>0.02</v>
+        <v>0.16</v>
       </c>
       <c r="J2">
-        <v>7.45</v>
+        <v>7.14</v>
       </c>
       <c r="K2">
-        <v>4.56</v>
+        <v>5.24</v>
       </c>
       <c r="L2">
-        <v>13.56</v>
+        <v>12.49</v>
       </c>
       <c r="M2">
-        <v>20.88</v>
+        <v>21.28</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P2">
-        <v>4053.02</v>
+        <v>4054.36</v>
       </c>
       <c r="Q2">
-        <v>3949.08</v>
+        <v>3961.48</v>
       </c>
       <c r="R2">
-        <v>3993.54</v>
+        <v>3996.21</v>
       </c>
       <c r="S2">
-        <v>3950.66</v>
+        <v>3951.43</v>
       </c>
       <c r="T2">
-        <v>2.69</v>
+        <v>3.42</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -986,43 +977,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>58.68</v>
+        <v>61.4</v>
       </c>
       <c r="Z2">
-        <v>33.12</v>
+        <v>36.17</v>
       </c>
       <c r="AA2">
-        <v>16.34</v>
+        <v>20.31</v>
       </c>
       <c r="AB2">
-        <v>16.78</v>
+        <v>15.86</v>
       </c>
       <c r="AC2">
-        <v>79.52</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="AD2">
-        <v>81.45</v>
+        <v>80.56</v>
       </c>
       <c r="AE2">
-        <v>62.06</v>
+        <v>61.97</v>
       </c>
       <c r="AF2">
-        <v>-47.36</v>
+        <v>-36.48</v>
       </c>
       <c r="AG2">
-        <v>4167.03</v>
+        <v>4181.21</v>
       </c>
       <c r="AH2">
-        <v>3731.14</v>
+        <v>3741.75</v>
       </c>
       <c r="AI2">
-        <v>3866.61</v>
+        <v>3870.45</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>35.83</v>
+        <v>35.62</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1033,10 +1024,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>306.3</v>
+        <v>315</v>
       </c>
       <c r="D3">
-        <v>-2.87</v>
+        <v>2.84</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1045,46 +1036,46 @@
         <v>195.76</v>
       </c>
       <c r="G3">
-        <v>-8.73</v>
+        <v>-6.14</v>
       </c>
       <c r="H3">
-        <v>56.47</v>
+        <v>60.91</v>
       </c>
       <c r="I3">
-        <v>-0.55</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J3">
-        <v>-1.05</v>
+        <v>1.6</v>
       </c>
       <c r="K3">
-        <v>11.01</v>
+        <v>14.5</v>
       </c>
       <c r="L3">
-        <v>58.08</v>
+        <v>60.77</v>
       </c>
       <c r="M3">
-        <v>31.32</v>
+        <v>32.68</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="P3">
-        <v>313.42</v>
+        <v>313.85</v>
       </c>
       <c r="Q3">
-        <v>311.09</v>
+        <v>311.55</v>
       </c>
       <c r="R3">
-        <v>304</v>
+        <v>304.92</v>
       </c>
       <c r="S3">
-        <v>289.25</v>
+        <v>289.5</v>
       </c>
       <c r="T3">
-        <v>5.89</v>
+        <v>8.81</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1099,34 +1090,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>45.82</v>
+        <v>53.56</v>
       </c>
       <c r="Z3">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AA3">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="AB3">
-        <v>-0.84</v>
+        <v>-0.64</v>
       </c>
       <c r="AC3">
-        <v>43.98</v>
+        <v>37.15</v>
       </c>
       <c r="AD3">
-        <v>57.42</v>
+        <v>48.87</v>
       </c>
       <c r="AE3">
-        <v>8.449999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="AF3">
-        <v>-21.62</v>
+        <v>-34.79</v>
       </c>
       <c r="AG3">
-        <v>321.37</v>
+        <v>321.66</v>
       </c>
       <c r="AH3">
-        <v>300.82</v>
+        <v>301.44</v>
       </c>
       <c r="AI3">
         <v>329.06</v>
@@ -1135,7 +1126,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>15.88</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1149,7 +1140,7 @@
         <v>3476.8</v>
       </c>
       <c r="D4">
-        <v>-3.55</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1164,40 +1155,40 @@
         <v>14.32</v>
       </c>
       <c r="I4">
-        <v>-3.39</v>
+        <v>-2.97</v>
       </c>
       <c r="J4">
-        <v>-0.1</v>
+        <v>1.8</v>
       </c>
       <c r="K4">
-        <v>-0.9399999999999999</v>
+        <v>-1.09</v>
       </c>
       <c r="L4">
-        <v>-15.53</v>
+        <v>-14.81</v>
       </c>
       <c r="M4">
-        <v>0.08</v>
+        <v>-0.72</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P4">
-        <v>3579.3</v>
+        <v>3557.98</v>
       </c>
       <c r="Q4">
-        <v>3513.6</v>
+        <v>3519.97</v>
       </c>
       <c r="R4">
-        <v>3382.02</v>
+        <v>3387.31</v>
       </c>
       <c r="S4">
-        <v>3687.45</v>
+        <v>3684.4</v>
       </c>
       <c r="T4">
-        <v>-5.71</v>
+        <v>-5.63</v>
       </c>
       <c r="U4" t="s">
         <v>42</v>
@@ -1215,31 +1206,31 @@
         <v>49.09</v>
       </c>
       <c r="Z4">
-        <v>56.5</v>
+        <v>46.53</v>
       </c>
       <c r="AA4">
-        <v>62.88</v>
+        <v>59.61</v>
       </c>
       <c r="AB4">
-        <v>-6.38</v>
+        <v>-13.09</v>
       </c>
       <c r="AC4">
-        <v>17.14</v>
+        <v>11.04</v>
       </c>
       <c r="AD4">
-        <v>42</v>
+        <v>25.68</v>
       </c>
       <c r="AE4">
-        <v>112.53</v>
+        <v>114.83</v>
       </c>
       <c r="AF4">
-        <v>10.5</v>
+        <v>-16.24</v>
       </c>
       <c r="AG4">
-        <v>3719.23</v>
+        <v>3711.61</v>
       </c>
       <c r="AH4">
-        <v>3307.98</v>
+        <v>3328.33</v>
       </c>
       <c r="AI4">
         <v>3316.13</v>
@@ -1248,7 +1239,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>33.02</v>
+        <v>29.74</v>
       </c>
     </row>
   </sheetData>
@@ -1389,7 +1380,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1447,305 +1438,302 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="E6" s="3" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>63</v>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>7.45</v>
+      </c>
+      <c r="D7" s="6">
+        <v>7.14</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>7.58</v>
+        <v>-1.05</v>
       </c>
       <c r="D8" s="6">
-        <v>7.45</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.13</v>
+        <v>1.6</v>
+      </c>
+      <c r="E8" s="8">
+        <v>2.65</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>0.9399999999999999</v>
+        <v>-0.1</v>
       </c>
       <c r="D9" s="6">
-        <v>-1.05</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-1.99</v>
+        <v>1.8</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1.9</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="6">
-        <v>2.75</v>
+        <v>0.02</v>
       </c>
       <c r="D10" s="6">
-        <v>-0.1</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-2.85</v>
+        <v>0.16</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.14</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>0.22</v>
+        <v>-0.55</v>
       </c>
       <c r="D11" s="6">
-        <v>0.02</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.2</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.24</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-0.41</v>
+        <v>-3.39</v>
       </c>
       <c r="D12" s="6">
-        <v>-0.55</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.14</v>
+        <v>-2.97</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.42</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C13" s="6">
-        <v>1.39</v>
+        <v>13.56</v>
       </c>
       <c r="D13" s="6">
-        <v>-3.39</v>
+        <v>12.49</v>
       </c>
       <c r="E13" s="7">
-        <v>-4.78</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>12.87</v>
+        <v>58.08</v>
       </c>
       <c r="D14" s="6">
-        <v>13.56</v>
+        <v>60.77</v>
       </c>
       <c r="E14" s="8">
-        <v>0.6899999999999999</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>59.07</v>
+        <v>-15.53</v>
       </c>
       <c r="D15" s="6">
-        <v>58.08</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.99</v>
+        <v>-14.81</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.72</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>-12.97</v>
+        <v>4.56</v>
       </c>
       <c r="D16" s="6">
-        <v>-15.53</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-2.56</v>
+        <v>5.24</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.68</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>5.15</v>
+        <v>11.01</v>
       </c>
       <c r="D17" s="6">
-        <v>4.56</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.59</v>
+        <v>14.5</v>
+      </c>
+      <c r="E17" s="8">
+        <v>3.49</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>13.48</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="D18" s="6">
-        <v>11.01</v>
+        <v>-1.09</v>
       </c>
       <c r="E18" s="7">
-        <v>-2.47</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C19" s="6">
-        <v>4.3</v>
+        <v>-7.28</v>
       </c>
       <c r="D19" s="6">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-5.24</v>
+        <v>-6.6</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.68</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-6.96</v>
+        <v>-8.73</v>
       </c>
       <c r="D20" s="6">
-        <v>-7.28</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.32</v>
+        <v>-6.14</v>
+      </c>
+      <c r="E20" s="8">
+        <v>2.59</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C21" s="6">
-        <v>-6.03</v>
+        <v>4057</v>
       </c>
       <c r="D21" s="6">
-        <v>-8.73</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-2.7</v>
+        <v>4086.7</v>
+      </c>
+      <c r="E21" s="8">
+        <v>29.7</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C22" s="6">
-        <v>-22.38</v>
+        <v>306.3</v>
       </c>
       <c r="D22" s="6">
-        <v>-25.13</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-2.75</v>
+        <v>315</v>
+      </c>
+      <c r="E22" s="8">
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1753,16 +1741,16 @@
         <v>37</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C23" s="6">
-        <v>4070.7</v>
+        <v>58.68</v>
       </c>
       <c r="D23" s="6">
-        <v>4057</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-13.7</v>
+        <v>61.4</v>
+      </c>
+      <c r="E23" s="8">
+        <v>2.72</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1770,141 +1758,73 @@
         <v>38</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C24" s="6">
-        <v>315.35</v>
+        <v>45.82</v>
       </c>
       <c r="D24" s="6">
-        <v>306.3</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-9.050000000000001</v>
+        <v>53.56</v>
+      </c>
+      <c r="E24" s="8">
+        <v>7.74</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="C25" s="6">
-        <v>3604.7</v>
+        <v>-47.36</v>
       </c>
       <c r="D25" s="6">
-        <v>3476.8</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-127.9</v>
+        <v>-36.48</v>
+      </c>
+      <c r="E25" s="8">
+        <v>10.88</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C26" s="6">
-        <v>60.5</v>
+        <v>-21.62</v>
       </c>
       <c r="D26" s="6">
-        <v>58.68</v>
+        <v>-34.79</v>
       </c>
       <c r="E26" s="7">
-        <v>-1.82</v>
+        <v>-13.17</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C27" s="6">
-        <v>54.61</v>
+        <v>10.5</v>
       </c>
       <c r="D27" s="6">
-        <v>45.82</v>
+        <v>-16.24</v>
       </c>
       <c r="E27" s="7">
-        <v>-8.789999999999999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="6">
-        <v>58.99</v>
-      </c>
-      <c r="D28" s="6">
-        <v>49.09</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-9.9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="6">
-        <v>25.12</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-47.36</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-72.48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-76.56999999999999</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-21.62</v>
-      </c>
-      <c r="E30" s="8">
-        <v>54.95</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-77.93000000000001</v>
-      </c>
-      <c r="D31" s="6">
-        <v>10.5</v>
-      </c>
-      <c r="E31" s="8">
-        <v>88.43000000000001</v>
+        <v>-26.74</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1928,28 +1848,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>68</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1963,16 +1883,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="11">
-        <v>51.2</v>
+        <v>54.7</v>
       </c>
       <c r="E2" s="11">
         <v>70</v>
       </c>
       <c r="F2" s="11">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="G2" s="11">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="H2" s="11">
         <v>66.3</v>
@@ -2091,13 +2011,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.3132</v>
+        <v>0.3268</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2088</v>
+        <v>0.2128</v>
       </c>
       <c r="C2" s="14">
-        <v>0.0008</v>
+        <v>-0.0072</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,7 +178,7 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>45.8 → 53.6</t>
+    <t>45.8 → 60.6</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
@@ -187,7 +187,16 @@
     <t>45.8</t>
   </si>
   <si>
-    <t>53.6</t>
+    <t>60.6</t>
+  </si>
+  <si>
+    <t>49.1 → 51.5</t>
+  </si>
+  <si>
+    <t>49.1</t>
+  </si>
+  <si>
+    <t>51.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -911,10 +920,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>4086.7</v>
+        <v>4064.3</v>
       </c>
       <c r="D2">
-        <v>0.73</v>
+        <v>-0.55</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -923,46 +932,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-6.6</v>
+        <v>-7.11</v>
       </c>
       <c r="H2">
-        <v>23.46</v>
+        <v>22.79</v>
       </c>
       <c r="I2">
-        <v>0.16</v>
+        <v>0.67</v>
       </c>
       <c r="J2">
-        <v>7.14</v>
+        <v>5.87</v>
       </c>
       <c r="K2">
-        <v>5.24</v>
+        <v>4.94</v>
       </c>
       <c r="L2">
-        <v>12.49</v>
+        <v>11.34</v>
       </c>
       <c r="M2">
-        <v>21.28</v>
+        <v>21.24</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P2">
-        <v>4054.36</v>
+        <v>4059.74</v>
       </c>
       <c r="Q2">
-        <v>3961.48</v>
+        <v>3972.36</v>
       </c>
       <c r="R2">
-        <v>3996.21</v>
+        <v>3999.99</v>
       </c>
       <c r="S2">
-        <v>3951.43</v>
+        <v>3952.15</v>
       </c>
       <c r="T2">
-        <v>3.42</v>
+        <v>2.84</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -977,43 +986,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>61.4</v>
+        <v>58.28</v>
       </c>
       <c r="Z2">
-        <v>36.17</v>
+        <v>36.36</v>
       </c>
       <c r="AA2">
-        <v>20.31</v>
+        <v>23.52</v>
       </c>
       <c r="AB2">
-        <v>15.86</v>
+        <v>12.84</v>
       </c>
       <c r="AC2">
-        <v>81.76000000000001</v>
+        <v>69.11</v>
       </c>
       <c r="AD2">
-        <v>80.56</v>
+        <v>76.8</v>
       </c>
       <c r="AE2">
-        <v>61.97</v>
+        <v>60.16</v>
       </c>
       <c r="AF2">
-        <v>-36.48</v>
+        <v>-17.2</v>
       </c>
       <c r="AG2">
-        <v>4181.21</v>
+        <v>4189.69</v>
       </c>
       <c r="AH2">
-        <v>3741.75</v>
+        <v>3755.04</v>
       </c>
       <c r="AI2">
-        <v>3870.45</v>
+        <v>3887.02</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>35.62</v>
+        <v>35.44</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1024,58 +1033,58 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>315</v>
+        <v>325.1</v>
       </c>
       <c r="D3">
-        <v>2.84</v>
+        <v>3.21</v>
       </c>
       <c r="E3">
         <v>335.6</v>
       </c>
       <c r="F3">
-        <v>195.76</v>
+        <v>199.29</v>
       </c>
       <c r="G3">
-        <v>-6.14</v>
+        <v>-3.13</v>
       </c>
       <c r="H3">
-        <v>60.91</v>
+        <v>63.13</v>
       </c>
       <c r="I3">
-        <v>0.6899999999999999</v>
+        <v>3.08</v>
       </c>
       <c r="J3">
-        <v>1.6</v>
+        <v>6.29</v>
       </c>
       <c r="K3">
-        <v>14.5</v>
+        <v>19.15</v>
       </c>
       <c r="L3">
-        <v>60.77</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="M3">
-        <v>32.68</v>
+        <v>33.5</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P3">
-        <v>313.85</v>
+        <v>315.79</v>
       </c>
       <c r="Q3">
-        <v>311.55</v>
+        <v>312.47</v>
       </c>
       <c r="R3">
-        <v>304.92</v>
+        <v>306.19</v>
       </c>
       <c r="S3">
-        <v>289.5</v>
+        <v>289.8</v>
       </c>
       <c r="T3">
-        <v>8.81</v>
+        <v>12.18</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1090,34 +1099,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>53.56</v>
+        <v>60.6</v>
       </c>
       <c r="Z3">
-        <v>1.92</v>
+        <v>2.73</v>
       </c>
       <c r="AA3">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AB3">
-        <v>-0.64</v>
+        <v>0.14</v>
       </c>
       <c r="AC3">
-        <v>37.15</v>
+        <v>52.1</v>
       </c>
       <c r="AD3">
-        <v>48.87</v>
+        <v>44.41</v>
       </c>
       <c r="AE3">
-        <v>8.59</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="AF3">
-        <v>-34.79</v>
+        <v>113.08</v>
       </c>
       <c r="AG3">
-        <v>321.66</v>
+        <v>323.98</v>
       </c>
       <c r="AH3">
-        <v>301.44</v>
+        <v>300.96</v>
       </c>
       <c r="AI3">
         <v>329.06</v>
@@ -1126,7 +1135,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>17.99</v>
+        <v>17.33</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1137,10 +1146,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3476.8</v>
+        <v>3509.9</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1149,46 +1158,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-25.13</v>
+        <v>-24.42</v>
       </c>
       <c r="H4">
-        <v>14.32</v>
+        <v>15.41</v>
       </c>
       <c r="I4">
-        <v>-2.97</v>
+        <v>-3.91</v>
       </c>
       <c r="J4">
-        <v>1.8</v>
+        <v>4.79</v>
       </c>
       <c r="K4">
-        <v>-1.09</v>
+        <v>-0.87</v>
       </c>
       <c r="L4">
-        <v>-14.81</v>
+        <v>-14.9</v>
       </c>
       <c r="M4">
-        <v>-0.72</v>
+        <v>-0.52</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="P4">
-        <v>3557.98</v>
+        <v>3529.42</v>
       </c>
       <c r="Q4">
-        <v>3519.97</v>
+        <v>3530.14</v>
       </c>
       <c r="R4">
-        <v>3387.31</v>
+        <v>3394.2</v>
       </c>
       <c r="S4">
-        <v>3684.4</v>
+        <v>3681.64</v>
       </c>
       <c r="T4">
-        <v>-5.63</v>
+        <v>-4.66</v>
       </c>
       <c r="U4" t="s">
         <v>42</v>
@@ -1203,34 +1212,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>49.09</v>
+        <v>51.53</v>
       </c>
       <c r="Z4">
-        <v>46.53</v>
+        <v>40.82</v>
       </c>
       <c r="AA4">
-        <v>59.61</v>
+        <v>55.85</v>
       </c>
       <c r="AB4">
-        <v>-13.09</v>
+        <v>-15.03</v>
       </c>
       <c r="AC4">
-        <v>11.04</v>
+        <v>5.44</v>
       </c>
       <c r="AD4">
-        <v>25.68</v>
+        <v>11.21</v>
       </c>
       <c r="AE4">
-        <v>114.83</v>
+        <v>112.71</v>
       </c>
       <c r="AF4">
-        <v>-16.24</v>
+        <v>-55.17</v>
       </c>
       <c r="AG4">
-        <v>3711.61</v>
+        <v>3693.58</v>
       </c>
       <c r="AH4">
-        <v>3328.33</v>
+        <v>3366.71</v>
       </c>
       <c r="AI4">
         <v>3316.13</v>
@@ -1239,7 +1248,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>29.74</v>
+        <v>26.9</v>
       </c>
     </row>
   </sheetData>
@@ -1380,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1438,302 +1447,305 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>7.45</v>
-      </c>
-      <c r="D7" s="6">
-        <v>7.14</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-0.31</v>
+      <c r="C7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-1.05</v>
+        <v>7.45</v>
       </c>
       <c r="D8" s="6">
-        <v>1.6</v>
-      </c>
-      <c r="E8" s="8">
-        <v>2.65</v>
+        <v>5.87</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.58</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-0.1</v>
+        <v>-1.05</v>
       </c>
       <c r="D9" s="6">
-        <v>1.8</v>
+        <v>6.29</v>
       </c>
       <c r="E9" s="8">
-        <v>1.9</v>
+        <v>7.34</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="D10" s="6">
-        <v>0.16</v>
+        <v>4.79</v>
       </c>
       <c r="E10" s="8">
-        <v>0.14</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>-0.55</v>
+        <v>0.02</v>
       </c>
       <c r="D11" s="6">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="E11" s="8">
-        <v>1.24</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-3.39</v>
+        <v>-0.55</v>
       </c>
       <c r="D12" s="6">
-        <v>-2.97</v>
+        <v>3.08</v>
       </c>
       <c r="E12" s="8">
-        <v>0.42</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>13.56</v>
+        <v>-3.39</v>
       </c>
       <c r="D13" s="6">
-        <v>12.49</v>
+        <v>-3.91</v>
       </c>
       <c r="E13" s="7">
-        <v>-1.07</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>58.08</v>
+        <v>13.56</v>
       </c>
       <c r="D14" s="6">
-        <v>60.77</v>
-      </c>
-      <c r="E14" s="8">
-        <v>2.69</v>
+        <v>11.34</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-2.22</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>-15.53</v>
+        <v>58.08</v>
       </c>
       <c r="D15" s="6">
-        <v>-14.81</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="E15" s="8">
-        <v>0.72</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="6">
-        <v>4.56</v>
+        <v>-15.53</v>
       </c>
       <c r="D16" s="6">
-        <v>5.24</v>
+        <v>-14.9</v>
       </c>
       <c r="E16" s="8">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>11.01</v>
+        <v>4.56</v>
       </c>
       <c r="D17" s="6">
-        <v>14.5</v>
+        <v>4.94</v>
       </c>
       <c r="E17" s="8">
-        <v>3.49</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-0.9399999999999999</v>
+        <v>11.01</v>
       </c>
       <c r="D18" s="6">
-        <v>-1.09</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.15</v>
+        <v>19.15</v>
+      </c>
+      <c r="E18" s="8">
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C19" s="6">
-        <v>-7.28</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="D19" s="6">
-        <v>-6.6</v>
+        <v>-0.87</v>
       </c>
       <c r="E19" s="8">
-        <v>0.68</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-8.73</v>
+        <v>-7.28</v>
       </c>
       <c r="D20" s="6">
-        <v>-6.14</v>
+        <v>-7.11</v>
       </c>
       <c r="E20" s="8">
-        <v>2.59</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>4057</v>
+        <v>-8.73</v>
       </c>
       <c r="D21" s="6">
-        <v>4086.7</v>
+        <v>-3.13</v>
       </c>
       <c r="E21" s="8">
-        <v>29.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C22" s="6">
-        <v>306.3</v>
+        <v>-25.13</v>
       </c>
       <c r="D22" s="6">
-        <v>315</v>
+        <v>-24.42</v>
       </c>
       <c r="E22" s="8">
-        <v>8.699999999999999</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1741,16 +1753,16 @@
         <v>37</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C23" s="6">
-        <v>58.68</v>
+        <v>4057</v>
       </c>
       <c r="D23" s="6">
-        <v>61.4</v>
+        <v>4064.3</v>
       </c>
       <c r="E23" s="8">
-        <v>2.72</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1758,73 +1770,141 @@
         <v>38</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>45.82</v>
+        <v>306.3</v>
       </c>
       <c r="D24" s="6">
-        <v>53.56</v>
+        <v>325.1</v>
       </c>
       <c r="E24" s="8">
-        <v>7.74</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="C25" s="6">
-        <v>-47.36</v>
+        <v>3476.8</v>
       </c>
       <c r="D25" s="6">
-        <v>-36.48</v>
+        <v>3509.9</v>
       </c>
       <c r="E25" s="8">
-        <v>10.88</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C26" s="6">
-        <v>-21.62</v>
+        <v>58.68</v>
       </c>
       <c r="D26" s="6">
-        <v>-34.79</v>
+        <v>58.28</v>
       </c>
       <c r="E26" s="7">
-        <v>-13.17</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="6">
+        <v>45.82</v>
+      </c>
+      <c r="D27" s="6">
+        <v>60.6</v>
+      </c>
+      <c r="E27" s="8">
+        <v>14.78</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="6">
+        <v>49.09</v>
+      </c>
+      <c r="D28" s="6">
+        <v>51.53</v>
+      </c>
+      <c r="E28" s="8">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C29" s="6">
+        <v>-47.36</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-17.2</v>
+      </c>
+      <c r="E29" s="8">
+        <v>30.16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-21.62</v>
+      </c>
+      <c r="D30" s="6">
+        <v>113.08</v>
+      </c>
+      <c r="E30" s="8">
+        <v>134.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="6">
         <v>10.5</v>
       </c>
-      <c r="D27" s="6">
-        <v>-16.24</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-26.74</v>
+      <c r="D31" s="6">
+        <v>-55.17</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-65.67</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1848,28 +1928,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1883,16 +1963,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="11">
-        <v>54.7</v>
+        <v>56.8</v>
       </c>
       <c r="E2" s="11">
         <v>70</v>
       </c>
       <c r="F2" s="11">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="G2" s="11">
-        <v>6.2</v>
+        <v>7.7</v>
       </c>
       <c r="H2" s="11">
         <v>66.3</v>
@@ -2011,13 +2091,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.3268</v>
+        <v>0.335</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2128</v>
+        <v>0.2124</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0072</v>
+        <v>-0.0052</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,43 +160,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>45.8 → 60.6</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>45.8</t>
-  </si>
-  <si>
-    <t>60.6</t>
-  </si>
-  <si>
-    <t>49.1 → 51.5</t>
-  </si>
-  <si>
-    <t>49.1</t>
-  </si>
-  <si>
-    <t>51.5</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -282,14 +246,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -322,13 +286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,18 +362,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -920,10 +883,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>4064.3</v>
+        <v>4041.3</v>
       </c>
       <c r="D2">
-        <v>-0.55</v>
+        <v>-0.57</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -932,46 +895,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-7.11</v>
+        <v>-7.64</v>
       </c>
       <c r="H2">
-        <v>22.79</v>
+        <v>22.09</v>
       </c>
       <c r="I2">
-        <v>0.67</v>
+        <v>0.53</v>
       </c>
       <c r="J2">
-        <v>5.87</v>
+        <v>5.06</v>
       </c>
       <c r="K2">
-        <v>4.94</v>
+        <v>3.88</v>
       </c>
       <c r="L2">
-        <v>11.34</v>
+        <v>10.48</v>
       </c>
       <c r="M2">
-        <v>21.24</v>
+        <v>21.7</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P2">
-        <v>4059.74</v>
+        <v>4064</v>
       </c>
       <c r="Q2">
-        <v>3972.36</v>
+        <v>3983.56</v>
       </c>
       <c r="R2">
-        <v>3999.99</v>
+        <v>4002.8</v>
       </c>
       <c r="S2">
-        <v>3952.15</v>
+        <v>3952.61</v>
       </c>
       <c r="T2">
-        <v>2.84</v>
+        <v>2.24</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -986,34 +949,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>58.28</v>
+        <v>55.19</v>
       </c>
       <c r="Z2">
-        <v>36.36</v>
+        <v>34.26</v>
       </c>
       <c r="AA2">
-        <v>23.52</v>
+        <v>25.66</v>
       </c>
       <c r="AB2">
-        <v>12.84</v>
+        <v>8.59</v>
       </c>
       <c r="AC2">
-        <v>69.11</v>
+        <v>49.95</v>
       </c>
       <c r="AD2">
-        <v>76.8</v>
+        <v>66.94</v>
       </c>
       <c r="AE2">
-        <v>60.16</v>
+        <v>59.02</v>
       </c>
       <c r="AF2">
-        <v>-17.2</v>
+        <v>-27.06</v>
       </c>
       <c r="AG2">
-        <v>4189.69</v>
+        <v>4190.07</v>
       </c>
       <c r="AH2">
-        <v>3755.04</v>
+        <v>3777.05</v>
       </c>
       <c r="AI2">
         <v>3887.02</v>
@@ -1022,7 +985,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>35.44</v>
+        <v>32.16</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1033,58 +996,58 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>325.1</v>
+        <v>315.4</v>
       </c>
       <c r="D3">
-        <v>3.21</v>
+        <v>-2.98</v>
       </c>
       <c r="E3">
         <v>335.6</v>
       </c>
       <c r="F3">
-        <v>199.29</v>
+        <v>200.02</v>
       </c>
       <c r="G3">
-        <v>-3.13</v>
+        <v>-6.02</v>
       </c>
       <c r="H3">
-        <v>63.13</v>
+        <v>57.68</v>
       </c>
       <c r="I3">
-        <v>3.08</v>
+        <v>-0.57</v>
       </c>
       <c r="J3">
-        <v>6.29</v>
+        <v>2.82</v>
       </c>
       <c r="K3">
-        <v>19.15</v>
+        <v>18.08</v>
       </c>
       <c r="L3">
-        <v>66.06999999999999</v>
+        <v>58.26</v>
       </c>
       <c r="M3">
-        <v>33.5</v>
+        <v>33.53</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P3">
-        <v>315.79</v>
+        <v>315.43</v>
       </c>
       <c r="Q3">
-        <v>312.47</v>
+        <v>312.94</v>
       </c>
       <c r="R3">
-        <v>306.19</v>
+        <v>307.19</v>
       </c>
       <c r="S3">
-        <v>289.8</v>
+        <v>290.05</v>
       </c>
       <c r="T3">
-        <v>12.18</v>
+        <v>8.74</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1099,34 +1062,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>60.6</v>
+        <v>52.39</v>
       </c>
       <c r="Z3">
-        <v>2.73</v>
+        <v>2.57</v>
       </c>
       <c r="AA3">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="AB3">
-        <v>0.14</v>
+        <v>-0.02</v>
       </c>
       <c r="AC3">
-        <v>52.1</v>
+        <v>66.92</v>
       </c>
       <c r="AD3">
-        <v>44.41</v>
+        <v>52.05</v>
       </c>
       <c r="AE3">
-        <v>9.279999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AF3">
-        <v>113.08</v>
+        <v>194.6</v>
       </c>
       <c r="AG3">
-        <v>323.98</v>
+        <v>324.09</v>
       </c>
       <c r="AH3">
-        <v>300.96</v>
+        <v>301.8</v>
       </c>
       <c r="AI3">
         <v>329.06</v>
@@ -1135,7 +1098,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>17.33</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1146,10 +1109,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3509.9</v>
+        <v>3540.9</v>
       </c>
       <c r="D4">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1158,46 +1121,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-24.42</v>
+        <v>-23.75</v>
       </c>
       <c r="H4">
-        <v>15.41</v>
+        <v>16.43</v>
       </c>
       <c r="I4">
-        <v>-3.91</v>
+        <v>-1.06</v>
       </c>
       <c r="J4">
-        <v>4.79</v>
+        <v>7.09</v>
       </c>
       <c r="K4">
-        <v>-0.87</v>
+        <v>-0.18</v>
       </c>
       <c r="L4">
-        <v>-14.9</v>
+        <v>-13.1</v>
       </c>
       <c r="M4">
-        <v>-0.52</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="P4">
-        <v>3529.42</v>
+        <v>3521.82</v>
       </c>
       <c r="Q4">
-        <v>3530.14</v>
+        <v>3540.53</v>
       </c>
       <c r="R4">
-        <v>3394.2</v>
+        <v>3396.66</v>
       </c>
       <c r="S4">
-        <v>3681.64</v>
+        <v>3679.03</v>
       </c>
       <c r="T4">
-        <v>-4.66</v>
+        <v>-3.75</v>
       </c>
       <c r="U4" t="s">
         <v>42</v>
@@ -1212,34 +1175,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>51.53</v>
+        <v>53.77</v>
       </c>
       <c r="Z4">
-        <v>40.82</v>
+        <v>38.36</v>
       </c>
       <c r="AA4">
-        <v>55.85</v>
+        <v>52.36</v>
       </c>
       <c r="AB4">
-        <v>-15.03</v>
+        <v>-14</v>
       </c>
       <c r="AC4">
-        <v>5.44</v>
+        <v>15.85</v>
       </c>
       <c r="AD4">
-        <v>11.21</v>
+        <v>10.78</v>
       </c>
       <c r="AE4">
-        <v>112.71</v>
+        <v>112.9</v>
       </c>
       <c r="AF4">
-        <v>-55.17</v>
+        <v>39.59</v>
       </c>
       <c r="AG4">
-        <v>3693.58</v>
+        <v>3675.12</v>
       </c>
       <c r="AH4">
-        <v>3366.71</v>
+        <v>3405.94</v>
       </c>
       <c r="AI4">
         <v>3316.13</v>
@@ -1248,7 +1211,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>26.9</v>
+        <v>25.58</v>
       </c>
     </row>
   </sheetData>
@@ -1389,7 +1352,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1409,502 +1372,447 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>63</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>5.87</v>
+      </c>
+      <c r="D7" s="5">
+        <v>5.06</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>6.29</v>
+      </c>
+      <c r="D8" s="5">
+        <v>2.82</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-3.47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>4.79</v>
+      </c>
+      <c r="D9" s="5">
+        <v>7.09</v>
+      </c>
+      <c r="E9" s="7">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>7.45</v>
-      </c>
-      <c r="D8" s="6">
-        <v>5.87</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-1.58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0.67</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0.53</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-1.05</v>
-      </c>
-      <c r="D9" s="6">
-        <v>6.29</v>
-      </c>
-      <c r="E9" s="8">
-        <v>7.34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5">
+        <v>3.08</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-0.57</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-3.65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-0.1</v>
-      </c>
-      <c r="D10" s="6">
-        <v>4.79</v>
-      </c>
-      <c r="E10" s="8">
-        <v>4.89</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-3.91</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-1.06</v>
+      </c>
+      <c r="E12" s="7">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.02</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5">
+        <v>11.34</v>
+      </c>
+      <c r="D13" s="5">
+        <v>10.48</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5">
+        <v>66.06999999999999</v>
+      </c>
+      <c r="D14" s="5">
+        <v>58.26</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-7.81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-14.9</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-13.1</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>4.94</v>
+      </c>
+      <c r="D16" s="5">
+        <v>3.88</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>19.15</v>
+      </c>
+      <c r="D17" s="5">
+        <v>18.08</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-1.07</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-0.87</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.18</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-7.11</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-7.64</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-3.13</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-6.02</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-2.89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-24.42</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-23.75</v>
+      </c>
+      <c r="E21" s="7">
         <v>0.67</v>
       </c>
-      <c r="E11" s="8">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5">
+        <v>4064.3</v>
+      </c>
+      <c r="D22" s="5">
+        <v>4041.3</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-0.55</v>
-      </c>
-      <c r="D12" s="6">
-        <v>3.08</v>
-      </c>
-      <c r="E12" s="8">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5">
+        <v>325.1</v>
+      </c>
+      <c r="D23" s="5">
+        <v>315.4</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-9.699999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-3.39</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-3.91</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5">
+        <v>3509.9</v>
+      </c>
+      <c r="D24" s="5">
+        <v>3540.9</v>
+      </c>
+      <c r="E24" s="7">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="6">
-        <v>13.56</v>
-      </c>
-      <c r="D14" s="6">
-        <v>11.34</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-2.22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="5">
+        <v>58.28</v>
+      </c>
+      <c r="D25" s="5">
+        <v>55.19</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-3.09</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="6">
-        <v>58.08</v>
-      </c>
-      <c r="D15" s="6">
-        <v>66.06999999999999</v>
-      </c>
-      <c r="E15" s="8">
-        <v>7.99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="5">
+        <v>60.6</v>
+      </c>
+      <c r="D26" s="5">
+        <v>52.39</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-8.210000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-15.53</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-14.9</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
+        <v>51.53</v>
+      </c>
+      <c r="D27" s="5">
+        <v>53.77</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="6">
-        <v>4.56</v>
-      </c>
-      <c r="D17" s="6">
-        <v>4.94</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-17.2</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-27.06</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-9.859999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="6">
-        <v>11.01</v>
-      </c>
-      <c r="D18" s="6">
-        <v>19.15</v>
-      </c>
-      <c r="E18" s="8">
-        <v>8.140000000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="5">
+        <v>113.08</v>
+      </c>
+      <c r="D29" s="5">
+        <v>194.6</v>
+      </c>
+      <c r="E29" s="7">
+        <v>81.52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-0.87</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-7.28</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-7.11</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-8.73</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-3.13</v>
-      </c>
-      <c r="E21" s="8">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-25.13</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-24.42</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6">
-        <v>4057</v>
-      </c>
-      <c r="D23" s="6">
-        <v>4064.3</v>
-      </c>
-      <c r="E23" s="8">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="6">
-        <v>306.3</v>
-      </c>
-      <c r="D24" s="6">
-        <v>325.1</v>
-      </c>
-      <c r="E24" s="8">
-        <v>18.8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" s="6">
-        <v>3476.8</v>
-      </c>
-      <c r="D25" s="6">
-        <v>3509.9</v>
-      </c>
-      <c r="E25" s="8">
-        <v>33.1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="6">
-        <v>58.68</v>
-      </c>
-      <c r="D26" s="6">
-        <v>58.28</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="6">
-        <v>45.82</v>
-      </c>
-      <c r="D27" s="6">
-        <v>60.6</v>
-      </c>
-      <c r="E27" s="8">
-        <v>14.78</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="6">
-        <v>49.09</v>
-      </c>
-      <c r="D28" s="6">
-        <v>51.53</v>
-      </c>
-      <c r="E28" s="8">
-        <v>2.44</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="6">
-        <v>-47.36</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-17.2</v>
-      </c>
-      <c r="E29" s="8">
-        <v>30.16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-21.62</v>
-      </c>
-      <c r="D30" s="6">
-        <v>113.08</v>
-      </c>
-      <c r="E30" s="8">
-        <v>134.7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="6">
-        <v>10.5</v>
-      </c>
-      <c r="D31" s="6">
+      <c r="C30" s="5">
         <v>-55.17</v>
       </c>
-      <c r="E31" s="7">
-        <v>-65.67</v>
+      <c r="D30" s="5">
+        <v>39.59</v>
+      </c>
+      <c r="E30" s="7">
+        <v>94.76000000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1924,60 +1832,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="10">
+        <v>64.52</v>
+      </c>
+      <c r="C2" s="11">
+        <v>3</v>
+      </c>
+      <c r="D2" s="10">
+        <v>53.8</v>
+      </c>
+      <c r="E2" s="10">
         <v>70</v>
       </c>
-      <c r="I1" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="11">
-        <v>64.52</v>
-      </c>
-      <c r="C2" s="12">
-        <v>3</v>
-      </c>
-      <c r="D2" s="11">
-        <v>56.8</v>
-      </c>
-      <c r="E2" s="11">
-        <v>70</v>
-      </c>
-      <c r="F2" s="11">
-        <v>5.6</v>
-      </c>
-      <c r="G2" s="11">
-        <v>7.7</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>5</v>
+      </c>
+      <c r="G2" s="10">
+        <v>7.3</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>30</v>
       </c>
     </row>
@@ -2079,25 +1987,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.335</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.2124</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0052</v>
+      <c r="A2" s="13">
+        <v>0.3353</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.217</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.005600000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -246,14 +246,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,13 +286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -883,10 +883,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>4041.3</v>
+        <v>4081</v>
       </c>
       <c r="D2">
-        <v>-0.57</v>
+        <v>0.98</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -895,25 +895,25 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-7.64</v>
+        <v>-6.73</v>
       </c>
       <c r="H2">
-        <v>22.09</v>
+        <v>23.29</v>
       </c>
       <c r="I2">
-        <v>0.53</v>
+        <v>0.25</v>
       </c>
       <c r="J2">
-        <v>5.06</v>
+        <v>6.91</v>
       </c>
       <c r="K2">
-        <v>3.88</v>
+        <v>3.93</v>
       </c>
       <c r="L2">
-        <v>10.48</v>
+        <v>12.07</v>
       </c>
       <c r="M2">
-        <v>21.7</v>
+        <v>21.93</v>
       </c>
       <c r="N2">
         <v>66</v>
@@ -922,19 +922,19 @@
         <v>64</v>
       </c>
       <c r="P2">
-        <v>4064</v>
+        <v>4066.06</v>
       </c>
       <c r="Q2">
-        <v>3983.56</v>
+        <v>3997.99</v>
       </c>
       <c r="R2">
-        <v>4002.8</v>
+        <v>4006.07</v>
       </c>
       <c r="S2">
-        <v>3952.61</v>
+        <v>3953.06</v>
       </c>
       <c r="T2">
-        <v>2.24</v>
+        <v>3.24</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -949,43 +949,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>55.19</v>
+        <v>59.22</v>
       </c>
       <c r="Z2">
-        <v>34.26</v>
+        <v>35.39</v>
       </c>
       <c r="AA2">
-        <v>25.66</v>
+        <v>27.61</v>
       </c>
       <c r="AB2">
-        <v>8.59</v>
+        <v>7.78</v>
       </c>
       <c r="AC2">
-        <v>49.95</v>
+        <v>39.11</v>
       </c>
       <c r="AD2">
-        <v>66.94</v>
+        <v>52.72</v>
       </c>
       <c r="AE2">
-        <v>59.02</v>
+        <v>57.92</v>
       </c>
       <c r="AF2">
-        <v>-27.06</v>
+        <v>-34.92</v>
       </c>
       <c r="AG2">
-        <v>4190.07</v>
+        <v>4187.93</v>
       </c>
       <c r="AH2">
-        <v>3777.05</v>
+        <v>3808.05</v>
       </c>
       <c r="AI2">
-        <v>3887.02</v>
+        <v>3892.84</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>32.16</v>
+        <v>30.66</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -996,58 +996,58 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>315.4</v>
+        <v>314.75</v>
       </c>
       <c r="D3">
-        <v>-2.98</v>
+        <v>-0.21</v>
       </c>
       <c r="E3">
         <v>335.6</v>
       </c>
       <c r="F3">
-        <v>200.02</v>
+        <v>208.31</v>
       </c>
       <c r="G3">
-        <v>-6.02</v>
+        <v>-6.21</v>
       </c>
       <c r="H3">
-        <v>57.68</v>
+        <v>51.1</v>
       </c>
       <c r="I3">
-        <v>-0.57</v>
+        <v>-0.19</v>
       </c>
       <c r="J3">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="K3">
-        <v>18.08</v>
+        <v>16.51</v>
       </c>
       <c r="L3">
-        <v>58.26</v>
+        <v>57.36</v>
       </c>
       <c r="M3">
-        <v>33.53</v>
+        <v>33.45</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P3">
-        <v>315.43</v>
+        <v>315.31</v>
       </c>
       <c r="Q3">
-        <v>312.94</v>
+        <v>313.43</v>
       </c>
       <c r="R3">
-        <v>307.19</v>
+        <v>308.28</v>
       </c>
       <c r="S3">
-        <v>290.05</v>
+        <v>290.28</v>
       </c>
       <c r="T3">
-        <v>8.74</v>
+        <v>8.43</v>
       </c>
       <c r="U3" t="s">
         <v>42</v>
@@ -1062,34 +1062,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>52.39</v>
+        <v>51.88</v>
       </c>
       <c r="Z3">
-        <v>2.57</v>
+        <v>2.36</v>
       </c>
       <c r="AA3">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="AB3">
-        <v>-0.02</v>
+        <v>-0.19</v>
       </c>
       <c r="AC3">
-        <v>66.92</v>
+        <v>61.82</v>
       </c>
       <c r="AD3">
-        <v>52.05</v>
+        <v>60.28</v>
       </c>
       <c r="AE3">
-        <v>9.640000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AF3">
-        <v>194.6</v>
+        <v>-41.15</v>
       </c>
       <c r="AG3">
-        <v>324.09</v>
+        <v>323.96</v>
       </c>
       <c r="AH3">
-        <v>301.8</v>
+        <v>302.9</v>
       </c>
       <c r="AI3">
         <v>329.06</v>
@@ -1098,7 +1098,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>17.24</v>
+        <v>17.16</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1109,10 +1109,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3540.9</v>
+        <v>3579.1</v>
       </c>
       <c r="D4">
-        <v>0.88</v>
+        <v>1.08</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1121,46 +1121,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-23.75</v>
+        <v>-22.93</v>
       </c>
       <c r="H4">
-        <v>16.43</v>
+        <v>17.68</v>
       </c>
       <c r="I4">
-        <v>-1.06</v>
+        <v>-0.71</v>
       </c>
       <c r="J4">
-        <v>7.09</v>
+        <v>7.38</v>
       </c>
       <c r="K4">
-        <v>-0.18</v>
+        <v>4.67</v>
       </c>
       <c r="L4">
-        <v>-13.1</v>
+        <v>-12.49</v>
       </c>
       <c r="M4">
-        <v>-0.5600000000000001</v>
+        <v>-0.34</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P4">
-        <v>3521.82</v>
+        <v>3516.7</v>
       </c>
       <c r="Q4">
-        <v>3540.53</v>
+        <v>3550.72</v>
       </c>
       <c r="R4">
-        <v>3396.66</v>
+        <v>3401.69</v>
       </c>
       <c r="S4">
-        <v>3679.03</v>
+        <v>3676.56</v>
       </c>
       <c r="T4">
-        <v>-3.75</v>
+        <v>-2.65</v>
       </c>
       <c r="U4" t="s">
         <v>42</v>
@@ -1175,34 +1175,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>53.77</v>
+        <v>56.44</v>
       </c>
       <c r="Z4">
-        <v>38.36</v>
+        <v>39.04</v>
       </c>
       <c r="AA4">
-        <v>52.36</v>
+        <v>49.69</v>
       </c>
       <c r="AB4">
-        <v>-14</v>
+        <v>-10.65</v>
       </c>
       <c r="AC4">
-        <v>15.85</v>
+        <v>32.2</v>
       </c>
       <c r="AD4">
-        <v>10.78</v>
+        <v>17.83</v>
       </c>
       <c r="AE4">
-        <v>112.9</v>
+        <v>113.62</v>
       </c>
       <c r="AF4">
-        <v>39.59</v>
+        <v>50.85</v>
       </c>
       <c r="AG4">
-        <v>3675.12</v>
+        <v>3661.37</v>
       </c>
       <c r="AH4">
-        <v>3405.94</v>
+        <v>3440.07</v>
       </c>
       <c r="AI4">
         <v>3316.13</v>
@@ -1211,7 +1211,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>25.58</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1409,13 +1409,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>5.87</v>
+        <v>5.06</v>
       </c>
       <c r="D7" s="5">
-        <v>5.06</v>
+        <v>6.91</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.8100000000000001</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1426,13 +1426,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>6.29</v>
+        <v>2.82</v>
       </c>
       <c r="D8" s="5">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="E8" s="6">
-        <v>-3.47</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1443,13 +1443,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>4.79</v>
+        <v>7.09</v>
       </c>
       <c r="D9" s="5">
-        <v>7.09</v>
-      </c>
-      <c r="E9" s="7">
-        <v>2.3</v>
+        <v>7.38</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.29</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1460,13 +1460,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>0.67</v>
+        <v>0.53</v>
       </c>
       <c r="D10" s="5">
-        <v>0.53</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-0.14</v>
+        <v>0.25</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1477,13 +1477,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>3.08</v>
+        <v>-0.57</v>
       </c>
       <c r="D11" s="5">
-        <v>-0.57</v>
+        <v>-0.19</v>
       </c>
       <c r="E11" s="6">
-        <v>-3.65</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1494,13 +1494,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-3.91</v>
+        <v>-1.06</v>
       </c>
       <c r="D12" s="5">
-        <v>-1.06</v>
-      </c>
-      <c r="E12" s="7">
-        <v>2.85</v>
+        <v>-0.71</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.35</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1511,13 +1511,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>11.34</v>
+        <v>10.48</v>
       </c>
       <c r="D13" s="5">
-        <v>10.48</v>
+        <v>12.07</v>
       </c>
       <c r="E13" s="6">
-        <v>-0.86</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1528,13 +1528,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>66.06999999999999</v>
+        <v>58.26</v>
       </c>
       <c r="D14" s="5">
-        <v>58.26</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-7.81</v>
+        <v>57.36</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1545,13 +1545,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-14.9</v>
+        <v>-13.1</v>
       </c>
       <c r="D15" s="5">
-        <v>-13.1</v>
-      </c>
-      <c r="E15" s="7">
-        <v>1.8</v>
+        <v>-12.49</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.61</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1562,13 +1562,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>4.94</v>
+        <v>3.88</v>
       </c>
       <c r="D16" s="5">
-        <v>3.88</v>
+        <v>3.93</v>
       </c>
       <c r="E16" s="6">
-        <v>-1.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1579,13 +1579,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>19.15</v>
+        <v>18.08</v>
       </c>
       <c r="D17" s="5">
-        <v>18.08</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-1.07</v>
+        <v>16.51</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.57</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1596,13 +1596,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-0.87</v>
+        <v>-0.18</v>
       </c>
       <c r="D18" s="5">
-        <v>-0.18</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.6899999999999999</v>
+        <v>4.67</v>
+      </c>
+      <c r="E18" s="6">
+        <v>4.85</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1613,13 +1613,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-7.11</v>
+        <v>-7.64</v>
       </c>
       <c r="D19" s="5">
-        <v>-7.64</v>
+        <v>-6.73</v>
       </c>
       <c r="E19" s="6">
-        <v>-0.53</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1630,13 +1630,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-3.13</v>
+        <v>-6.02</v>
       </c>
       <c r="D20" s="5">
-        <v>-6.02</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-2.89</v>
+        <v>-6.21</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1647,13 +1647,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-24.42</v>
+        <v>-23.75</v>
       </c>
       <c r="D21" s="5">
-        <v>-23.75</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.67</v>
+        <v>-22.93</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.82</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1664,13 +1664,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>4064.3</v>
+        <v>4041.3</v>
       </c>
       <c r="D22" s="5">
-        <v>4041.3</v>
+        <v>4081</v>
       </c>
       <c r="E22" s="6">
-        <v>-23</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1681,13 +1681,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>325.1</v>
+        <v>315.4</v>
       </c>
       <c r="D23" s="5">
-        <v>315.4</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-9.699999999999999</v>
+        <v>314.75</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1698,13 +1698,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>3509.9</v>
+        <v>3540.9</v>
       </c>
       <c r="D24" s="5">
-        <v>3540.9</v>
-      </c>
-      <c r="E24" s="7">
-        <v>31</v>
+        <v>3579.1</v>
+      </c>
+      <c r="E24" s="6">
+        <v>38.2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1715,13 +1715,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>58.28</v>
+        <v>55.19</v>
       </c>
       <c r="D25" s="5">
-        <v>55.19</v>
+        <v>59.22</v>
       </c>
       <c r="E25" s="6">
-        <v>-3.09</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>60.6</v>
+        <v>52.39</v>
       </c>
       <c r="D26" s="5">
-        <v>52.39</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-8.210000000000001</v>
+        <v>51.88</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1749,13 +1749,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>51.53</v>
+        <v>53.77</v>
       </c>
       <c r="D27" s="5">
-        <v>53.77</v>
-      </c>
-      <c r="E27" s="7">
-        <v>2.24</v>
+        <v>56.44</v>
+      </c>
+      <c r="E27" s="6">
+        <v>2.67</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1766,13 +1766,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>-17.2</v>
+        <v>-27.06</v>
       </c>
       <c r="D28" s="5">
-        <v>-27.06</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-9.859999999999999</v>
+        <v>-34.92</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-7.86</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1783,13 +1783,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>113.08</v>
+        <v>194.6</v>
       </c>
       <c r="D29" s="5">
-        <v>194.6</v>
+        <v>-41.15</v>
       </c>
       <c r="E29" s="7">
-        <v>81.52</v>
+        <v>-235.75</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1800,13 +1800,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-55.17</v>
+        <v>39.59</v>
       </c>
       <c r="D30" s="5">
-        <v>39.59</v>
-      </c>
-      <c r="E30" s="7">
-        <v>94.76000000000001</v>
+        <v>50.85</v>
+      </c>
+      <c r="E30" s="6">
+        <v>11.26</v>
       </c>
     </row>
   </sheetData>
@@ -1871,16 +1871,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>53.8</v>
+        <v>55.8</v>
       </c>
       <c r="E2" s="10">
         <v>70</v>
       </c>
       <c r="F2" s="10">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="G2" s="10">
-        <v>7.3</v>
+        <v>8.4</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -1999,13 +1999,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.3353</v>
+        <v>0.3345</v>
       </c>
       <c r="B2" s="13">
-        <v>0.217</v>
+        <v>0.2193</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.005600000000000001</v>
+        <v>-0.0034</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -145,10 +145,10 @@
     <t>Unknown</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>No</t>
-  </si>
-  <si>
-    <t>Yes</t>
   </si>
   <si>
     <t>UP</t>
@@ -883,10 +883,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>4081</v>
+        <v>4090</v>
       </c>
       <c r="D2">
-        <v>0.98</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -895,97 +895,97 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-6.73</v>
+        <v>-6.52</v>
       </c>
       <c r="H2">
-        <v>23.29</v>
+        <v>23.56</v>
       </c>
       <c r="I2">
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
       <c r="J2">
-        <v>6.91</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="K2">
-        <v>3.93</v>
+        <v>1.29</v>
       </c>
       <c r="L2">
-        <v>12.07</v>
+        <v>14.31</v>
       </c>
       <c r="M2">
-        <v>21.93</v>
+        <v>21.8</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P2">
-        <v>4066.06</v>
+        <v>4073.92</v>
       </c>
       <c r="Q2">
-        <v>3997.99</v>
+        <v>4027.56</v>
       </c>
       <c r="R2">
-        <v>4006.07</v>
+        <v>4011.51</v>
       </c>
       <c r="S2">
-        <v>3953.06</v>
+        <v>3954.83</v>
       </c>
       <c r="T2">
-        <v>3.24</v>
+        <v>3.42</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
       </c>
       <c r="V2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W2" t="s">
         <v>41</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y2">
-        <v>59.22</v>
+        <v>59.92</v>
       </c>
       <c r="Z2">
-        <v>35.39</v>
+        <v>37.3</v>
       </c>
       <c r="AA2">
-        <v>27.61</v>
+        <v>31.02</v>
       </c>
       <c r="AB2">
-        <v>7.78</v>
+        <v>6.27</v>
       </c>
       <c r="AC2">
-        <v>39.11</v>
+        <v>54.37</v>
       </c>
       <c r="AD2">
-        <v>52.72</v>
+        <v>45.4</v>
       </c>
       <c r="AE2">
-        <v>57.92</v>
+        <v>54.6</v>
       </c>
       <c r="AF2">
-        <v>-34.92</v>
+        <v>-15.3</v>
       </c>
       <c r="AG2">
-        <v>4187.93</v>
+        <v>4164.75</v>
       </c>
       <c r="AH2">
-        <v>3808.05</v>
+        <v>3890.37</v>
       </c>
       <c r="AI2">
-        <v>3892.84</v>
+        <v>3928.6</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>30.66</v>
+        <v>30.92</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -996,37 +996,37 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>314.75</v>
+        <v>315.85</v>
       </c>
       <c r="D3">
-        <v>-0.21</v>
+        <v>-0.41</v>
       </c>
       <c r="E3">
         <v>335.6</v>
       </c>
       <c r="F3">
-        <v>208.31</v>
+        <v>214.23</v>
       </c>
       <c r="G3">
-        <v>-6.21</v>
+        <v>-5.88</v>
       </c>
       <c r="H3">
-        <v>51.1</v>
+        <v>47.44</v>
       </c>
       <c r="I3">
-        <v>-0.19</v>
+        <v>0.27</v>
       </c>
       <c r="J3">
-        <v>2.89</v>
+        <v>4.45</v>
       </c>
       <c r="K3">
-        <v>16.51</v>
+        <v>11.73</v>
       </c>
       <c r="L3">
-        <v>57.36</v>
+        <v>47.03</v>
       </c>
       <c r="M3">
-        <v>33.45</v>
+        <v>33.46</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1035,61 +1035,61 @@
         <v>84</v>
       </c>
       <c r="P3">
-        <v>315.31</v>
+        <v>317.65</v>
       </c>
       <c r="Q3">
-        <v>313.43</v>
+        <v>314.35</v>
       </c>
       <c r="R3">
-        <v>308.28</v>
+        <v>310.28</v>
       </c>
       <c r="S3">
-        <v>290.28</v>
+        <v>290.68</v>
       </c>
       <c r="T3">
-        <v>8.43</v>
+        <v>8.66</v>
       </c>
       <c r="U3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X3">
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>51.88</v>
+        <v>52.53</v>
       </c>
       <c r="Z3">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="AA3">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="AB3">
-        <v>-0.19</v>
+        <v>-0.23</v>
       </c>
       <c r="AC3">
-        <v>61.82</v>
+        <v>46.5</v>
       </c>
       <c r="AD3">
-        <v>60.28</v>
+        <v>51.5</v>
       </c>
       <c r="AE3">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="AF3">
-        <v>-41.15</v>
+        <v>-36.25</v>
       </c>
       <c r="AG3">
-        <v>323.96</v>
+        <v>323.59</v>
       </c>
       <c r="AH3">
-        <v>302.9</v>
+        <v>305.1</v>
       </c>
       <c r="AI3">
         <v>329.06</v>
@@ -1098,7 +1098,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>17.16</v>
+        <v>19.19</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1109,10 +1109,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3579.1</v>
+        <v>3584.6</v>
       </c>
       <c r="D4">
-        <v>1.08</v>
+        <v>-0.55</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1121,88 +1121,88 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-22.93</v>
+        <v>-22.81</v>
       </c>
       <c r="H4">
-        <v>17.68</v>
+        <v>17.86</v>
       </c>
       <c r="I4">
-        <v>-0.71</v>
+        <v>3.1</v>
       </c>
       <c r="J4">
-        <v>7.38</v>
+        <v>4.87</v>
       </c>
       <c r="K4">
-        <v>4.67</v>
+        <v>1.24</v>
       </c>
       <c r="L4">
-        <v>-12.49</v>
+        <v>-12.76</v>
       </c>
       <c r="M4">
-        <v>-0.34</v>
+        <v>-0.1</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P4">
-        <v>3516.7</v>
+        <v>3563.82</v>
       </c>
       <c r="Q4">
-        <v>3550.72</v>
+        <v>3564.37</v>
       </c>
       <c r="R4">
-        <v>3401.69</v>
+        <v>3412.63</v>
       </c>
       <c r="S4">
-        <v>3676.56</v>
+        <v>3671.91</v>
       </c>
       <c r="T4">
-        <v>-2.65</v>
+        <v>-2.38</v>
       </c>
       <c r="U4" t="s">
+        <v>41</v>
+      </c>
+      <c r="V4" t="s">
         <v>42</v>
       </c>
-      <c r="V4" t="s">
-        <v>41</v>
-      </c>
       <c r="W4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="X4">
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>56.44</v>
+        <v>56.28</v>
       </c>
       <c r="Z4">
-        <v>39.04</v>
+        <v>40.76</v>
       </c>
       <c r="AA4">
-        <v>49.69</v>
+        <v>46.54</v>
       </c>
       <c r="AB4">
-        <v>-10.65</v>
+        <v>-5.78</v>
       </c>
       <c r="AC4">
-        <v>32.2</v>
+        <v>52.57</v>
       </c>
       <c r="AD4">
-        <v>17.83</v>
+        <v>43.92</v>
       </c>
       <c r="AE4">
-        <v>113.62</v>
+        <v>108.27</v>
       </c>
       <c r="AF4">
-        <v>50.85</v>
+        <v>-34.99</v>
       </c>
       <c r="AG4">
-        <v>3661.37</v>
+        <v>3653.96</v>
       </c>
       <c r="AH4">
-        <v>3440.07</v>
+        <v>3474.78</v>
       </c>
       <c r="AI4">
         <v>3316.13</v>
@@ -1211,7 +1211,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>26</v>
+        <v>28.19</v>
       </c>
     </row>
   </sheetData>
@@ -1409,13 +1409,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>5.06</v>
+        <v>7.93</v>
       </c>
       <c r="D7" s="5">
-        <v>6.91</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="E7" s="6">
-        <v>1.85</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1426,13 +1426,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>2.82</v>
+        <v>3.97</v>
       </c>
       <c r="D8" s="5">
-        <v>2.89</v>
+        <v>4.45</v>
       </c>
       <c r="E8" s="6">
-        <v>0.07000000000000001</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1443,13 +1443,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>7.09</v>
+        <v>6.79</v>
       </c>
       <c r="D9" s="5">
-        <v>7.38</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0.29</v>
+        <v>4.87</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.92</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1460,13 +1460,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>0.53</v>
+        <v>0.89</v>
       </c>
       <c r="D10" s="5">
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.28</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1477,13 +1477,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-0.57</v>
+        <v>3.54</v>
       </c>
       <c r="D11" s="5">
-        <v>-0.19</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0.38</v>
+        <v>0.27</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-3.27</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1494,13 +1494,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-1.06</v>
+        <v>3.68</v>
       </c>
       <c r="D12" s="5">
-        <v>-0.71</v>
-      </c>
-      <c r="E12" s="6">
-        <v>0.35</v>
+        <v>3.1</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1511,13 +1511,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>10.48</v>
+        <v>13.7</v>
       </c>
       <c r="D13" s="5">
-        <v>12.07</v>
+        <v>14.31</v>
       </c>
       <c r="E13" s="6">
-        <v>1.59</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1528,13 +1528,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>58.26</v>
+        <v>52.25</v>
       </c>
       <c r="D14" s="5">
-        <v>57.36</v>
+        <v>47.03</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.9</v>
+        <v>-5.22</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1545,13 +1545,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-13.1</v>
+        <v>-12.02</v>
       </c>
       <c r="D15" s="5">
-        <v>-12.49</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0.61</v>
+        <v>-12.76</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1562,13 +1562,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>3.88</v>
+        <v>1.48</v>
       </c>
       <c r="D16" s="5">
-        <v>3.93</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0.05</v>
+        <v>1.29</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1579,13 +1579,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>18.08</v>
+        <v>13.53</v>
       </c>
       <c r="D17" s="5">
-        <v>16.51</v>
+        <v>11.73</v>
       </c>
       <c r="E17" s="7">
-        <v>-1.57</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1596,13 +1596,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-0.18</v>
+        <v>1.65</v>
       </c>
       <c r="D18" s="5">
-        <v>4.67</v>
-      </c>
-      <c r="E18" s="6">
-        <v>4.85</v>
+        <v>1.24</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1613,13 +1613,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-7.64</v>
+        <v>-6.45</v>
       </c>
       <c r="D19" s="5">
-        <v>-6.73</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0.91</v>
+        <v>-6.52</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1630,13 +1630,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-6.02</v>
+        <v>-5.5</v>
       </c>
       <c r="D20" s="5">
-        <v>-6.21</v>
+        <v>-5.88</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.19</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1647,13 +1647,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-23.75</v>
+        <v>-22.38</v>
       </c>
       <c r="D21" s="5">
-        <v>-22.93</v>
-      </c>
-      <c r="E21" s="6">
-        <v>0.82</v>
+        <v>-22.81</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1664,13 +1664,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>4041.3</v>
+        <v>4093</v>
       </c>
       <c r="D22" s="5">
-        <v>4081</v>
-      </c>
-      <c r="E22" s="6">
-        <v>39.7</v>
+        <v>4090</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-3</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1681,13 +1681,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>315.4</v>
+        <v>317.15</v>
       </c>
       <c r="D23" s="5">
-        <v>314.75</v>
+        <v>315.85</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.65</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1698,13 +1698,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>3540.9</v>
+        <v>3604.6</v>
       </c>
       <c r="D24" s="5">
-        <v>3579.1</v>
-      </c>
-      <c r="E24" s="6">
-        <v>38.2</v>
+        <v>3584.6</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-20</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1715,13 +1715,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>55.19</v>
+        <v>60.37</v>
       </c>
       <c r="D25" s="5">
-        <v>59.22</v>
-      </c>
-      <c r="E25" s="6">
-        <v>4.03</v>
+        <v>59.92</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>52.39</v>
+        <v>53.66</v>
       </c>
       <c r="D26" s="5">
-        <v>51.88</v>
+        <v>52.53</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.51</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1749,13 +1749,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>53.77</v>
+        <v>58.17</v>
       </c>
       <c r="D27" s="5">
-        <v>56.44</v>
-      </c>
-      <c r="E27" s="6">
-        <v>2.67</v>
+        <v>56.28</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.89</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1766,13 +1766,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>-27.06</v>
+        <v>-22.19</v>
       </c>
       <c r="D28" s="5">
-        <v>-34.92</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-7.86</v>
+        <v>-15.3</v>
+      </c>
+      <c r="E28" s="6">
+        <v>6.89</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1783,13 +1783,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>194.6</v>
+        <v>-34.7</v>
       </c>
       <c r="D29" s="5">
-        <v>-41.15</v>
+        <v>-36.25</v>
       </c>
       <c r="E29" s="7">
-        <v>-235.75</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1800,13 +1800,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>39.59</v>
+        <v>-49.17</v>
       </c>
       <c r="D30" s="5">
-        <v>50.85</v>
+        <v>-34.99</v>
       </c>
       <c r="E30" s="6">
-        <v>11.26</v>
+        <v>14.18</v>
       </c>
     </row>
   </sheetData>
@@ -1871,22 +1871,22 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>55.8</v>
+        <v>56.2</v>
       </c>
       <c r="E2" s="10">
         <v>70</v>
       </c>
       <c r="F2" s="10">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="G2" s="10">
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
       </c>
       <c r="I2" s="10">
-        <v>30</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1999,13 +1999,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.3345</v>
+        <v>0.3346</v>
       </c>
       <c r="B2" s="13">
-        <v>0.2193</v>
+        <v>0.218</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0034</v>
+        <v>-0.001</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -883,10 +883,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>4090</v>
+        <v>4119</v>
       </c>
       <c r="D2">
-        <v>-0.07000000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -895,46 +895,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-6.52</v>
+        <v>-5.86</v>
       </c>
       <c r="H2">
-        <v>23.56</v>
+        <v>24.44</v>
       </c>
       <c r="I2">
-        <v>0.08</v>
+        <v>1.35</v>
       </c>
       <c r="J2">
-        <v>8.039999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="K2">
-        <v>1.29</v>
+        <v>1.77</v>
       </c>
       <c r="L2">
-        <v>14.31</v>
+        <v>15.78</v>
       </c>
       <c r="M2">
-        <v>21.8</v>
+        <v>22.15</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P2">
-        <v>4073.92</v>
+        <v>4084.86</v>
       </c>
       <c r="Q2">
-        <v>4027.56</v>
+        <v>4041.91</v>
       </c>
       <c r="R2">
-        <v>4011.51</v>
+        <v>4010.49</v>
       </c>
       <c r="S2">
-        <v>3954.83</v>
+        <v>3956.2</v>
       </c>
       <c r="T2">
-        <v>3.42</v>
+        <v>4.11</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -949,43 +949,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>59.92</v>
+        <v>62.85</v>
       </c>
       <c r="Z2">
-        <v>37.3</v>
+        <v>39.55</v>
       </c>
       <c r="AA2">
-        <v>31.02</v>
+        <v>32.73</v>
       </c>
       <c r="AB2">
-        <v>6.27</v>
+        <v>6.82</v>
       </c>
       <c r="AC2">
-        <v>54.37</v>
+        <v>68.56</v>
       </c>
       <c r="AD2">
-        <v>45.4</v>
+        <v>55.22</v>
       </c>
       <c r="AE2">
-        <v>54.6</v>
+        <v>54.89</v>
       </c>
       <c r="AF2">
-        <v>-15.3</v>
+        <v>-17.25</v>
       </c>
       <c r="AG2">
-        <v>4164.75</v>
+        <v>4149.9</v>
       </c>
       <c r="AH2">
-        <v>3890.37</v>
+        <v>3933.92</v>
       </c>
       <c r="AI2">
-        <v>3928.6</v>
+        <v>3931.27</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>30.92</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -996,10 +996,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>315.85</v>
+        <v>319.5</v>
       </c>
       <c r="D3">
-        <v>-0.41</v>
+        <v>1.16</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1008,25 +1008,25 @@
         <v>214.23</v>
       </c>
       <c r="G3">
-        <v>-5.88</v>
+        <v>-4.8</v>
       </c>
       <c r="H3">
-        <v>47.44</v>
+        <v>49.14</v>
       </c>
       <c r="I3">
-        <v>0.27</v>
+        <v>-1.72</v>
       </c>
       <c r="J3">
-        <v>4.45</v>
+        <v>2.32</v>
       </c>
       <c r="K3">
-        <v>11.73</v>
+        <v>13.42</v>
       </c>
       <c r="L3">
-        <v>47.03</v>
+        <v>49.08</v>
       </c>
       <c r="M3">
-        <v>33.46</v>
+        <v>33.56</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1035,19 +1035,19 @@
         <v>84</v>
       </c>
       <c r="P3">
-        <v>317.65</v>
+        <v>316.53</v>
       </c>
       <c r="Q3">
-        <v>314.35</v>
+        <v>314.77</v>
       </c>
       <c r="R3">
-        <v>310.28</v>
+        <v>310.8</v>
       </c>
       <c r="S3">
-        <v>290.68</v>
+        <v>290.91</v>
       </c>
       <c r="T3">
-        <v>8.66</v>
+        <v>9.83</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1062,34 +1062,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>52.53</v>
+        <v>55.38</v>
       </c>
       <c r="Z3">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="AA3">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AB3">
-        <v>-0.23</v>
+        <v>-0.05</v>
       </c>
       <c r="AC3">
-        <v>46.5</v>
+        <v>54.4</v>
       </c>
       <c r="AD3">
-        <v>51.5</v>
+        <v>49.03</v>
       </c>
       <c r="AE3">
-        <v>9.1</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AF3">
-        <v>-36.25</v>
+        <v>-28.32</v>
       </c>
       <c r="AG3">
-        <v>323.59</v>
+        <v>324.15</v>
       </c>
       <c r="AH3">
-        <v>305.1</v>
+        <v>305.39</v>
       </c>
       <c r="AI3">
         <v>329.06</v>
@@ -1098,7 +1098,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>19.19</v>
+        <v>20.41</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1109,10 +1109,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3584.6</v>
+        <v>3568.2</v>
       </c>
       <c r="D4">
-        <v>-0.55</v>
+        <v>-0.46</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1121,46 +1121,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-22.81</v>
+        <v>-23.16</v>
       </c>
       <c r="H4">
-        <v>17.86</v>
+        <v>17.32</v>
       </c>
       <c r="I4">
-        <v>3.1</v>
+        <v>1.66</v>
       </c>
       <c r="J4">
-        <v>4.87</v>
+        <v>2</v>
       </c>
       <c r="K4">
-        <v>1.24</v>
+        <v>2.19</v>
       </c>
       <c r="L4">
-        <v>-12.76</v>
+        <v>-14.4</v>
       </c>
       <c r="M4">
-        <v>-0.1</v>
+        <v>-0.35</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="P4">
-        <v>3563.82</v>
+        <v>3575.48</v>
       </c>
       <c r="Q4">
-        <v>3564.37</v>
+        <v>3562.81</v>
       </c>
       <c r="R4">
-        <v>3412.63</v>
+        <v>3416.08</v>
       </c>
       <c r="S4">
-        <v>3671.91</v>
+        <v>3669.48</v>
       </c>
       <c r="T4">
-        <v>-2.38</v>
+        <v>-2.76</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1175,34 +1175,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>56.28</v>
+        <v>54.71</v>
       </c>
       <c r="Z4">
-        <v>40.76</v>
+        <v>38.68</v>
       </c>
       <c r="AA4">
-        <v>46.54</v>
+        <v>44.97</v>
       </c>
       <c r="AB4">
-        <v>-5.78</v>
+        <v>-6.29</v>
       </c>
       <c r="AC4">
-        <v>52.57</v>
+        <v>48.72</v>
       </c>
       <c r="AD4">
-        <v>43.92</v>
+        <v>49.42</v>
       </c>
       <c r="AE4">
-        <v>108.27</v>
+        <v>104.76</v>
       </c>
       <c r="AF4">
-        <v>-34.99</v>
+        <v>-65.31</v>
       </c>
       <c r="AG4">
-        <v>3653.96</v>
+        <v>3650.92</v>
       </c>
       <c r="AH4">
-        <v>3474.78</v>
+        <v>3474.71</v>
       </c>
       <c r="AI4">
         <v>3316.13</v>
@@ -1211,7 +1211,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>28.19</v>
+        <v>27.78</v>
       </c>
     </row>
   </sheetData>
@@ -1409,13 +1409,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>7.93</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="D7" s="5">
-        <v>8.039999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="E7" s="6">
-        <v>0.11</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1426,13 +1426,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>3.97</v>
+        <v>4.45</v>
       </c>
       <c r="D8" s="5">
-        <v>4.45</v>
-      </c>
-      <c r="E8" s="6">
-        <v>0.48</v>
+        <v>2.32</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-2.13</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1443,13 +1443,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>6.79</v>
+        <v>4.87</v>
       </c>
       <c r="D9" s="5">
-        <v>4.87</v>
+        <v>2</v>
       </c>
       <c r="E9" s="7">
-        <v>-1.92</v>
+        <v>-2.87</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1460,13 +1460,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>0.89</v>
+        <v>0.08</v>
       </c>
       <c r="D10" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.8100000000000001</v>
+        <v>1.35</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1.27</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1477,13 +1477,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>3.54</v>
+        <v>0.27</v>
       </c>
       <c r="D11" s="5">
-        <v>0.27</v>
+        <v>-1.72</v>
       </c>
       <c r="E11" s="7">
-        <v>-3.27</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1494,13 +1494,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>3.68</v>
+        <v>3.1</v>
       </c>
       <c r="D12" s="5">
-        <v>3.1</v>
+        <v>1.66</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.58</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1511,13 +1511,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>13.7</v>
+        <v>14.31</v>
       </c>
       <c r="D13" s="5">
-        <v>14.31</v>
+        <v>15.78</v>
       </c>
       <c r="E13" s="6">
-        <v>0.61</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1528,13 +1528,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>52.25</v>
+        <v>47.03</v>
       </c>
       <c r="D14" s="5">
-        <v>47.03</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-5.22</v>
+        <v>49.08</v>
+      </c>
+      <c r="E14" s="6">
+        <v>2.05</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1545,13 +1545,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-12.02</v>
+        <v>-12.76</v>
       </c>
       <c r="D15" s="5">
-        <v>-12.76</v>
+        <v>-14.4</v>
       </c>
       <c r="E15" s="7">
-        <v>-0.74</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1562,13 +1562,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="D16" s="5">
-        <v>1.29</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-0.19</v>
+        <v>1.77</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.48</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1579,13 +1579,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>13.53</v>
+        <v>11.73</v>
       </c>
       <c r="D17" s="5">
-        <v>11.73</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.8</v>
+        <v>13.42</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1.69</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1596,13 +1596,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="D18" s="5">
-        <v>1.24</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.41</v>
+        <v>2.19</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.95</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1613,13 +1613,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-6.45</v>
+        <v>-6.52</v>
       </c>
       <c r="D19" s="5">
-        <v>-6.52</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.07000000000000001</v>
+        <v>-5.86</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.66</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1630,13 +1630,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-5.5</v>
+        <v>-5.88</v>
       </c>
       <c r="D20" s="5">
-        <v>-5.88</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.38</v>
+        <v>-4.8</v>
+      </c>
+      <c r="E20" s="6">
+        <v>1.08</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1647,13 +1647,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-22.38</v>
+        <v>-22.81</v>
       </c>
       <c r="D21" s="5">
-        <v>-22.81</v>
+        <v>-23.16</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.43</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1664,13 +1664,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>4093</v>
+        <v>4090</v>
       </c>
       <c r="D22" s="5">
-        <v>4090</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-3</v>
+        <v>4119</v>
+      </c>
+      <c r="E22" s="6">
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1681,13 +1681,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>317.15</v>
+        <v>315.85</v>
       </c>
       <c r="D23" s="5">
-        <v>315.85</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-1.3</v>
+        <v>319.5</v>
+      </c>
+      <c r="E23" s="6">
+        <v>3.65</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1698,13 +1698,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>3604.6</v>
+        <v>3584.6</v>
       </c>
       <c r="D24" s="5">
-        <v>3584.6</v>
+        <v>3568.2</v>
       </c>
       <c r="E24" s="7">
-        <v>-20</v>
+        <v>-16.4</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1715,13 +1715,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>60.37</v>
+        <v>59.92</v>
       </c>
       <c r="D25" s="5">
-        <v>59.92</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.45</v>
+        <v>62.85</v>
+      </c>
+      <c r="E25" s="6">
+        <v>2.93</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>53.66</v>
+        <v>52.53</v>
       </c>
       <c r="D26" s="5">
-        <v>52.53</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.13</v>
+        <v>55.38</v>
+      </c>
+      <c r="E26" s="6">
+        <v>2.85</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1749,13 +1749,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>58.17</v>
+        <v>56.28</v>
       </c>
       <c r="D27" s="5">
-        <v>56.28</v>
+        <v>54.71</v>
       </c>
       <c r="E27" s="7">
-        <v>-1.89</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1766,13 +1766,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>-22.19</v>
+        <v>-15.3</v>
       </c>
       <c r="D28" s="5">
-        <v>-15.3</v>
-      </c>
-      <c r="E28" s="6">
-        <v>6.89</v>
+        <v>-17.25</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-1.95</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1783,13 +1783,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-34.7</v>
+        <v>-36.25</v>
       </c>
       <c r="D29" s="5">
-        <v>-36.25</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.55</v>
+        <v>-28.32</v>
+      </c>
+      <c r="E29" s="6">
+        <v>7.93</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1800,13 +1800,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-49.17</v>
+        <v>-34.99</v>
       </c>
       <c r="D30" s="5">
-        <v>-34.99</v>
-      </c>
-      <c r="E30" s="6">
-        <v>14.18</v>
+        <v>-65.31</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-30.32</v>
       </c>
     </row>
   </sheetData>
@@ -1871,16 +1871,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>56.2</v>
+        <v>57.6</v>
       </c>
       <c r="E2" s="10">
         <v>70</v>
       </c>
       <c r="F2" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="G2" s="10">
         <v>5.8</v>
-      </c>
-      <c r="G2" s="10">
-        <v>4.8</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -1999,13 +1999,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.3346</v>
+        <v>0.3356</v>
       </c>
       <c r="B2" s="13">
-        <v>0.218</v>
+        <v>0.2215</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.001</v>
+        <v>-0.0035</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -246,14 +246,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,13 +286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -883,10 +883,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>4119</v>
+        <v>4038.1</v>
       </c>
       <c r="D2">
-        <v>0.71</v>
+        <v>-1.96</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -895,46 +895,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-5.86</v>
+        <v>-7.71</v>
       </c>
       <c r="H2">
-        <v>24.44</v>
+        <v>21.99</v>
       </c>
       <c r="I2">
-        <v>1.35</v>
+        <v>-0.08</v>
       </c>
       <c r="J2">
-        <v>8.220000000000001</v>
+        <v>5.38</v>
       </c>
       <c r="K2">
-        <v>1.77</v>
+        <v>-0.23</v>
       </c>
       <c r="L2">
-        <v>15.78</v>
+        <v>12.87</v>
       </c>
       <c r="M2">
-        <v>22.15</v>
+        <v>21.64</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="P2">
-        <v>4084.86</v>
+        <v>4084.22</v>
       </c>
       <c r="Q2">
-        <v>4041.91</v>
+        <v>4047.24</v>
       </c>
       <c r="R2">
-        <v>4010.49</v>
+        <v>4007.52</v>
       </c>
       <c r="S2">
-        <v>3956.2</v>
+        <v>3957.17</v>
       </c>
       <c r="T2">
-        <v>4.11</v>
+        <v>2.05</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -949,34 +949,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>62.85</v>
+        <v>51.52</v>
       </c>
       <c r="Z2">
-        <v>39.55</v>
+        <v>34.42</v>
       </c>
       <c r="AA2">
-        <v>32.73</v>
+        <v>33.07</v>
       </c>
       <c r="AB2">
-        <v>6.82</v>
+        <v>1.35</v>
       </c>
       <c r="AC2">
-        <v>68.56</v>
+        <v>48.33</v>
       </c>
       <c r="AD2">
-        <v>55.22</v>
+        <v>57.09</v>
       </c>
       <c r="AE2">
-        <v>54.89</v>
+        <v>57.17</v>
       </c>
       <c r="AF2">
-        <v>-17.25</v>
+        <v>-12.41</v>
       </c>
       <c r="AG2">
-        <v>4149.9</v>
+        <v>4141.98</v>
       </c>
       <c r="AH2">
-        <v>3933.92</v>
+        <v>3952.51</v>
       </c>
       <c r="AI2">
         <v>3931.27</v>
@@ -985,7 +985,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>32.53</v>
+        <v>30.02</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -996,10 +996,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>319.5</v>
+        <v>322.2</v>
       </c>
       <c r="D3">
-        <v>1.16</v>
+        <v>0.85</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1008,46 +1008,46 @@
         <v>214.23</v>
       </c>
       <c r="G3">
-        <v>-4.8</v>
+        <v>-3.99</v>
       </c>
       <c r="H3">
-        <v>49.14</v>
+        <v>50.4</v>
       </c>
       <c r="I3">
-        <v>-1.72</v>
+        <v>2.16</v>
       </c>
       <c r="J3">
-        <v>2.32</v>
+        <v>3.6</v>
       </c>
       <c r="K3">
-        <v>13.42</v>
+        <v>14.38</v>
       </c>
       <c r="L3">
-        <v>49.08</v>
+        <v>46.77</v>
       </c>
       <c r="M3">
-        <v>33.56</v>
+        <v>33.41</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P3">
-        <v>316.53</v>
+        <v>317.89</v>
       </c>
       <c r="Q3">
-        <v>314.77</v>
+        <v>315.42</v>
       </c>
       <c r="R3">
-        <v>310.8</v>
+        <v>311.36</v>
       </c>
       <c r="S3">
-        <v>290.91</v>
+        <v>291.02</v>
       </c>
       <c r="T3">
-        <v>9.83</v>
+        <v>10.71</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1062,34 +1062,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>55.38</v>
+        <v>57.42</v>
       </c>
       <c r="Z3">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AA3">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="AB3">
-        <v>-0.05</v>
+        <v>0.21</v>
       </c>
       <c r="AC3">
-        <v>54.4</v>
+        <v>62.88</v>
       </c>
       <c r="AD3">
-        <v>49.03</v>
+        <v>54.59</v>
       </c>
       <c r="AE3">
-        <v>8.859999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AF3">
-        <v>-28.32</v>
+        <v>-30.85</v>
       </c>
       <c r="AG3">
-        <v>324.15</v>
+        <v>324.97</v>
       </c>
       <c r="AH3">
-        <v>305.39</v>
+        <v>305.88</v>
       </c>
       <c r="AI3">
         <v>329.06</v>
@@ -1098,7 +1098,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>20.41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1109,10 +1109,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3568.2</v>
+        <v>3543.2</v>
       </c>
       <c r="D4">
-        <v>-0.46</v>
+        <v>-0.7</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1121,46 +1121,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-23.16</v>
+        <v>-23.7</v>
       </c>
       <c r="H4">
-        <v>17.32</v>
+        <v>16.5</v>
       </c>
       <c r="I4">
-        <v>1.66</v>
+        <v>0.06</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>-1.56</v>
       </c>
       <c r="K4">
-        <v>2.19</v>
+        <v>1.48</v>
       </c>
       <c r="L4">
-        <v>-14.4</v>
+        <v>-16.1</v>
       </c>
       <c r="M4">
-        <v>-0.35</v>
+        <v>-0.49</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P4">
-        <v>3575.48</v>
+        <v>3575.94</v>
       </c>
       <c r="Q4">
-        <v>3562.81</v>
+        <v>3560.72</v>
       </c>
       <c r="R4">
-        <v>3416.08</v>
+        <v>3417.69</v>
       </c>
       <c r="S4">
-        <v>3669.48</v>
+        <v>3666.98</v>
       </c>
       <c r="T4">
-        <v>-2.76</v>
+        <v>-3.38</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1175,34 +1175,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>54.71</v>
+        <v>52.31</v>
       </c>
       <c r="Z4">
-        <v>38.68</v>
+        <v>34.61</v>
       </c>
       <c r="AA4">
-        <v>44.97</v>
+        <v>42.9</v>
       </c>
       <c r="AB4">
-        <v>-6.29</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="AC4">
-        <v>48.72</v>
+        <v>35.66</v>
       </c>
       <c r="AD4">
-        <v>49.42</v>
+        <v>45.65</v>
       </c>
       <c r="AE4">
-        <v>104.76</v>
+        <v>102.91</v>
       </c>
       <c r="AF4">
-        <v>-65.31</v>
+        <v>-65.66</v>
       </c>
       <c r="AG4">
-        <v>3650.92</v>
+        <v>3648.6</v>
       </c>
       <c r="AH4">
-        <v>3474.71</v>
+        <v>3472.85</v>
       </c>
       <c r="AI4">
         <v>3316.13</v>
@@ -1211,7 +1211,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>27.78</v>
+        <v>25.93</v>
       </c>
     </row>
   </sheetData>
@@ -1409,13 +1409,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>8.039999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="D7" s="5">
-        <v>8.220000000000001</v>
+        <v>5.38</v>
       </c>
       <c r="E7" s="6">
-        <v>0.18</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1426,13 +1426,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>4.45</v>
+        <v>2.32</v>
       </c>
       <c r="D8" s="5">
-        <v>2.32</v>
+        <v>3.6</v>
       </c>
       <c r="E8" s="7">
-        <v>-2.13</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1443,13 +1443,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>4.87</v>
+        <v>2</v>
       </c>
       <c r="D9" s="5">
-        <v>2</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-2.87</v>
+        <v>-1.56</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-3.56</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1460,13 +1460,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>0.08</v>
+        <v>1.35</v>
       </c>
       <c r="D10" s="5">
-        <v>1.35</v>
+        <v>-0.08</v>
       </c>
       <c r="E10" s="6">
-        <v>1.27</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1477,13 +1477,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>0.27</v>
+        <v>-1.72</v>
       </c>
       <c r="D11" s="5">
-        <v>-1.72</v>
+        <v>2.16</v>
       </c>
       <c r="E11" s="7">
-        <v>-1.99</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1494,13 +1494,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>3.1</v>
+        <v>1.66</v>
       </c>
       <c r="D12" s="5">
-        <v>1.66</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-1.44</v>
+        <v>0.06</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1511,13 +1511,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>14.31</v>
+        <v>15.78</v>
       </c>
       <c r="D13" s="5">
-        <v>15.78</v>
+        <v>12.87</v>
       </c>
       <c r="E13" s="6">
-        <v>1.47</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1528,13 +1528,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>47.03</v>
+        <v>49.08</v>
       </c>
       <c r="D14" s="5">
-        <v>49.08</v>
+        <v>46.77</v>
       </c>
       <c r="E14" s="6">
-        <v>2.05</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1545,13 +1545,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-12.76</v>
+        <v>-14.4</v>
       </c>
       <c r="D15" s="5">
-        <v>-14.4</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-1.64</v>
+        <v>-16.1</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-1.7</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1562,13 +1562,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>1.29</v>
+        <v>1.77</v>
       </c>
       <c r="D16" s="5">
-        <v>1.77</v>
+        <v>-0.23</v>
       </c>
       <c r="E16" s="6">
-        <v>0.48</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1579,13 +1579,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>11.73</v>
+        <v>13.42</v>
       </c>
       <c r="D17" s="5">
-        <v>13.42</v>
-      </c>
-      <c r="E17" s="6">
-        <v>1.69</v>
+        <v>14.38</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.96</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1596,13 +1596,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>1.24</v>
+        <v>2.19</v>
       </c>
       <c r="D18" s="5">
-        <v>2.19</v>
+        <v>1.48</v>
       </c>
       <c r="E18" s="6">
-        <v>0.95</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1613,13 +1613,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-6.52</v>
+        <v>-5.86</v>
       </c>
       <c r="D19" s="5">
-        <v>-5.86</v>
+        <v>-7.71</v>
       </c>
       <c r="E19" s="6">
-        <v>0.66</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1630,13 +1630,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-5.88</v>
+        <v>-4.8</v>
       </c>
       <c r="D20" s="5">
-        <v>-4.8</v>
-      </c>
-      <c r="E20" s="6">
-        <v>1.08</v>
+        <v>-3.99</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1647,13 +1647,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-22.81</v>
+        <v>-23.16</v>
       </c>
       <c r="D21" s="5">
-        <v>-23.16</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.35</v>
+        <v>-23.7</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1664,13 +1664,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>4090</v>
+        <v>4119</v>
       </c>
       <c r="D22" s="5">
-        <v>4119</v>
+        <v>4038.1</v>
       </c>
       <c r="E22" s="6">
-        <v>29</v>
+        <v>-80.90000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1681,13 +1681,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>315.85</v>
+        <v>319.5</v>
       </c>
       <c r="D23" s="5">
-        <v>319.5</v>
-      </c>
-      <c r="E23" s="6">
-        <v>3.65</v>
+        <v>322.2</v>
+      </c>
+      <c r="E23" s="7">
+        <v>2.7</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1698,13 +1698,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>3584.6</v>
+        <v>3568.2</v>
       </c>
       <c r="D24" s="5">
-        <v>3568.2</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-16.4</v>
+        <v>3543.2</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-25</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1715,13 +1715,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>59.92</v>
+        <v>62.85</v>
       </c>
       <c r="D25" s="5">
-        <v>62.85</v>
+        <v>51.52</v>
       </c>
       <c r="E25" s="6">
-        <v>2.93</v>
+        <v>-11.33</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>52.53</v>
+        <v>55.38</v>
       </c>
       <c r="D26" s="5">
-        <v>55.38</v>
-      </c>
-      <c r="E26" s="6">
-        <v>2.85</v>
+        <v>57.42</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2.04</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1749,13 +1749,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>56.28</v>
+        <v>54.71</v>
       </c>
       <c r="D27" s="5">
-        <v>54.71</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-1.57</v>
+        <v>52.31</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-2.4</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1766,13 +1766,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>-15.3</v>
+        <v>-17.25</v>
       </c>
       <c r="D28" s="5">
-        <v>-17.25</v>
+        <v>-12.41</v>
       </c>
       <c r="E28" s="7">
-        <v>-1.95</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1783,13 +1783,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-36.25</v>
+        <v>-28.32</v>
       </c>
       <c r="D29" s="5">
-        <v>-28.32</v>
+        <v>-30.85</v>
       </c>
       <c r="E29" s="6">
-        <v>7.93</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1800,13 +1800,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-34.99</v>
+        <v>-65.31</v>
       </c>
       <c r="D30" s="5">
-        <v>-65.31</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-30.32</v>
+        <v>-65.66</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-0.35</v>
       </c>
     </row>
   </sheetData>
@@ -1871,16 +1871,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>57.6</v>
+        <v>53.8</v>
       </c>
       <c r="E2" s="10">
         <v>70</v>
       </c>
       <c r="F2" s="10">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="G2" s="10">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -1999,13 +1999,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.3356</v>
+        <v>0.3341</v>
       </c>
       <c r="B2" s="13">
-        <v>0.2215</v>
+        <v>0.2164</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0035</v>
+        <v>-0.0049</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -883,10 +883,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>4038.1</v>
+        <v>4027</v>
       </c>
       <c r="D2">
-        <v>-1.96</v>
+        <v>-0.27</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -895,25 +895,25 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-7.71</v>
+        <v>-7.96</v>
       </c>
       <c r="H2">
-        <v>21.99</v>
+        <v>21.66</v>
       </c>
       <c r="I2">
-        <v>-0.08</v>
+        <v>-1.32</v>
       </c>
       <c r="J2">
-        <v>5.38</v>
+        <v>2.43</v>
       </c>
       <c r="K2">
-        <v>-0.23</v>
+        <v>-1.21</v>
       </c>
       <c r="L2">
-        <v>12.87</v>
+        <v>13.09</v>
       </c>
       <c r="M2">
-        <v>21.64</v>
+        <v>20.94</v>
       </c>
       <c r="N2">
         <v>66</v>
@@ -922,19 +922,19 @@
         <v>62</v>
       </c>
       <c r="P2">
-        <v>4084.22</v>
+        <v>4073.42</v>
       </c>
       <c r="Q2">
-        <v>4047.24</v>
+        <v>4051.71</v>
       </c>
       <c r="R2">
-        <v>4007.52</v>
+        <v>4003.91</v>
       </c>
       <c r="S2">
-        <v>3957.17</v>
+        <v>3957.9</v>
       </c>
       <c r="T2">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -949,34 +949,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>51.52</v>
+        <v>50.18</v>
       </c>
       <c r="Z2">
-        <v>34.42</v>
+        <v>29.11</v>
       </c>
       <c r="AA2">
-        <v>33.07</v>
+        <v>32.28</v>
       </c>
       <c r="AB2">
-        <v>1.35</v>
+        <v>-3.16</v>
       </c>
       <c r="AC2">
-        <v>48.33</v>
+        <v>29.89</v>
       </c>
       <c r="AD2">
-        <v>57.09</v>
+        <v>48.93</v>
       </c>
       <c r="AE2">
-        <v>57.17</v>
+        <v>56.25</v>
       </c>
       <c r="AF2">
-        <v>-12.41</v>
+        <v>-25.84</v>
       </c>
       <c r="AG2">
-        <v>4141.98</v>
+        <v>4132.02</v>
       </c>
       <c r="AH2">
-        <v>3952.51</v>
+        <v>3971.4</v>
       </c>
       <c r="AI2">
         <v>3931.27</v>
@@ -985,7 +985,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>30.02</v>
+        <v>26.16</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -996,10 +996,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>322.2</v>
+        <v>321.9</v>
       </c>
       <c r="D3">
-        <v>0.85</v>
+        <v>-0.09</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1008,46 +1008,46 @@
         <v>214.23</v>
       </c>
       <c r="G3">
-        <v>-3.99</v>
+        <v>-4.08</v>
       </c>
       <c r="H3">
-        <v>50.4</v>
+        <v>50.26</v>
       </c>
       <c r="I3">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="J3">
-        <v>3.6</v>
+        <v>4.12</v>
       </c>
       <c r="K3">
-        <v>14.38</v>
+        <v>12.32</v>
       </c>
       <c r="L3">
-        <v>46.77</v>
+        <v>46.03</v>
       </c>
       <c r="M3">
-        <v>33.41</v>
+        <v>33.3</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="P3">
-        <v>317.89</v>
+        <v>319.32</v>
       </c>
       <c r="Q3">
-        <v>315.42</v>
+        <v>316.21</v>
       </c>
       <c r="R3">
-        <v>311.36</v>
+        <v>311.92</v>
       </c>
       <c r="S3">
-        <v>291.02</v>
+        <v>291.14</v>
       </c>
       <c r="T3">
-        <v>10.71</v>
+        <v>10.56</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1062,34 +1062,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>57.42</v>
+        <v>57.11</v>
       </c>
       <c r="Z3">
-        <v>2.7</v>
+        <v>2.89</v>
       </c>
       <c r="AA3">
-        <v>2.49</v>
+        <v>2.57</v>
       </c>
       <c r="AB3">
-        <v>0.21</v>
+        <v>0.32</v>
       </c>
       <c r="AC3">
-        <v>62.88</v>
+        <v>73.22</v>
       </c>
       <c r="AD3">
-        <v>54.59</v>
+        <v>63.5</v>
       </c>
       <c r="AE3">
-        <v>8.779999999999999</v>
+        <v>8.52</v>
       </c>
       <c r="AF3">
-        <v>-30.85</v>
+        <v>-36.73</v>
       </c>
       <c r="AG3">
-        <v>324.97</v>
+        <v>325.13</v>
       </c>
       <c r="AH3">
-        <v>305.88</v>
+        <v>307.28</v>
       </c>
       <c r="AI3">
         <v>329.06</v>
@@ -1098,7 +1098,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>24</v>
+        <v>25.35</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1109,10 +1109,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3543.2</v>
+        <v>3537.9</v>
       </c>
       <c r="D4">
-        <v>-0.7</v>
+        <v>-0.15</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1121,46 +1121,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-23.7</v>
+        <v>-23.82</v>
       </c>
       <c r="H4">
-        <v>16.5</v>
+        <v>16.33</v>
       </c>
       <c r="I4">
-        <v>0.06</v>
+        <v>-1.15</v>
       </c>
       <c r="J4">
-        <v>-1.56</v>
+        <v>-1.31</v>
       </c>
       <c r="K4">
-        <v>1.48</v>
+        <v>3.07</v>
       </c>
       <c r="L4">
-        <v>-16.1</v>
+        <v>-15.93</v>
       </c>
       <c r="M4">
-        <v>-0.49</v>
+        <v>-1.13</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P4">
-        <v>3575.94</v>
+        <v>3567.7</v>
       </c>
       <c r="Q4">
-        <v>3560.72</v>
+        <v>3559.66</v>
       </c>
       <c r="R4">
-        <v>3417.69</v>
+        <v>3419.37</v>
       </c>
       <c r="S4">
-        <v>3666.98</v>
+        <v>3664.46</v>
       </c>
       <c r="T4">
-        <v>-3.38</v>
+        <v>-3.45</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1175,34 +1175,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>52.31</v>
+        <v>51.79</v>
       </c>
       <c r="Z4">
-        <v>34.61</v>
+        <v>30.6</v>
       </c>
       <c r="AA4">
-        <v>42.9</v>
+        <v>40.44</v>
       </c>
       <c r="AB4">
-        <v>-8.289999999999999</v>
+        <v>-9.84</v>
       </c>
       <c r="AC4">
-        <v>35.66</v>
+        <v>25.67</v>
       </c>
       <c r="AD4">
-        <v>45.65</v>
+        <v>36.68</v>
       </c>
       <c r="AE4">
-        <v>102.91</v>
+        <v>98.31999999999999</v>
       </c>
       <c r="AF4">
-        <v>-65.66</v>
+        <v>-60.58</v>
       </c>
       <c r="AG4">
-        <v>3648.6</v>
+        <v>3648.13</v>
       </c>
       <c r="AH4">
-        <v>3472.85</v>
+        <v>3471.2</v>
       </c>
       <c r="AI4">
         <v>3316.13</v>
@@ -1211,7 +1211,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>25.93</v>
+        <v>23.97</v>
       </c>
     </row>
   </sheetData>
@@ -1409,13 +1409,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>8.220000000000001</v>
+        <v>5.38</v>
       </c>
       <c r="D7" s="5">
-        <v>5.38</v>
+        <v>2.43</v>
       </c>
       <c r="E7" s="6">
-        <v>-2.84</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1426,13 +1426,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>2.32</v>
+        <v>3.6</v>
       </c>
       <c r="D8" s="5">
-        <v>3.6</v>
+        <v>4.12</v>
       </c>
       <c r="E8" s="7">
-        <v>1.28</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1443,13 +1443,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>2</v>
+        <v>-1.56</v>
       </c>
       <c r="D9" s="5">
-        <v>-1.56</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-3.56</v>
+        <v>-1.31</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.25</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1460,13 +1460,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>1.35</v>
+        <v>-0.08</v>
       </c>
       <c r="D10" s="5">
-        <v>-0.08</v>
+        <v>-1.32</v>
       </c>
       <c r="E10" s="6">
-        <v>-1.43</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1477,13 +1477,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-1.72</v>
+        <v>2.16</v>
       </c>
       <c r="D11" s="5">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="E11" s="7">
-        <v>3.88</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1494,13 +1494,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>1.66</v>
+        <v>0.06</v>
       </c>
       <c r="D12" s="5">
-        <v>0.06</v>
+        <v>-1.15</v>
       </c>
       <c r="E12" s="6">
-        <v>-1.6</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1511,13 +1511,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>15.78</v>
+        <v>12.87</v>
       </c>
       <c r="D13" s="5">
-        <v>12.87</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-2.91</v>
+        <v>13.09</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.22</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1528,13 +1528,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>49.08</v>
+        <v>46.77</v>
       </c>
       <c r="D14" s="5">
-        <v>46.77</v>
+        <v>46.03</v>
       </c>
       <c r="E14" s="6">
-        <v>-2.31</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1545,13 +1545,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-14.4</v>
+        <v>-16.1</v>
       </c>
       <c r="D15" s="5">
-        <v>-16.1</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-1.7</v>
+        <v>-15.93</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.17</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1562,13 +1562,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>1.77</v>
+        <v>-0.23</v>
       </c>
       <c r="D16" s="5">
-        <v>-0.23</v>
+        <v>-1.21</v>
       </c>
       <c r="E16" s="6">
-        <v>-2</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1579,13 +1579,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>13.42</v>
+        <v>14.38</v>
       </c>
       <c r="D17" s="5">
-        <v>14.38</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.96</v>
+        <v>12.32</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-2.06</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1596,13 +1596,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>2.19</v>
+        <v>1.48</v>
       </c>
       <c r="D18" s="5">
-        <v>1.48</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-0.71</v>
+        <v>3.07</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.59</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1613,13 +1613,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-5.86</v>
+        <v>-7.71</v>
       </c>
       <c r="D19" s="5">
-        <v>-7.71</v>
+        <v>-7.96</v>
       </c>
       <c r="E19" s="6">
-        <v>-1.85</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1630,13 +1630,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-4.8</v>
+        <v>-3.99</v>
       </c>
       <c r="D20" s="5">
-        <v>-3.99</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.8100000000000001</v>
+        <v>-4.08</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1647,13 +1647,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-23.16</v>
+        <v>-23.7</v>
       </c>
       <c r="D21" s="5">
-        <v>-23.7</v>
+        <v>-23.82</v>
       </c>
       <c r="E21" s="6">
-        <v>-0.54</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1664,13 +1664,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>4119</v>
+        <v>4038.1</v>
       </c>
       <c r="D22" s="5">
-        <v>4038.1</v>
+        <v>4027</v>
       </c>
       <c r="E22" s="6">
-        <v>-80.90000000000001</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1681,13 +1681,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>319.5</v>
+        <v>322.2</v>
       </c>
       <c r="D23" s="5">
-        <v>322.2</v>
-      </c>
-      <c r="E23" s="7">
-        <v>2.7</v>
+        <v>321.9</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1698,13 +1698,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>3568.2</v>
+        <v>3543.2</v>
       </c>
       <c r="D24" s="5">
-        <v>3543.2</v>
+        <v>3537.9</v>
       </c>
       <c r="E24" s="6">
-        <v>-25</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1715,13 +1715,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>62.85</v>
+        <v>51.52</v>
       </c>
       <c r="D25" s="5">
-        <v>51.52</v>
+        <v>50.18</v>
       </c>
       <c r="E25" s="6">
-        <v>-11.33</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1732,13 +1732,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>55.38</v>
+        <v>57.42</v>
       </c>
       <c r="D26" s="5">
-        <v>57.42</v>
-      </c>
-      <c r="E26" s="7">
-        <v>2.04</v>
+        <v>57.11</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1749,13 +1749,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>54.71</v>
+        <v>52.31</v>
       </c>
       <c r="D27" s="5">
-        <v>52.31</v>
+        <v>51.79</v>
       </c>
       <c r="E27" s="6">
-        <v>-2.4</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1766,13 +1766,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>-17.25</v>
+        <v>-12.41</v>
       </c>
       <c r="D28" s="5">
-        <v>-12.41</v>
-      </c>
-      <c r="E28" s="7">
-        <v>4.84</v>
+        <v>-25.84</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-13.43</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1783,13 +1783,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-28.32</v>
+        <v>-30.85</v>
       </c>
       <c r="D29" s="5">
-        <v>-30.85</v>
+        <v>-36.73</v>
       </c>
       <c r="E29" s="6">
-        <v>-2.53</v>
+        <v>-5.88</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1800,13 +1800,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-65.31</v>
+        <v>-65.66</v>
       </c>
       <c r="D30" s="5">
-        <v>-65.66</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-0.35</v>
+        <v>-60.58</v>
+      </c>
+      <c r="E30" s="7">
+        <v>5.08</v>
       </c>
     </row>
   </sheetData>
@@ -1871,16 +1871,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>53.8</v>
+        <v>53</v>
       </c>
       <c r="E2" s="10">
         <v>70</v>
       </c>
       <c r="F2" s="10">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="G2" s="10">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -1999,13 +1999,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.3341</v>
+        <v>0.333</v>
       </c>
       <c r="B2" s="13">
-        <v>0.2164</v>
+        <v>0.2094</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0049</v>
+        <v>-0.0113</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,7 +160,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>57.1 → 49.7</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>57.1</t>
+  </si>
+  <si>
+    <t>49.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -362,17 +389,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -883,10 +911,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>4027</v>
+        <v>4045.8</v>
       </c>
       <c r="D2">
-        <v>-0.27</v>
+        <v>0.47</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -895,46 +923,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-7.96</v>
+        <v>-7.53</v>
       </c>
       <c r="H2">
-        <v>21.66</v>
+        <v>22.23</v>
       </c>
       <c r="I2">
-        <v>-1.32</v>
+        <v>-1.15</v>
       </c>
       <c r="J2">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="K2">
-        <v>-1.21</v>
+        <v>0.87</v>
       </c>
       <c r="L2">
-        <v>13.09</v>
+        <v>13.38</v>
       </c>
       <c r="M2">
-        <v>20.94</v>
+        <v>20.75</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P2">
-        <v>4073.42</v>
+        <v>4063.98</v>
       </c>
       <c r="Q2">
-        <v>4051.71</v>
+        <v>4057.06</v>
       </c>
       <c r="R2">
-        <v>4003.91</v>
+        <v>4001.03</v>
       </c>
       <c r="S2">
-        <v>3957.9</v>
+        <v>3958.55</v>
       </c>
       <c r="T2">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -949,34 +977,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>50.18</v>
+        <v>52.43</v>
       </c>
       <c r="Z2">
-        <v>29.11</v>
+        <v>26.13</v>
       </c>
       <c r="AA2">
-        <v>32.28</v>
+        <v>31.05</v>
       </c>
       <c r="AB2">
-        <v>-3.16</v>
+        <v>-4.92</v>
       </c>
       <c r="AC2">
-        <v>29.89</v>
+        <v>5.92</v>
       </c>
       <c r="AD2">
-        <v>48.93</v>
+        <v>28.05</v>
       </c>
       <c r="AE2">
-        <v>56.25</v>
+        <v>55</v>
       </c>
       <c r="AF2">
-        <v>-25.84</v>
+        <v>-39.3</v>
       </c>
       <c r="AG2">
-        <v>4132.02</v>
+        <v>4117.54</v>
       </c>
       <c r="AH2">
-        <v>3971.4</v>
+        <v>3996.57</v>
       </c>
       <c r="AI2">
         <v>3931.27</v>
@@ -985,7 +1013,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>26.16</v>
+        <v>22.72</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -996,10 +1024,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>321.9</v>
+        <v>314.3</v>
       </c>
       <c r="D3">
-        <v>-0.09</v>
+        <v>-2.36</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1008,46 +1036,46 @@
         <v>214.23</v>
       </c>
       <c r="G3">
-        <v>-4.08</v>
+        <v>-6.35</v>
       </c>
       <c r="H3">
-        <v>50.26</v>
+        <v>46.71</v>
       </c>
       <c r="I3">
-        <v>2.27</v>
+        <v>-0.9</v>
       </c>
       <c r="J3">
-        <v>4.12</v>
+        <v>2.63</v>
       </c>
       <c r="K3">
-        <v>12.32</v>
+        <v>15.87</v>
       </c>
       <c r="L3">
-        <v>46.03</v>
+        <v>45.87</v>
       </c>
       <c r="M3">
-        <v>33.3</v>
+        <v>31.92</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P3">
-        <v>319.32</v>
+        <v>318.75</v>
       </c>
       <c r="Q3">
-        <v>316.21</v>
+        <v>316.36</v>
       </c>
       <c r="R3">
-        <v>311.92</v>
+        <v>312.47</v>
       </c>
       <c r="S3">
-        <v>291.14</v>
+        <v>291.25</v>
       </c>
       <c r="T3">
-        <v>10.56</v>
+        <v>7.91</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1062,34 +1090,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>57.11</v>
+        <v>49.73</v>
       </c>
       <c r="Z3">
-        <v>2.89</v>
+        <v>2.4</v>
       </c>
       <c r="AA3">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="AB3">
-        <v>0.32</v>
+        <v>-0.13</v>
       </c>
       <c r="AC3">
-        <v>73.22</v>
+        <v>60.47</v>
       </c>
       <c r="AD3">
-        <v>63.5</v>
+        <v>65.52</v>
       </c>
       <c r="AE3">
-        <v>8.52</v>
+        <v>8.49</v>
       </c>
       <c r="AF3">
-        <v>-36.73</v>
+        <v>-37.84</v>
       </c>
       <c r="AG3">
-        <v>325.13</v>
+        <v>325.03</v>
       </c>
       <c r="AH3">
-        <v>307.28</v>
+        <v>307.69</v>
       </c>
       <c r="AI3">
         <v>329.06</v>
@@ -1098,7 +1126,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>25.35</v>
+        <v>23.38</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1109,10 +1137,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3537.9</v>
+        <v>3568.7</v>
       </c>
       <c r="D4">
-        <v>-0.15</v>
+        <v>0.87</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1121,46 +1149,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-23.82</v>
+        <v>-23.15</v>
       </c>
       <c r="H4">
-        <v>16.33</v>
+        <v>17.34</v>
       </c>
       <c r="I4">
-        <v>-1.15</v>
+        <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1.31</v>
+        <v>0.27</v>
       </c>
       <c r="K4">
-        <v>3.07</v>
+        <v>5.41</v>
       </c>
       <c r="L4">
-        <v>-15.93</v>
+        <v>-17.18</v>
       </c>
       <c r="M4">
-        <v>-1.13</v>
+        <v>-0.63</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P4">
-        <v>3567.7</v>
+        <v>3560.52</v>
       </c>
       <c r="Q4">
-        <v>3559.66</v>
+        <v>3560.33</v>
       </c>
       <c r="R4">
-        <v>3419.37</v>
+        <v>3422.59</v>
       </c>
       <c r="S4">
-        <v>3664.46</v>
+        <v>3662.02</v>
       </c>
       <c r="T4">
-        <v>-3.45</v>
+        <v>-2.55</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1175,34 +1203,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>51.79</v>
+        <v>54.6</v>
       </c>
       <c r="Z4">
-        <v>30.6</v>
+        <v>29.57</v>
       </c>
       <c r="AA4">
-        <v>40.44</v>
+        <v>38.26</v>
       </c>
       <c r="AB4">
-        <v>-9.84</v>
+        <v>-8.69</v>
       </c>
       <c r="AC4">
-        <v>25.67</v>
+        <v>25.44</v>
       </c>
       <c r="AD4">
-        <v>36.68</v>
+        <v>28.92</v>
       </c>
       <c r="AE4">
-        <v>98.31999999999999</v>
+        <v>95.95</v>
       </c>
       <c r="AF4">
-        <v>-60.58</v>
+        <v>-46.29</v>
       </c>
       <c r="AG4">
-        <v>3648.13</v>
+        <v>3648.86</v>
       </c>
       <c r="AH4">
-        <v>3471.2</v>
+        <v>3471.8</v>
       </c>
       <c r="AI4">
         <v>3316.13</v>
@@ -1211,7 +1239,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>23.97</v>
+        <v>24.45</v>
       </c>
     </row>
   </sheetData>
@@ -1372,12 +1400,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>46</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1385,428 +1448,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>51</v>
+      <c r="B6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>5.38</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>2.43</v>
       </c>
-      <c r="E7" s="6">
-        <v>-2.95</v>
+      <c r="D7" s="6">
+        <v>2.75</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.32</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>3.6</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>4.12</v>
       </c>
-      <c r="E8" s="7">
-        <v>0.52</v>
+      <c r="D8" s="6">
+        <v>2.63</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-1.56</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-1.31</v>
       </c>
+      <c r="D9" s="6">
+        <v>0.27</v>
+      </c>
       <c r="E9" s="7">
-        <v>0.25</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
-        <v>-0.08</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-1.32</v>
       </c>
-      <c r="E10" s="6">
-        <v>-1.24</v>
+      <c r="D10" s="6">
+        <v>-1.15</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.17</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>2.16</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>2.27</v>
       </c>
-      <c r="E11" s="7">
-        <v>0.11</v>
+      <c r="D11" s="6">
+        <v>-0.9</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-3.17</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>0.06</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-1.15</v>
       </c>
-      <c r="E12" s="6">
+      <c r="D12" s="6">
+        <v>-1</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="6">
+        <v>13.09</v>
+      </c>
+      <c r="D13" s="6">
+        <v>13.38</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="6">
+        <v>46.03</v>
+      </c>
+      <c r="D14" s="6">
+        <v>45.87</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-15.93</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-17.18</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="6">
         <v>-1.21</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D16" s="6">
+        <v>0.87</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="6">
+        <v>12.32</v>
+      </c>
+      <c r="D17" s="6">
+        <v>15.87</v>
+      </c>
+      <c r="E17" s="7">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="6">
+        <v>3.07</v>
+      </c>
+      <c r="D18" s="6">
+        <v>5.41</v>
+      </c>
+      <c r="E18" s="7">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="5">
-        <v>12.87</v>
-      </c>
-      <c r="D13" s="5">
-        <v>13.09</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B19" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-7.96</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-7.53</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="5">
-        <v>46.77</v>
-      </c>
-      <c r="D14" s="5">
-        <v>46.03</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-0.74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-4.08</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-6.35</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-2.27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-16.1</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-15.93</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-23.82</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-23.15</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-0.23</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-1.21</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B22" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="6">
+        <v>4027</v>
+      </c>
+      <c r="D22" s="6">
+        <v>4045.8</v>
+      </c>
+      <c r="E22" s="7">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="5">
-        <v>14.38</v>
-      </c>
-      <c r="D17" s="5">
-        <v>12.32</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-2.06</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B23" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="6">
+        <v>321.9</v>
+      </c>
+      <c r="D23" s="6">
+        <v>314.3</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-7.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="5">
-        <v>1.48</v>
-      </c>
-      <c r="D18" s="5">
-        <v>3.07</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="6">
+        <v>3537.9</v>
+      </c>
+      <c r="D24" s="6">
+        <v>3568.7</v>
+      </c>
+      <c r="E24" s="7">
+        <v>30.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-7.71</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-7.96</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="6">
+        <v>50.18</v>
+      </c>
+      <c r="D25" s="6">
+        <v>52.43</v>
+      </c>
+      <c r="E25" s="7">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-3.99</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-4.08</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="6">
+        <v>57.11</v>
+      </c>
+      <c r="D26" s="6">
+        <v>49.73</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-7.38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-23.7</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-23.82</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="6">
+        <v>51.79</v>
+      </c>
+      <c r="D27" s="6">
+        <v>54.6</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2.81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="5">
-        <v>4038.1</v>
-      </c>
-      <c r="D22" s="5">
-        <v>4027</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-11.1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B28" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-25.84</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-39.3</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-13.46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="5">
-        <v>322.2</v>
-      </c>
-      <c r="D23" s="5">
-        <v>321.9</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-36.73</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-37.84</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="5">
-        <v>3543.2</v>
-      </c>
-      <c r="D24" s="5">
-        <v>3537.9</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-5.3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="5">
-        <v>51.52</v>
-      </c>
-      <c r="D25" s="5">
-        <v>50.18</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-1.34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="5">
-        <v>57.42</v>
-      </c>
-      <c r="D26" s="5">
-        <v>57.11</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="5">
-        <v>52.31</v>
-      </c>
-      <c r="D27" s="5">
-        <v>51.79</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="5">
-        <v>-12.41</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-25.84</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-13.43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-30.85</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-36.73</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-5.88</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-65.66</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C30" s="6">
         <v>-60.58</v>
       </c>
+      <c r="D30" s="6">
+        <v>-46.29</v>
+      </c>
       <c r="E30" s="7">
-        <v>5.08</v>
+        <v>14.29</v>
       </c>
     </row>
   </sheetData>
@@ -1832,60 +1895,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>59</v>
+      <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>64.52</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>3</v>
       </c>
-      <c r="D2" s="10">
-        <v>53</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>52.3</v>
+      </c>
+      <c r="E2" s="11">
         <v>70</v>
       </c>
-      <c r="F2" s="10">
-        <v>1.7</v>
-      </c>
-      <c r="G2" s="10">
-        <v>4.7</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>1.9</v>
+      </c>
+      <c r="G2" s="11">
+        <v>7.4</v>
+      </c>
+      <c r="H2" s="11">
         <v>66.3</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>70</v>
       </c>
     </row>
@@ -1987,25 +2050,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13">
-        <v>0.333</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.2094</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0113</v>
+      <c r="A2" s="14">
+        <v>0.3192</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2075</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0063</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -178,16 +178,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>57.1 → 49.7</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>57.1</t>
+    <t>49.7 → 55.2</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>49.7</t>
+  </si>
+  <si>
+    <t>55.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +273,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +313,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -911,10 +911,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>4045.8</v>
+        <v>4044.9</v>
       </c>
       <c r="D2">
-        <v>0.47</v>
+        <v>-0.02</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -923,25 +923,25 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-7.53</v>
+        <v>-7.55</v>
       </c>
       <c r="H2">
-        <v>22.23</v>
+        <v>22.2</v>
       </c>
       <c r="I2">
-        <v>-1.15</v>
+        <v>-1.1</v>
       </c>
       <c r="J2">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="K2">
-        <v>0.87</v>
+        <v>1.1</v>
       </c>
       <c r="L2">
-        <v>13.38</v>
+        <v>15.34</v>
       </c>
       <c r="M2">
-        <v>20.75</v>
+        <v>20.55</v>
       </c>
       <c r="N2">
         <v>66</v>
@@ -950,19 +950,19 @@
         <v>63</v>
       </c>
       <c r="P2">
-        <v>4063.98</v>
+        <v>4054.96</v>
       </c>
       <c r="Q2">
-        <v>4057.06</v>
+        <v>4058.05</v>
       </c>
       <c r="R2">
-        <v>4001.03</v>
+        <v>3997.74</v>
       </c>
       <c r="S2">
-        <v>3958.55</v>
+        <v>3959.19</v>
       </c>
       <c r="T2">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -977,34 +977,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>52.43</v>
+        <v>52.31</v>
       </c>
       <c r="Z2">
-        <v>26.13</v>
+        <v>23.42</v>
       </c>
       <c r="AA2">
-        <v>31.05</v>
+        <v>29.52</v>
       </c>
       <c r="AB2">
-        <v>-4.92</v>
+        <v>-6.1</v>
       </c>
       <c r="AC2">
-        <v>5.92</v>
+        <v>11.53</v>
       </c>
       <c r="AD2">
-        <v>28.05</v>
+        <v>15.78</v>
       </c>
       <c r="AE2">
-        <v>55</v>
+        <v>56.06</v>
       </c>
       <c r="AF2">
-        <v>-39.3</v>
+        <v>9.92</v>
       </c>
       <c r="AG2">
-        <v>4117.54</v>
+        <v>4116.95</v>
       </c>
       <c r="AH2">
-        <v>3996.57</v>
+        <v>3999.15</v>
       </c>
       <c r="AI2">
         <v>3931.27</v>
@@ -1013,7 +1013,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>22.72</v>
+        <v>23.79</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1024,10 +1024,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>314.3</v>
+        <v>321</v>
       </c>
       <c r="D3">
-        <v>-2.36</v>
+        <v>2.13</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1036,46 +1036,46 @@
         <v>214.23</v>
       </c>
       <c r="G3">
-        <v>-6.35</v>
+        <v>-4.35</v>
       </c>
       <c r="H3">
-        <v>46.71</v>
+        <v>49.84</v>
       </c>
       <c r="I3">
-        <v>-0.9</v>
+        <v>1.63</v>
       </c>
       <c r="J3">
-        <v>2.63</v>
+        <v>3.13</v>
       </c>
       <c r="K3">
-        <v>15.87</v>
+        <v>18.58</v>
       </c>
       <c r="L3">
-        <v>45.87</v>
+        <v>47.41</v>
       </c>
       <c r="M3">
-        <v>31.92</v>
+        <v>32.63</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P3">
-        <v>318.75</v>
+        <v>319.78</v>
       </c>
       <c r="Q3">
-        <v>316.36</v>
+        <v>316.51</v>
       </c>
       <c r="R3">
-        <v>312.47</v>
+        <v>313.16</v>
       </c>
       <c r="S3">
-        <v>291.25</v>
+        <v>291.4</v>
       </c>
       <c r="T3">
-        <v>7.91</v>
+        <v>10.16</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1090,34 +1090,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>49.73</v>
+        <v>55.22</v>
       </c>
       <c r="Z3">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="AA3">
         <v>2.54</v>
       </c>
       <c r="AB3">
-        <v>-0.13</v>
+        <v>-0.01</v>
       </c>
       <c r="AC3">
-        <v>60.47</v>
+        <v>55.5</v>
       </c>
       <c r="AD3">
-        <v>65.52</v>
+        <v>63.06</v>
       </c>
       <c r="AE3">
-        <v>8.49</v>
+        <v>8.91</v>
       </c>
       <c r="AF3">
-        <v>-37.84</v>
+        <v>-3.38</v>
       </c>
       <c r="AG3">
-        <v>325.03</v>
+        <v>325.4</v>
       </c>
       <c r="AH3">
-        <v>307.69</v>
+        <v>307.62</v>
       </c>
       <c r="AI3">
         <v>329.06</v>
@@ -1126,7 +1126,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>23.38</v>
+        <v>22.78</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1137,10 +1137,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3568.7</v>
+        <v>3608.4</v>
       </c>
       <c r="D4">
-        <v>0.87</v>
+        <v>1.11</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1149,46 +1149,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-23.15</v>
+        <v>-22.3</v>
       </c>
       <c r="H4">
-        <v>17.34</v>
+        <v>18.65</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>0.66</v>
       </c>
       <c r="J4">
-        <v>0.27</v>
+        <v>1.49</v>
       </c>
       <c r="K4">
-        <v>5.41</v>
+        <v>2.85</v>
       </c>
       <c r="L4">
-        <v>-17.18</v>
+        <v>-15.26</v>
       </c>
       <c r="M4">
-        <v>-0.63</v>
+        <v>-0.46</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="P4">
-        <v>3560.52</v>
+        <v>3565.28</v>
       </c>
       <c r="Q4">
-        <v>3560.33</v>
+        <v>3562.51</v>
       </c>
       <c r="R4">
-        <v>3422.59</v>
+        <v>3428.13</v>
       </c>
       <c r="S4">
-        <v>3662.02</v>
+        <v>3659.39</v>
       </c>
       <c r="T4">
-        <v>-2.55</v>
+        <v>-1.39</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1203,34 +1203,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>54.6</v>
+        <v>58.01</v>
       </c>
       <c r="Z4">
-        <v>29.57</v>
+        <v>31.59</v>
       </c>
       <c r="AA4">
-        <v>38.26</v>
+        <v>36.93</v>
       </c>
       <c r="AB4">
-        <v>-8.69</v>
+        <v>-5.34</v>
       </c>
       <c r="AC4">
-        <v>25.44</v>
+        <v>48.31</v>
       </c>
       <c r="AD4">
-        <v>28.92</v>
+        <v>33.14</v>
       </c>
       <c r="AE4">
-        <v>95.95</v>
+        <v>102.28</v>
       </c>
       <c r="AF4">
-        <v>-46.29</v>
+        <v>678.38</v>
       </c>
       <c r="AG4">
-        <v>3648.86</v>
+        <v>3653.61</v>
       </c>
       <c r="AH4">
-        <v>3471.8</v>
+        <v>3471.41</v>
       </c>
       <c r="AI4">
         <v>3316.13</v>
@@ -1239,7 +1239,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>24.45</v>
+        <v>27.59</v>
       </c>
     </row>
   </sheetData>
@@ -1472,13 +1472,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="D7" s="6">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="E7" s="7">
-        <v>0.32</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1489,13 +1489,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>4.12</v>
+        <v>2.63</v>
       </c>
       <c r="D8" s="6">
-        <v>2.63</v>
+        <v>3.13</v>
       </c>
       <c r="E8" s="8">
-        <v>-1.49</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1506,13 +1506,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-1.31</v>
+        <v>0.27</v>
       </c>
       <c r="D9" s="6">
-        <v>0.27</v>
-      </c>
-      <c r="E9" s="7">
-        <v>1.58</v>
+        <v>1.49</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1.22</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1523,13 +1523,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="6">
-        <v>-1.32</v>
+        <v>-1.15</v>
       </c>
       <c r="D10" s="6">
-        <v>-1.15</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.17</v>
+        <v>-1.1</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.05</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1540,13 +1540,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>2.27</v>
+        <v>-0.9</v>
       </c>
       <c r="D11" s="6">
-        <v>-0.9</v>
+        <v>1.63</v>
       </c>
       <c r="E11" s="8">
-        <v>-3.17</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1557,13 +1557,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-1.15</v>
+        <v>-1</v>
       </c>
       <c r="D12" s="6">
-        <v>-1</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.15</v>
+        <v>0.66</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1.66</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1574,13 +1574,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="6">
-        <v>13.09</v>
+        <v>13.38</v>
       </c>
       <c r="D13" s="6">
-        <v>13.38</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.29</v>
+        <v>15.34</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1.96</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1591,13 +1591,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>46.03</v>
+        <v>45.87</v>
       </c>
       <c r="D14" s="6">
-        <v>45.87</v>
+        <v>47.41</v>
       </c>
       <c r="E14" s="8">
-        <v>-0.16</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1608,13 +1608,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>-15.93</v>
+        <v>-17.18</v>
       </c>
       <c r="D15" s="6">
-        <v>-17.18</v>
+        <v>-15.26</v>
       </c>
       <c r="E15" s="8">
-        <v>-1.25</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1625,13 +1625,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>-1.21</v>
+        <v>0.87</v>
       </c>
       <c r="D16" s="6">
-        <v>0.87</v>
-      </c>
-      <c r="E16" s="7">
-        <v>2.08</v>
+        <v>1.1</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.23</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1642,13 +1642,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>12.32</v>
+        <v>15.87</v>
       </c>
       <c r="D17" s="6">
-        <v>15.87</v>
-      </c>
-      <c r="E17" s="7">
-        <v>3.55</v>
+        <v>18.58</v>
+      </c>
+      <c r="E17" s="8">
+        <v>2.71</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1659,13 +1659,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>3.07</v>
+        <v>5.41</v>
       </c>
       <c r="D18" s="6">
-        <v>5.41</v>
+        <v>2.85</v>
       </c>
       <c r="E18" s="7">
-        <v>2.34</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1676,13 +1676,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="6">
-        <v>-7.96</v>
+        <v>-7.53</v>
       </c>
       <c r="D19" s="6">
-        <v>-7.53</v>
+        <v>-7.55</v>
       </c>
       <c r="E19" s="7">
-        <v>0.43</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1693,13 +1693,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-4.08</v>
+        <v>-6.35</v>
       </c>
       <c r="D20" s="6">
-        <v>-6.35</v>
+        <v>-4.35</v>
       </c>
       <c r="E20" s="8">
-        <v>-2.27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1710,13 +1710,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>-23.82</v>
+        <v>-23.15</v>
       </c>
       <c r="D21" s="6">
-        <v>-23.15</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.67</v>
+        <v>-22.3</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.85</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1727,13 +1727,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="6">
-        <v>4027</v>
+        <v>4045.8</v>
       </c>
       <c r="D22" s="6">
-        <v>4045.8</v>
+        <v>4044.9</v>
       </c>
       <c r="E22" s="7">
-        <v>18.8</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1744,13 +1744,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="6">
-        <v>321.9</v>
+        <v>314.3</v>
       </c>
       <c r="D23" s="6">
-        <v>314.3</v>
+        <v>321</v>
       </c>
       <c r="E23" s="8">
-        <v>-7.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1761,13 +1761,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>3537.9</v>
+        <v>3568.7</v>
       </c>
       <c r="D24" s="6">
-        <v>3568.7</v>
-      </c>
-      <c r="E24" s="7">
-        <v>30.8</v>
+        <v>3608.4</v>
+      </c>
+      <c r="E24" s="8">
+        <v>39.7</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1778,13 +1778,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="6">
-        <v>50.18</v>
+        <v>52.43</v>
       </c>
       <c r="D25" s="6">
-        <v>52.43</v>
+        <v>52.31</v>
       </c>
       <c r="E25" s="7">
-        <v>2.25</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1795,13 +1795,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="6">
-        <v>57.11</v>
+        <v>49.73</v>
       </c>
       <c r="D26" s="6">
-        <v>49.73</v>
+        <v>55.22</v>
       </c>
       <c r="E26" s="8">
-        <v>-7.38</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1812,13 +1812,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="6">
-        <v>51.79</v>
+        <v>54.6</v>
       </c>
       <c r="D27" s="6">
-        <v>54.6</v>
-      </c>
-      <c r="E27" s="7">
-        <v>2.81</v>
+        <v>58.01</v>
+      </c>
+      <c r="E27" s="8">
+        <v>3.41</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1829,13 +1829,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="6">
-        <v>-25.84</v>
+        <v>-39.3</v>
       </c>
       <c r="D28" s="6">
-        <v>-39.3</v>
+        <v>9.92</v>
       </c>
       <c r="E28" s="8">
-        <v>-13.46</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1846,13 +1846,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="6">
-        <v>-36.73</v>
+        <v>-37.84</v>
       </c>
       <c r="D29" s="6">
-        <v>-37.84</v>
+        <v>-3.38</v>
       </c>
       <c r="E29" s="8">
-        <v>-1.11</v>
+        <v>34.46</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1863,13 +1863,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="6">
-        <v>-60.58</v>
+        <v>-46.29</v>
       </c>
       <c r="D30" s="6">
-        <v>-46.29</v>
-      </c>
-      <c r="E30" s="7">
-        <v>14.29</v>
+        <v>678.38</v>
+      </c>
+      <c r="E30" s="8">
+        <v>724.67</v>
       </c>
     </row>
   </sheetData>
@@ -1934,16 +1934,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="11">
-        <v>52.3</v>
+        <v>55.2</v>
       </c>
       <c r="E2" s="11">
         <v>70</v>
       </c>
       <c r="F2" s="11">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="G2" s="11">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="H2" s="11">
         <v>66.3</v>
@@ -2062,13 +2062,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.3192</v>
+        <v>0.3263</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2075</v>
+        <v>0.2055</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0063</v>
+        <v>-0.0046</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,16 +178,25 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>49.7 → 55.2</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>49.7</t>
+    <t>52.3 → 44.3</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>52.3</t>
+  </si>
+  <si>
+    <t>44.3</t>
+  </si>
+  <si>
+    <t>55.2 → 45.6</t>
   </si>
   <si>
     <t>55.2</t>
+  </si>
+  <si>
+    <t>45.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +282,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +322,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -399,8 +408,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -911,10 +920,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>4044.9</v>
+        <v>3980.1</v>
       </c>
       <c r="D2">
-        <v>-0.02</v>
+        <v>-1.6</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -923,46 +932,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-7.55</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="H2">
-        <v>22.2</v>
+        <v>20.24</v>
       </c>
       <c r="I2">
-        <v>-1.1</v>
+        <v>-3.37</v>
       </c>
       <c r="J2">
-        <v>2.69</v>
+        <v>-1.12</v>
       </c>
       <c r="K2">
-        <v>1.1</v>
+        <v>0.68</v>
       </c>
       <c r="L2">
-        <v>15.34</v>
+        <v>12.89</v>
       </c>
       <c r="M2">
-        <v>20.55</v>
+        <v>19.95</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="P2">
-        <v>4054.96</v>
+        <v>4027.18</v>
       </c>
       <c r="Q2">
-        <v>4058.05</v>
+        <v>4057.56</v>
       </c>
       <c r="R2">
-        <v>3997.74</v>
+        <v>3993.31</v>
       </c>
       <c r="S2">
-        <v>3959.19</v>
+        <v>3959.27</v>
       </c>
       <c r="T2">
-        <v>2.16</v>
+        <v>0.53</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -977,34 +986,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>52.31</v>
+        <v>44.32</v>
       </c>
       <c r="Z2">
-        <v>23.42</v>
+        <v>15.86</v>
       </c>
       <c r="AA2">
-        <v>29.52</v>
+        <v>26.79</v>
       </c>
       <c r="AB2">
-        <v>-6.1</v>
+        <v>-10.93</v>
       </c>
       <c r="AC2">
         <v>11.53</v>
       </c>
       <c r="AD2">
-        <v>15.78</v>
+        <v>9.66</v>
       </c>
       <c r="AE2">
-        <v>56.06</v>
+        <v>56.68</v>
       </c>
       <c r="AF2">
-        <v>9.92</v>
+        <v>-32.71</v>
       </c>
       <c r="AG2">
-        <v>4116.95</v>
+        <v>4118.97</v>
       </c>
       <c r="AH2">
-        <v>3999.15</v>
+        <v>3996.14</v>
       </c>
       <c r="AI2">
         <v>3931.27</v>
@@ -1013,7 +1022,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>23.79</v>
+        <v>24.72</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1024,58 +1033,58 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>321</v>
+        <v>309.05</v>
       </c>
       <c r="D3">
-        <v>2.13</v>
+        <v>-3.72</v>
       </c>
       <c r="E3">
         <v>335.6</v>
       </c>
       <c r="F3">
-        <v>214.23</v>
+        <v>214.95</v>
       </c>
       <c r="G3">
-        <v>-4.35</v>
+        <v>-7.91</v>
       </c>
       <c r="H3">
-        <v>49.84</v>
+        <v>43.78</v>
       </c>
       <c r="I3">
-        <v>1.63</v>
+        <v>-3.27</v>
       </c>
       <c r="J3">
-        <v>3.13</v>
+        <v>-2.81</v>
       </c>
       <c r="K3">
-        <v>18.58</v>
+        <v>15.38</v>
       </c>
       <c r="L3">
-        <v>47.41</v>
+        <v>44.26</v>
       </c>
       <c r="M3">
-        <v>32.63</v>
+        <v>31.44</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P3">
-        <v>319.78</v>
+        <v>317.69</v>
       </c>
       <c r="Q3">
-        <v>316.51</v>
+        <v>316.07</v>
       </c>
       <c r="R3">
-        <v>313.16</v>
+        <v>313.56</v>
       </c>
       <c r="S3">
-        <v>291.4</v>
+        <v>291.5</v>
       </c>
       <c r="T3">
-        <v>10.16</v>
+        <v>6.02</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1090,34 +1099,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>55.22</v>
+        <v>45.64</v>
       </c>
       <c r="Z3">
-        <v>2.53</v>
+        <v>1.64</v>
       </c>
       <c r="AA3">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AB3">
-        <v>-0.01</v>
+        <v>-0.71</v>
       </c>
       <c r="AC3">
-        <v>55.5</v>
+        <v>30.03</v>
       </c>
       <c r="AD3">
-        <v>63.06</v>
+        <v>48.67</v>
       </c>
       <c r="AE3">
-        <v>8.91</v>
+        <v>9.4</v>
       </c>
       <c r="AF3">
-        <v>-3.38</v>
+        <v>103.41</v>
       </c>
       <c r="AG3">
-        <v>325.4</v>
+        <v>325.53</v>
       </c>
       <c r="AH3">
-        <v>307.62</v>
+        <v>306.61</v>
       </c>
       <c r="AI3">
         <v>329.06</v>
@@ -1137,10 +1146,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3608.4</v>
+        <v>3587.8</v>
       </c>
       <c r="D4">
-        <v>1.11</v>
+        <v>-0.57</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1149,25 +1158,25 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-22.3</v>
+        <v>-22.74</v>
       </c>
       <c r="H4">
-        <v>18.65</v>
+        <v>17.97</v>
       </c>
       <c r="I4">
-        <v>0.66</v>
+        <v>0.55</v>
       </c>
       <c r="J4">
-        <v>1.49</v>
+        <v>0.65</v>
       </c>
       <c r="K4">
-        <v>2.85</v>
+        <v>8.75</v>
       </c>
       <c r="L4">
-        <v>-15.26</v>
+        <v>-13.78</v>
       </c>
       <c r="M4">
-        <v>-0.46</v>
+        <v>-0.49</v>
       </c>
       <c r="N4">
         <v>34</v>
@@ -1176,19 +1185,19 @@
         <v>48</v>
       </c>
       <c r="P4">
-        <v>3565.28</v>
+        <v>3569.2</v>
       </c>
       <c r="Q4">
-        <v>3562.51</v>
+        <v>3566.8</v>
       </c>
       <c r="R4">
-        <v>3428.13</v>
+        <v>3433.13</v>
       </c>
       <c r="S4">
-        <v>3659.39</v>
+        <v>3656.77</v>
       </c>
       <c r="T4">
-        <v>-1.39</v>
+        <v>-1.89</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1203,34 +1212,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>58.01</v>
+        <v>55.68</v>
       </c>
       <c r="Z4">
-        <v>31.59</v>
+        <v>31.17</v>
       </c>
       <c r="AA4">
-        <v>36.93</v>
+        <v>35.78</v>
       </c>
       <c r="AB4">
-        <v>-5.34</v>
+        <v>-4.6</v>
       </c>
       <c r="AC4">
-        <v>48.31</v>
+        <v>64.47</v>
       </c>
       <c r="AD4">
-        <v>33.14</v>
+        <v>46.07</v>
       </c>
       <c r="AE4">
-        <v>102.28</v>
+        <v>101.26</v>
       </c>
       <c r="AF4">
-        <v>678.38</v>
+        <v>-68.68000000000001</v>
       </c>
       <c r="AG4">
-        <v>3653.61</v>
+        <v>3653.9</v>
       </c>
       <c r="AH4">
-        <v>3471.41</v>
+        <v>3479.7</v>
       </c>
       <c r="AI4">
         <v>3316.13</v>
@@ -1239,7 +1248,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>27.59</v>
+        <v>30.32</v>
       </c>
     </row>
   </sheetData>
@@ -1380,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1420,7 +1429,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>51</v>
@@ -1438,444 +1447,464 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>2.75</v>
-      </c>
-      <c r="D7" s="6">
-        <v>2.69</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-0.06</v>
+      <c r="C7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="D8" s="6">
-        <v>3.13</v>
-      </c>
-      <c r="E8" s="8">
-        <v>0.5</v>
+        <v>-1.12</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-3.81</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>0.27</v>
+        <v>3.13</v>
       </c>
       <c r="D9" s="6">
-        <v>1.49</v>
-      </c>
-      <c r="E9" s="8">
-        <v>1.22</v>
+        <v>-2.81</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-5.94</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-1.15</v>
+        <v>1.49</v>
       </c>
       <c r="D10" s="6">
-        <v>-1.1</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.05</v>
+        <v>0.65</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.84</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>-0.9</v>
+        <v>-1.1</v>
       </c>
       <c r="D11" s="6">
-        <v>1.63</v>
-      </c>
-      <c r="E11" s="8">
-        <v>2.53</v>
+        <v>-3.37</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-2.27</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-1</v>
+        <v>1.63</v>
       </c>
       <c r="D12" s="6">
-        <v>0.66</v>
-      </c>
-      <c r="E12" s="8">
-        <v>1.66</v>
+        <v>-3.27</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-4.9</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>13.38</v>
+        <v>0.66</v>
       </c>
       <c r="D13" s="6">
-        <v>15.34</v>
-      </c>
-      <c r="E13" s="8">
-        <v>1.96</v>
+        <v>0.55</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>45.87</v>
+        <v>15.34</v>
       </c>
       <c r="D14" s="6">
-        <v>47.41</v>
-      </c>
-      <c r="E14" s="8">
-        <v>1.54</v>
+        <v>12.89</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-2.45</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>-17.18</v>
+        <v>47.41</v>
       </c>
       <c r="D15" s="6">
-        <v>-15.26</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1.92</v>
+        <v>44.26</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-3.15</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="6">
-        <v>0.87</v>
+        <v>-15.26</v>
       </c>
       <c r="D16" s="6">
-        <v>1.1</v>
+        <v>-13.78</v>
       </c>
       <c r="E16" s="8">
-        <v>0.23</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>15.87</v>
+        <v>1.1</v>
       </c>
       <c r="D17" s="6">
-        <v>18.58</v>
-      </c>
-      <c r="E17" s="8">
-        <v>2.71</v>
+        <v>0.68</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>5.41</v>
+        <v>18.58</v>
       </c>
       <c r="D18" s="6">
-        <v>2.85</v>
+        <v>15.38</v>
       </c>
       <c r="E18" s="7">
-        <v>-2.56</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C19" s="6">
-        <v>-7.53</v>
+        <v>2.85</v>
       </c>
       <c r="D19" s="6">
-        <v>-7.55</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.02</v>
+        <v>8.75</v>
+      </c>
+      <c r="E19" s="8">
+        <v>5.9</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-6.35</v>
+        <v>-7.55</v>
       </c>
       <c r="D20" s="6">
-        <v>-4.35</v>
-      </c>
-      <c r="E20" s="8">
-        <v>2</v>
+        <v>-9.029999999999999</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.48</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>-23.15</v>
+        <v>-4.35</v>
       </c>
       <c r="D21" s="6">
-        <v>-22.3</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.85</v>
+        <v>-7.91</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-3.56</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C22" s="6">
-        <v>4045.8</v>
+        <v>-22.3</v>
       </c>
       <c r="D22" s="6">
-        <v>4044.9</v>
+        <v>-22.74</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.9</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="6">
-        <v>314.3</v>
+        <v>4044.9</v>
       </c>
       <c r="D23" s="6">
-        <v>321</v>
-      </c>
-      <c r="E23" s="8">
-        <v>6.7</v>
+        <v>3980.1</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-64.8</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>3568.7</v>
+        <v>321</v>
       </c>
       <c r="D24" s="6">
-        <v>3608.4</v>
-      </c>
-      <c r="E24" s="8">
-        <v>39.7</v>
+        <v>309.05</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-11.95</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C25" s="6">
-        <v>52.43</v>
+        <v>3608.4</v>
       </c>
       <c r="D25" s="6">
-        <v>52.31</v>
+        <v>3587.8</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.12</v>
+        <v>-20.6</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="6">
-        <v>49.73</v>
+        <v>52.31</v>
       </c>
       <c r="D26" s="6">
-        <v>55.22</v>
-      </c>
-      <c r="E26" s="8">
-        <v>5.49</v>
+        <v>44.32</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-7.99</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="6">
-        <v>54.6</v>
+        <v>55.22</v>
       </c>
       <c r="D27" s="6">
-        <v>58.01</v>
-      </c>
-      <c r="E27" s="8">
-        <v>3.41</v>
+        <v>45.64</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-9.58</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C28" s="6">
-        <v>-39.3</v>
+        <v>58.01</v>
       </c>
       <c r="D28" s="6">
-        <v>9.92</v>
-      </c>
-      <c r="E28" s="8">
-        <v>49.22</v>
+        <v>55.68</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-2.33</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="6">
-        <v>-37.84</v>
+        <v>9.92</v>
       </c>
       <c r="D29" s="6">
-        <v>-3.38</v>
-      </c>
-      <c r="E29" s="8">
-        <v>34.46</v>
+        <v>-32.71</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-42.63</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="6">
-        <v>-46.29</v>
+        <v>-3.38</v>
       </c>
       <c r="D30" s="6">
+        <v>103.41</v>
+      </c>
+      <c r="E30" s="8">
+        <v>106.79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="6">
         <v>678.38</v>
       </c>
-      <c r="E30" s="8">
-        <v>724.67</v>
+      <c r="D31" s="6">
+        <v>-68.68000000000001</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-747.0599999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1899,28 +1928,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1934,16 +1963,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="11">
-        <v>55.2</v>
+        <v>48.5</v>
       </c>
       <c r="E2" s="11">
         <v>70</v>
       </c>
       <c r="F2" s="11">
-        <v>2.4</v>
+        <v>-1.1</v>
       </c>
       <c r="G2" s="11">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H2" s="11">
         <v>66.3</v>
@@ -2062,13 +2091,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.3263</v>
+        <v>0.3144</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2055</v>
+        <v>0.1995</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0046</v>
+        <v>-0.0049</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,25 +178,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>52.3 → 44.3</t>
+    <t>55.7 → 47.4</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>52.3</t>
-  </si>
-  <si>
-    <t>44.3</t>
-  </si>
-  <si>
-    <t>55.2 → 45.6</t>
-  </si>
-  <si>
-    <t>55.2</t>
-  </si>
-  <si>
-    <t>45.6</t>
+    <t>55.7</t>
+  </si>
+  <si>
+    <t>47.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -408,8 +399,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -920,10 +911,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3980.1</v>
+        <v>3981</v>
       </c>
       <c r="D2">
-        <v>-1.6</v>
+        <v>0.02</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -932,46 +923,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-9.029999999999999</v>
+        <v>-9.01</v>
       </c>
       <c r="H2">
-        <v>20.24</v>
+        <v>20.27</v>
       </c>
       <c r="I2">
-        <v>-3.37</v>
+        <v>-1.41</v>
       </c>
       <c r="J2">
-        <v>-1.12</v>
+        <v>-0.23</v>
       </c>
       <c r="K2">
-        <v>0.68</v>
+        <v>0.99</v>
       </c>
       <c r="L2">
-        <v>12.89</v>
+        <v>11.63</v>
       </c>
       <c r="M2">
-        <v>19.95</v>
+        <v>19.96</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="P2">
-        <v>4027.18</v>
+        <v>4015.76</v>
       </c>
       <c r="Q2">
-        <v>4057.56</v>
+        <v>4053.76</v>
       </c>
       <c r="R2">
-        <v>3993.31</v>
+        <v>3989.34</v>
       </c>
       <c r="S2">
-        <v>3959.27</v>
+        <v>3959.35</v>
       </c>
       <c r="T2">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -986,34 +977,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>44.32</v>
+        <v>44.45</v>
       </c>
       <c r="Z2">
-        <v>15.86</v>
+        <v>9.83</v>
       </c>
       <c r="AA2">
-        <v>26.79</v>
+        <v>23.4</v>
       </c>
       <c r="AB2">
-        <v>-10.93</v>
+        <v>-13.57</v>
       </c>
       <c r="AC2">
-        <v>11.53</v>
+        <v>5.83</v>
       </c>
       <c r="AD2">
-        <v>9.66</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="AE2">
-        <v>56.68</v>
+        <v>55.89</v>
       </c>
       <c r="AF2">
-        <v>-32.71</v>
+        <v>-3.81</v>
       </c>
       <c r="AG2">
-        <v>4118.97</v>
+        <v>4124.08</v>
       </c>
       <c r="AH2">
-        <v>3996.14</v>
+        <v>3983.43</v>
       </c>
       <c r="AI2">
         <v>3931.27</v>
@@ -1022,7 +1013,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>24.72</v>
+        <v>27.13</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1033,37 +1024,37 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>309.05</v>
+        <v>312.8</v>
       </c>
       <c r="D3">
-        <v>-3.72</v>
+        <v>1.21</v>
       </c>
       <c r="E3">
         <v>335.6</v>
       </c>
       <c r="F3">
-        <v>214.95</v>
+        <v>219.67</v>
       </c>
       <c r="G3">
-        <v>-7.91</v>
+        <v>-6.79</v>
       </c>
       <c r="H3">
-        <v>43.78</v>
+        <v>42.4</v>
       </c>
       <c r="I3">
-        <v>-3.27</v>
+        <v>-2.92</v>
       </c>
       <c r="J3">
-        <v>-2.81</v>
+        <v>-1.6</v>
       </c>
       <c r="K3">
-        <v>15.38</v>
+        <v>17.29</v>
       </c>
       <c r="L3">
-        <v>44.26</v>
+        <v>45.52</v>
       </c>
       <c r="M3">
-        <v>31.44</v>
+        <v>31.52</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1072,19 +1063,19 @@
         <v>82</v>
       </c>
       <c r="P3">
-        <v>317.69</v>
+        <v>315.81</v>
       </c>
       <c r="Q3">
-        <v>316.07</v>
+        <v>315.79</v>
       </c>
       <c r="R3">
-        <v>313.56</v>
+        <v>314.09</v>
       </c>
       <c r="S3">
-        <v>291.5</v>
+        <v>291.61</v>
       </c>
       <c r="T3">
-        <v>6.02</v>
+        <v>7.27</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1099,34 +1090,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>45.64</v>
+        <v>48.65</v>
       </c>
       <c r="Z3">
-        <v>1.64</v>
+        <v>1.23</v>
       </c>
       <c r="AA3">
-        <v>2.36</v>
+        <v>2.13</v>
       </c>
       <c r="AB3">
-        <v>-0.71</v>
+        <v>-0.9</v>
       </c>
       <c r="AC3">
-        <v>30.03</v>
+        <v>27.93</v>
       </c>
       <c r="AD3">
-        <v>48.67</v>
+        <v>37.82</v>
       </c>
       <c r="AE3">
-        <v>9.4</v>
+        <v>9.49</v>
       </c>
       <c r="AF3">
-        <v>103.41</v>
+        <v>33.32</v>
       </c>
       <c r="AG3">
-        <v>325.53</v>
+        <v>325.29</v>
       </c>
       <c r="AH3">
-        <v>306.61</v>
+        <v>306.29</v>
       </c>
       <c r="AI3">
         <v>329.06</v>
@@ -1135,7 +1126,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>22.78</v>
+        <v>23.83</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1146,10 +1137,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3587.8</v>
+        <v>3505</v>
       </c>
       <c r="D4">
-        <v>-0.57</v>
+        <v>-2.31</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1158,46 +1149,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-22.74</v>
+        <v>-24.52</v>
       </c>
       <c r="H4">
-        <v>17.97</v>
+        <v>15.25</v>
       </c>
       <c r="I4">
-        <v>0.55</v>
+        <v>-1.08</v>
       </c>
       <c r="J4">
-        <v>0.65</v>
+        <v>0.09</v>
       </c>
       <c r="K4">
-        <v>8.75</v>
+        <v>7.12</v>
       </c>
       <c r="L4">
-        <v>-13.78</v>
+        <v>-15.71</v>
       </c>
       <c r="M4">
-        <v>-0.49</v>
+        <v>-1.67</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P4">
-        <v>3569.2</v>
+        <v>3561.56</v>
       </c>
       <c r="Q4">
-        <v>3566.8</v>
+        <v>3563.28</v>
       </c>
       <c r="R4">
-        <v>3433.13</v>
+        <v>3436.74</v>
       </c>
       <c r="S4">
-        <v>3656.77</v>
+        <v>3654.09</v>
       </c>
       <c r="T4">
-        <v>-1.89</v>
+        <v>-4.08</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1212,34 +1203,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>55.68</v>
+        <v>47.42</v>
       </c>
       <c r="Z4">
-        <v>31.17</v>
+        <v>23.89</v>
       </c>
       <c r="AA4">
-        <v>35.78</v>
+        <v>33.4</v>
       </c>
       <c r="AB4">
-        <v>-4.6</v>
+        <v>-9.51</v>
       </c>
       <c r="AC4">
-        <v>64.47</v>
+        <v>52.19</v>
       </c>
       <c r="AD4">
-        <v>46.07</v>
+        <v>54.99</v>
       </c>
       <c r="AE4">
-        <v>101.26</v>
+        <v>101.07</v>
       </c>
       <c r="AF4">
-        <v>-68.68000000000001</v>
+        <v>-62.58</v>
       </c>
       <c r="AG4">
-        <v>3653.9</v>
+        <v>3654.51</v>
       </c>
       <c r="AH4">
-        <v>3479.7</v>
+        <v>3472.06</v>
       </c>
       <c r="AI4">
         <v>3316.13</v>
@@ -1248,7 +1239,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>30.32</v>
+        <v>28.49</v>
       </c>
     </row>
   </sheetData>
@@ -1389,7 +1380,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1429,7 +1420,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>51</v>
@@ -1447,464 +1438,444 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="E6" s="3" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>63</v>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-1.12</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-0.23</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.89</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>2.69</v>
+        <v>-2.81</v>
       </c>
       <c r="D8" s="6">
-        <v>-1.12</v>
+        <v>-1.6</v>
       </c>
       <c r="E8" s="7">
-        <v>-3.81</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>3.13</v>
+        <v>0.65</v>
       </c>
       <c r="D9" s="6">
-        <v>-2.81</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-5.94</v>
+        <v>0.09</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="6">
-        <v>1.49</v>
+        <v>-3.37</v>
       </c>
       <c r="D10" s="6">
-        <v>0.65</v>
+        <v>-1.41</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.84</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>-1.1</v>
+        <v>-3.27</v>
       </c>
       <c r="D11" s="6">
-        <v>-3.37</v>
+        <v>-2.92</v>
       </c>
       <c r="E11" s="7">
-        <v>-2.27</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>1.63</v>
+        <v>0.55</v>
       </c>
       <c r="D12" s="6">
-        <v>-3.27</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-4.9</v>
+        <v>-1.08</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-1.63</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C13" s="6">
-        <v>0.66</v>
+        <v>12.89</v>
       </c>
       <c r="D13" s="6">
-        <v>0.55</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.11</v>
+        <v>11.63</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-1.26</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>15.34</v>
+        <v>44.26</v>
       </c>
       <c r="D14" s="6">
-        <v>12.89</v>
+        <v>45.52</v>
       </c>
       <c r="E14" s="7">
-        <v>-2.45</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>47.41</v>
+        <v>-13.78</v>
       </c>
       <c r="D15" s="6">
-        <v>44.26</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-3.15</v>
+        <v>-15.71</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-1.93</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>-15.26</v>
+        <v>0.68</v>
       </c>
       <c r="D16" s="6">
-        <v>-13.78</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1.48</v>
+        <v>0.99</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.31</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>1.1</v>
+        <v>15.38</v>
       </c>
       <c r="D17" s="6">
-        <v>0.68</v>
+        <v>17.29</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.42</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>18.58</v>
+        <v>8.75</v>
       </c>
       <c r="D18" s="6">
-        <v>15.38</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-3.2</v>
+        <v>7.12</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.63</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C19" s="6">
-        <v>2.85</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="D19" s="6">
-        <v>8.75</v>
-      </c>
-      <c r="E19" s="8">
-        <v>5.9</v>
+        <v>-9.01</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-7.55</v>
+        <v>-7.91</v>
       </c>
       <c r="D20" s="6">
-        <v>-9.029999999999999</v>
+        <v>-6.79</v>
       </c>
       <c r="E20" s="7">
-        <v>-1.48</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>-4.35</v>
+        <v>-22.74</v>
       </c>
       <c r="D21" s="6">
-        <v>-7.91</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-3.56</v>
+        <v>-24.52</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-1.78</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C22" s="6">
-        <v>-22.3</v>
+        <v>3980.1</v>
       </c>
       <c r="D22" s="6">
-        <v>-22.74</v>
+        <v>3981</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.44</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C23" s="6">
-        <v>4044.9</v>
+        <v>309.05</v>
       </c>
       <c r="D23" s="6">
-        <v>3980.1</v>
+        <v>312.8</v>
       </c>
       <c r="E23" s="7">
-        <v>-64.8</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>321</v>
+        <v>3587.8</v>
       </c>
       <c r="D24" s="6">
-        <v>309.05</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-11.95</v>
+        <v>3505</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-82.8</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C25" s="6">
-        <v>3608.4</v>
+        <v>44.32</v>
       </c>
       <c r="D25" s="6">
-        <v>3587.8</v>
+        <v>44.45</v>
       </c>
       <c r="E25" s="7">
-        <v>-20.6</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="6">
-        <v>52.31</v>
+        <v>45.64</v>
       </c>
       <c r="D26" s="6">
-        <v>44.32</v>
+        <v>48.65</v>
       </c>
       <c r="E26" s="7">
-        <v>-7.99</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="6">
-        <v>55.22</v>
+        <v>55.68</v>
       </c>
       <c r="D27" s="6">
-        <v>45.64</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-9.58</v>
+        <v>47.42</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-8.26</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C28" s="6">
-        <v>58.01</v>
+        <v>-32.71</v>
       </c>
       <c r="D28" s="6">
-        <v>55.68</v>
+        <v>-3.81</v>
       </c>
       <c r="E28" s="7">
-        <v>-2.33</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="6">
-        <v>9.92</v>
+        <v>103.41</v>
       </c>
       <c r="D29" s="6">
-        <v>-32.71</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-42.63</v>
+        <v>33.32</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-70.09</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="6">
-        <v>-3.38</v>
+        <v>-68.68000000000001</v>
       </c>
       <c r="D30" s="6">
-        <v>103.41</v>
-      </c>
-      <c r="E30" s="8">
-        <v>106.79</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="6">
-        <v>678.38</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-68.68000000000001</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-747.0599999999999</v>
+        <v>-62.58</v>
+      </c>
+      <c r="E30" s="7">
+        <v>6.1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1928,28 +1899,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>68</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1963,16 +1934,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="11">
-        <v>48.5</v>
+        <v>46.8</v>
       </c>
       <c r="E2" s="11">
         <v>70</v>
       </c>
       <c r="F2" s="11">
-        <v>-1.1</v>
+        <v>-0.6</v>
       </c>
       <c r="G2" s="11">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H2" s="11">
         <v>66.3</v>
@@ -2091,13 +2062,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.3144</v>
+        <v>0.3152</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1995</v>
+        <v>0.1996</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0049</v>
+        <v>-0.0167</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -178,16 +178,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>55.7 → 47.4</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>55.7</t>
-  </si>
-  <si>
-    <t>47.4</t>
+    <t>48.6 → 51.8</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>48.6</t>
+  </si>
+  <si>
+    <t>51.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +273,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +313,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -778,7 +778,8 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="6.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -911,10 +912,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3981</v>
+        <v>3975</v>
       </c>
       <c r="D2">
-        <v>0.02</v>
+        <v>-0.15</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -923,25 +924,25 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-9.01</v>
+        <v>-9.15</v>
       </c>
       <c r="H2">
-        <v>20.27</v>
+        <v>20.09</v>
       </c>
       <c r="I2">
-        <v>-1.41</v>
+        <v>-1.29</v>
       </c>
       <c r="J2">
-        <v>-0.23</v>
+        <v>-2.02</v>
       </c>
       <c r="K2">
-        <v>0.99</v>
+        <v>0.55</v>
       </c>
       <c r="L2">
-        <v>11.63</v>
+        <v>11.54</v>
       </c>
       <c r="M2">
-        <v>19.96</v>
+        <v>19.85</v>
       </c>
       <c r="N2">
         <v>66</v>
@@ -950,19 +951,19 @@
         <v>62</v>
       </c>
       <c r="P2">
-        <v>4015.76</v>
+        <v>4005.36</v>
       </c>
       <c r="Q2">
-        <v>4053.76</v>
+        <v>4049.42</v>
       </c>
       <c r="R2">
-        <v>3989.34</v>
+        <v>3985.21</v>
       </c>
       <c r="S2">
-        <v>3959.35</v>
+        <v>3959.28</v>
       </c>
       <c r="T2">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -977,34 +978,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>44.45</v>
+        <v>43.73</v>
       </c>
       <c r="Z2">
-        <v>9.83</v>
+        <v>4.51</v>
       </c>
       <c r="AA2">
-        <v>23.4</v>
+        <v>19.62</v>
       </c>
       <c r="AB2">
-        <v>-13.57</v>
+        <v>-15.11</v>
       </c>
       <c r="AC2">
-        <v>5.83</v>
+        <v>0.23</v>
       </c>
       <c r="AD2">
-        <v>9.630000000000001</v>
+        <v>5.86</v>
       </c>
       <c r="AE2">
-        <v>55.89</v>
+        <v>55.66</v>
       </c>
       <c r="AF2">
-        <v>-3.81</v>
+        <v>-29.51</v>
       </c>
       <c r="AG2">
-        <v>4124.08</v>
+        <v>4127.89</v>
       </c>
       <c r="AH2">
-        <v>3983.43</v>
+        <v>3970.94</v>
       </c>
       <c r="AI2">
         <v>3931.27</v>
@@ -1013,7 +1014,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>27.13</v>
+        <v>25.82</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1024,10 +1025,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>312.8</v>
+        <v>316.9</v>
       </c>
       <c r="D3">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1036,46 +1037,46 @@
         <v>219.67</v>
       </c>
       <c r="G3">
-        <v>-6.79</v>
+        <v>-5.57</v>
       </c>
       <c r="H3">
-        <v>42.4</v>
+        <v>44.26</v>
       </c>
       <c r="I3">
-        <v>-2.92</v>
+        <v>-1.55</v>
       </c>
       <c r="J3">
-        <v>-1.6</v>
+        <v>-0.47</v>
       </c>
       <c r="K3">
-        <v>17.29</v>
+        <v>17.98</v>
       </c>
       <c r="L3">
-        <v>45.52</v>
+        <v>43.84</v>
       </c>
       <c r="M3">
-        <v>31.52</v>
+        <v>31.93</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="P3">
-        <v>315.81</v>
+        <v>314.81</v>
       </c>
       <c r="Q3">
-        <v>315.79</v>
+        <v>315.8</v>
       </c>
       <c r="R3">
-        <v>314.09</v>
+        <v>314.5</v>
       </c>
       <c r="S3">
-        <v>291.61</v>
+        <v>291.71</v>
       </c>
       <c r="T3">
-        <v>7.27</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1090,31 +1091,31 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>48.65</v>
+        <v>51.79</v>
       </c>
       <c r="Z3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AA3">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="AB3">
-        <v>-0.9</v>
+        <v>-0.73</v>
       </c>
       <c r="AC3">
-        <v>27.93</v>
+        <v>20.43</v>
       </c>
       <c r="AD3">
-        <v>37.82</v>
+        <v>26.13</v>
       </c>
       <c r="AE3">
-        <v>9.49</v>
+        <v>9.26</v>
       </c>
       <c r="AF3">
-        <v>33.32</v>
+        <v>-31.47</v>
       </c>
       <c r="AG3">
-        <v>325.29</v>
+        <v>325.31</v>
       </c>
       <c r="AH3">
         <v>306.29</v>
@@ -1126,7 +1127,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>23.83</v>
+        <v>21.87</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1137,10 +1138,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3505</v>
+        <v>3501.2</v>
       </c>
       <c r="D4">
-        <v>-2.31</v>
+        <v>-0.11</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1149,25 +1150,25 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-24.52</v>
+        <v>-24.61</v>
       </c>
       <c r="H4">
-        <v>15.25</v>
+        <v>15.12</v>
       </c>
       <c r="I4">
-        <v>-1.08</v>
+        <v>-1.04</v>
       </c>
       <c r="J4">
-        <v>0.09</v>
+        <v>-2.07</v>
       </c>
       <c r="K4">
-        <v>7.12</v>
+        <v>8.98</v>
       </c>
       <c r="L4">
-        <v>-15.71</v>
+        <v>-16.21</v>
       </c>
       <c r="M4">
-        <v>-1.67</v>
+        <v>-3.05</v>
       </c>
       <c r="N4">
         <v>34</v>
@@ -1176,19 +1177,19 @@
         <v>47</v>
       </c>
       <c r="P4">
-        <v>3561.56</v>
+        <v>3554.22</v>
       </c>
       <c r="Q4">
-        <v>3563.28</v>
+        <v>3560.57</v>
       </c>
       <c r="R4">
-        <v>3436.74</v>
+        <v>3440.31</v>
       </c>
       <c r="S4">
-        <v>3654.09</v>
+        <v>3651.3</v>
       </c>
       <c r="T4">
-        <v>-4.08</v>
+        <v>-4.11</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1203,34 +1204,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>47.42</v>
+        <v>47.07</v>
       </c>
       <c r="Z4">
-        <v>23.89</v>
+        <v>17.6</v>
       </c>
       <c r="AA4">
-        <v>33.4</v>
+        <v>30.24</v>
       </c>
       <c r="AB4">
-        <v>-9.51</v>
+        <v>-12.64</v>
       </c>
       <c r="AC4">
-        <v>52.19</v>
+        <v>22.17</v>
       </c>
       <c r="AD4">
-        <v>54.99</v>
+        <v>46.28</v>
       </c>
       <c r="AE4">
-        <v>101.07</v>
+        <v>99.13</v>
       </c>
       <c r="AF4">
-        <v>-62.58</v>
+        <v>-58.05</v>
       </c>
       <c r="AG4">
-        <v>3654.51</v>
+        <v>3655.92</v>
       </c>
       <c r="AH4">
-        <v>3472.06</v>
+        <v>3465.23</v>
       </c>
       <c r="AI4">
         <v>3316.13</v>
@@ -1239,7 +1240,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>28.49</v>
+        <v>25.35</v>
       </c>
     </row>
   </sheetData>
@@ -1420,7 +1421,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>51</v>
@@ -1472,13 +1473,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-1.12</v>
+        <v>-0.23</v>
       </c>
       <c r="D7" s="6">
-        <v>-0.23</v>
+        <v>-2.02</v>
       </c>
       <c r="E7" s="7">
-        <v>0.89</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1489,13 +1490,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-2.81</v>
+        <v>-1.6</v>
       </c>
       <c r="D8" s="6">
-        <v>-1.6</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1.21</v>
+        <v>-0.47</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1.13</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1506,13 +1507,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>0.65</v>
+        <v>0.09</v>
       </c>
       <c r="D9" s="6">
-        <v>0.09</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-0.5600000000000001</v>
+        <v>-2.07</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-2.16</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1523,13 +1524,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="6">
-        <v>-3.37</v>
+        <v>-1.41</v>
       </c>
       <c r="D10" s="6">
-        <v>-1.41</v>
-      </c>
-      <c r="E10" s="7">
-        <v>1.96</v>
+        <v>-1.29</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.12</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1540,13 +1541,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>-3.27</v>
+        <v>-2.92</v>
       </c>
       <c r="D11" s="6">
-        <v>-2.92</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.35</v>
+        <v>-1.55</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.37</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1557,13 +1558,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>0.55</v>
+        <v>-1.08</v>
       </c>
       <c r="D12" s="6">
-        <v>-1.08</v>
+        <v>-1.04</v>
       </c>
       <c r="E12" s="8">
-        <v>-1.63</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1574,13 +1575,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="6">
-        <v>12.89</v>
+        <v>11.63</v>
       </c>
       <c r="D13" s="6">
-        <v>11.63</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-1.26</v>
+        <v>11.54</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1591,13 +1592,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>44.26</v>
+        <v>45.52</v>
       </c>
       <c r="D14" s="6">
-        <v>45.52</v>
+        <v>43.84</v>
       </c>
       <c r="E14" s="7">
-        <v>1.26</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1608,13 +1609,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>-13.78</v>
+        <v>-15.71</v>
       </c>
       <c r="D15" s="6">
-        <v>-15.71</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-1.93</v>
+        <v>-16.21</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1625,13 +1626,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>0.68</v>
+        <v>0.99</v>
       </c>
       <c r="D16" s="6">
-        <v>0.99</v>
+        <v>0.55</v>
       </c>
       <c r="E16" s="7">
-        <v>0.31</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1642,13 +1643,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>15.38</v>
+        <v>17.29</v>
       </c>
       <c r="D17" s="6">
-        <v>17.29</v>
-      </c>
-      <c r="E17" s="7">
-        <v>1.91</v>
+        <v>17.98</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1659,13 +1660,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>8.75</v>
+        <v>7.12</v>
       </c>
       <c r="D18" s="6">
-        <v>7.12</v>
+        <v>8.98</v>
       </c>
       <c r="E18" s="8">
-        <v>-1.63</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1676,13 +1677,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="6">
-        <v>-9.029999999999999</v>
+        <v>-9.01</v>
       </c>
       <c r="D19" s="6">
-        <v>-9.01</v>
+        <v>-9.15</v>
       </c>
       <c r="E19" s="7">
-        <v>0.02</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1693,13 +1694,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-7.91</v>
+        <v>-6.79</v>
       </c>
       <c r="D20" s="6">
-        <v>-6.79</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.12</v>
+        <v>-5.57</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1.22</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1710,13 +1711,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>-22.74</v>
+        <v>-24.52</v>
       </c>
       <c r="D21" s="6">
-        <v>-24.52</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-1.78</v>
+        <v>-24.61</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1727,13 +1728,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="6">
-        <v>3980.1</v>
+        <v>3981</v>
       </c>
       <c r="D22" s="6">
-        <v>3981</v>
+        <v>3975</v>
       </c>
       <c r="E22" s="7">
-        <v>0.9</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1744,13 +1745,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="6">
-        <v>309.05</v>
+        <v>312.8</v>
       </c>
       <c r="D23" s="6">
-        <v>312.8</v>
-      </c>
-      <c r="E23" s="7">
-        <v>3.75</v>
+        <v>316.9</v>
+      </c>
+      <c r="E23" s="8">
+        <v>4.1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1761,13 +1762,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>3587.8</v>
+        <v>3505</v>
       </c>
       <c r="D24" s="6">
-        <v>3505</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-82.8</v>
+        <v>3501.2</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-3.8</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1778,13 +1779,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="6">
-        <v>44.32</v>
+        <v>44.45</v>
       </c>
       <c r="D25" s="6">
-        <v>44.45</v>
+        <v>43.73</v>
       </c>
       <c r="E25" s="7">
-        <v>0.13</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1795,13 +1796,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="6">
-        <v>45.64</v>
+        <v>48.65</v>
       </c>
       <c r="D26" s="6">
-        <v>48.65</v>
-      </c>
-      <c r="E26" s="7">
-        <v>3.01</v>
+        <v>51.79</v>
+      </c>
+      <c r="E26" s="8">
+        <v>3.14</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1812,13 +1813,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="6">
-        <v>55.68</v>
+        <v>47.42</v>
       </c>
       <c r="D27" s="6">
-        <v>47.42</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-8.26</v>
+        <v>47.07</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1829,13 +1830,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="6">
-        <v>-32.71</v>
+        <v>-3.81</v>
       </c>
       <c r="D28" s="6">
-        <v>-3.81</v>
+        <v>-29.51</v>
       </c>
       <c r="E28" s="7">
-        <v>28.9</v>
+        <v>-25.7</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1846,13 +1847,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="6">
-        <v>103.41</v>
+        <v>33.32</v>
       </c>
       <c r="D29" s="6">
-        <v>33.32</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-70.09</v>
+        <v>-31.47</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-64.79000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1863,13 +1864,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="6">
-        <v>-68.68000000000001</v>
+        <v>-62.58</v>
       </c>
       <c r="D30" s="6">
-        <v>-62.58</v>
-      </c>
-      <c r="E30" s="7">
-        <v>6.1</v>
+        <v>-58.05</v>
+      </c>
+      <c r="E30" s="8">
+        <v>4.53</v>
       </c>
     </row>
   </sheetData>
@@ -1934,16 +1935,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="11">
-        <v>46.8</v>
+        <v>47.5</v>
       </c>
       <c r="E2" s="11">
         <v>70</v>
       </c>
       <c r="F2" s="11">
-        <v>-0.6</v>
+        <v>-1.5</v>
       </c>
       <c r="G2" s="11">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H2" s="11">
         <v>66.3</v>
@@ -2062,13 +2063,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.3152</v>
+        <v>0.3193</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1996</v>
+        <v>0.1985</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0167</v>
+        <v>-0.0305</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -178,16 +178,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>48.6 → 51.8</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>48.6</t>
+    <t>51.8 → 49.5</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>51.8</t>
+  </si>
+  <si>
+    <t>49.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +273,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +313,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -399,8 +399,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -778,8 +778,7 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="6.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -912,10 +911,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3975</v>
+        <v>3964.1</v>
       </c>
       <c r="D2">
-        <v>-0.15</v>
+        <v>-0.27</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -924,46 +923,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-9.15</v>
+        <v>-9.4</v>
       </c>
       <c r="H2">
-        <v>20.09</v>
+        <v>19.76</v>
       </c>
       <c r="I2">
-        <v>-1.29</v>
+        <v>-2.02</v>
       </c>
       <c r="J2">
-        <v>-2.02</v>
+        <v>-2.41</v>
       </c>
       <c r="K2">
-        <v>0.55</v>
+        <v>2.29</v>
       </c>
       <c r="L2">
-        <v>11.54</v>
+        <v>11.97</v>
       </c>
       <c r="M2">
-        <v>19.85</v>
+        <v>19.77</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="P2">
-        <v>4005.36</v>
+        <v>3989.02</v>
       </c>
       <c r="Q2">
-        <v>4049.42</v>
+        <v>4044.82</v>
       </c>
       <c r="R2">
-        <v>3985.21</v>
+        <v>3980.16</v>
       </c>
       <c r="S2">
-        <v>3959.28</v>
+        <v>3959.29</v>
       </c>
       <c r="T2">
-        <v>0.4</v>
+        <v>0.12</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -978,34 +977,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>43.73</v>
+        <v>42.4</v>
       </c>
       <c r="Z2">
-        <v>4.51</v>
+        <v>-0.57</v>
       </c>
       <c r="AA2">
-        <v>19.62</v>
+        <v>15.58</v>
       </c>
       <c r="AB2">
-        <v>-15.11</v>
+        <v>-16.15</v>
       </c>
       <c r="AC2">
         <v>0.23</v>
       </c>
       <c r="AD2">
-        <v>5.86</v>
+        <v>2.1</v>
       </c>
       <c r="AE2">
-        <v>55.66</v>
+        <v>53.89</v>
       </c>
       <c r="AF2">
-        <v>-29.51</v>
+        <v>2.45</v>
       </c>
       <c r="AG2">
-        <v>4127.89</v>
+        <v>4131.95</v>
       </c>
       <c r="AH2">
-        <v>3970.94</v>
+        <v>3957.69</v>
       </c>
       <c r="AI2">
         <v>3931.27</v>
@@ -1014,7 +1013,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>25.82</v>
+        <v>25.58</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1025,58 +1024,58 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>316.9</v>
+        <v>314</v>
       </c>
       <c r="D3">
-        <v>1.31</v>
+        <v>-0.92</v>
       </c>
       <c r="E3">
         <v>335.6</v>
       </c>
       <c r="F3">
-        <v>219.67</v>
+        <v>224.84</v>
       </c>
       <c r="G3">
-        <v>-5.57</v>
+        <v>-6.44</v>
       </c>
       <c r="H3">
-        <v>44.26</v>
+        <v>39.65</v>
       </c>
       <c r="I3">
-        <v>-1.55</v>
+        <v>-0.1</v>
       </c>
       <c r="J3">
-        <v>-0.47</v>
+        <v>-0.84</v>
       </c>
       <c r="K3">
-        <v>17.98</v>
+        <v>19.98</v>
       </c>
       <c r="L3">
-        <v>43.84</v>
+        <v>42.94</v>
       </c>
       <c r="M3">
-        <v>31.93</v>
+        <v>31.75</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="P3">
-        <v>314.81</v>
+        <v>314.75</v>
       </c>
       <c r="Q3">
-        <v>315.8</v>
+        <v>316.1</v>
       </c>
       <c r="R3">
-        <v>314.5</v>
+        <v>314.8</v>
       </c>
       <c r="S3">
-        <v>291.71</v>
+        <v>291.81</v>
       </c>
       <c r="T3">
-        <v>8.640000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1091,34 +1090,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>51.79</v>
+        <v>49.49</v>
       </c>
       <c r="Z3">
-        <v>1.22</v>
+        <v>0.97</v>
       </c>
       <c r="AA3">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AB3">
-        <v>-0.73</v>
+        <v>-0.79</v>
       </c>
       <c r="AC3">
-        <v>20.43</v>
+        <v>29.01</v>
       </c>
       <c r="AD3">
-        <v>26.13</v>
+        <v>25.79</v>
       </c>
       <c r="AE3">
-        <v>9.26</v>
+        <v>9.1</v>
       </c>
       <c r="AF3">
-        <v>-31.47</v>
+        <v>-27.73</v>
       </c>
       <c r="AG3">
-        <v>325.31</v>
+        <v>324.92</v>
       </c>
       <c r="AH3">
-        <v>306.29</v>
+        <v>307.28</v>
       </c>
       <c r="AI3">
         <v>329.06</v>
@@ -1127,7 +1126,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>21.87</v>
+        <v>19.32</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1138,10 +1137,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3501.2</v>
+        <v>3493.3</v>
       </c>
       <c r="D4">
-        <v>-0.11</v>
+        <v>-0.23</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1150,46 +1149,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-24.61</v>
+        <v>-24.78</v>
       </c>
       <c r="H4">
-        <v>15.12</v>
+        <v>14.86</v>
       </c>
       <c r="I4">
-        <v>-1.04</v>
+        <v>-2.11</v>
       </c>
       <c r="J4">
-        <v>-2.07</v>
+        <v>-1.75</v>
       </c>
       <c r="K4">
-        <v>8.98</v>
+        <v>10.37</v>
       </c>
       <c r="L4">
-        <v>-16.21</v>
+        <v>-15.66</v>
       </c>
       <c r="M4">
-        <v>-3.05</v>
+        <v>-3.12</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="P4">
-        <v>3554.22</v>
+        <v>3539.14</v>
       </c>
       <c r="Q4">
-        <v>3560.57</v>
+        <v>3555.3</v>
       </c>
       <c r="R4">
-        <v>3440.31</v>
+        <v>3443.73</v>
       </c>
       <c r="S4">
-        <v>3651.3</v>
+        <v>3648.62</v>
       </c>
       <c r="T4">
-        <v>-4.11</v>
+        <v>-4.26</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1204,34 +1203,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>47.07</v>
+        <v>46.32</v>
       </c>
       <c r="Z4">
-        <v>17.6</v>
+        <v>11.84</v>
       </c>
       <c r="AA4">
-        <v>30.24</v>
+        <v>26.56</v>
       </c>
       <c r="AB4">
-        <v>-12.64</v>
+        <v>-14.72</v>
       </c>
       <c r="AC4">
-        <v>22.17</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>46.28</v>
+        <v>24.79</v>
       </c>
       <c r="AE4">
-        <v>99.13</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="AF4">
-        <v>-58.05</v>
+        <v>-50.27</v>
       </c>
       <c r="AG4">
-        <v>3655.92</v>
+        <v>3653.39</v>
       </c>
       <c r="AH4">
-        <v>3465.23</v>
+        <v>3457.22</v>
       </c>
       <c r="AI4">
         <v>3316.13</v>
@@ -1240,7 +1239,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>25.35</v>
+        <v>22.3</v>
       </c>
     </row>
   </sheetData>
@@ -1473,13 +1472,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-0.23</v>
+        <v>-2.02</v>
       </c>
       <c r="D7" s="6">
-        <v>-2.02</v>
+        <v>-2.41</v>
       </c>
       <c r="E7" s="7">
-        <v>-1.79</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1490,13 +1489,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-1.6</v>
+        <v>-0.47</v>
       </c>
       <c r="D8" s="6">
-        <v>-0.47</v>
-      </c>
-      <c r="E8" s="8">
-        <v>1.13</v>
+        <v>-0.84</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.37</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1507,13 +1506,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>0.09</v>
+        <v>-2.07</v>
       </c>
       <c r="D9" s="6">
-        <v>-2.07</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-2.16</v>
+        <v>-1.75</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.32</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1524,13 +1523,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="6">
-        <v>-1.41</v>
+        <v>-1.29</v>
       </c>
       <c r="D10" s="6">
-        <v>-1.29</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.12</v>
+        <v>-2.02</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1541,13 +1540,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="6">
-        <v>-2.92</v>
+        <v>-1.55</v>
       </c>
       <c r="D11" s="6">
-        <v>-1.55</v>
+        <v>-0.1</v>
       </c>
       <c r="E11" s="8">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1558,13 +1557,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-1.08</v>
+        <v>-1.04</v>
       </c>
       <c r="D12" s="6">
-        <v>-1.04</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.04</v>
+        <v>-2.11</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-1.07</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1575,13 +1574,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="6">
-        <v>11.63</v>
+        <v>11.54</v>
       </c>
       <c r="D13" s="6">
-        <v>11.54</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.09</v>
+        <v>11.97</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.43</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1592,13 +1591,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>45.52</v>
+        <v>43.84</v>
       </c>
       <c r="D14" s="6">
-        <v>43.84</v>
+        <v>42.94</v>
       </c>
       <c r="E14" s="7">
-        <v>-1.68</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1609,13 +1608,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="6">
-        <v>-15.71</v>
+        <v>-16.21</v>
       </c>
       <c r="D15" s="6">
-        <v>-16.21</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.5</v>
+        <v>-15.66</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.55</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1626,13 +1625,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>0.99</v>
+        <v>0.55</v>
       </c>
       <c r="D16" s="6">
-        <v>0.55</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-0.44</v>
+        <v>2.29</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1.74</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1643,13 +1642,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>17.29</v>
+        <v>17.98</v>
       </c>
       <c r="D17" s="6">
-        <v>17.98</v>
+        <v>19.98</v>
       </c>
       <c r="E17" s="8">
-        <v>0.6899999999999999</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1660,13 +1659,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>7.12</v>
+        <v>8.98</v>
       </c>
       <c r="D18" s="6">
-        <v>8.98</v>
+        <v>10.37</v>
       </c>
       <c r="E18" s="8">
-        <v>1.86</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1677,13 +1676,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="6">
-        <v>-9.01</v>
+        <v>-9.15</v>
       </c>
       <c r="D19" s="6">
-        <v>-9.15</v>
+        <v>-9.4</v>
       </c>
       <c r="E19" s="7">
-        <v>-0.14</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1694,13 +1693,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="6">
-        <v>-6.79</v>
+        <v>-5.57</v>
       </c>
       <c r="D20" s="6">
-        <v>-5.57</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1.22</v>
+        <v>-6.44</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1711,13 +1710,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="6">
-        <v>-24.52</v>
+        <v>-24.61</v>
       </c>
       <c r="D21" s="6">
-        <v>-24.61</v>
+        <v>-24.78</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.09</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1728,13 +1727,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="6">
-        <v>3981</v>
+        <v>3975</v>
       </c>
       <c r="D22" s="6">
-        <v>3975</v>
+        <v>3964.1</v>
       </c>
       <c r="E22" s="7">
-        <v>-6</v>
+        <v>-10.9</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1745,13 +1744,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="6">
-        <v>312.8</v>
+        <v>316.9</v>
       </c>
       <c r="D23" s="6">
-        <v>316.9</v>
-      </c>
-      <c r="E23" s="8">
-        <v>4.1</v>
+        <v>314</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-2.9</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1762,13 +1761,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="6">
-        <v>3505</v>
+        <v>3501.2</v>
       </c>
       <c r="D24" s="6">
-        <v>3501.2</v>
+        <v>3493.3</v>
       </c>
       <c r="E24" s="7">
-        <v>-3.8</v>
+        <v>-7.9</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1779,13 +1778,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="6">
-        <v>44.45</v>
+        <v>43.73</v>
       </c>
       <c r="D25" s="6">
-        <v>43.73</v>
+        <v>42.4</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.72</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1796,13 +1795,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="6">
-        <v>48.65</v>
+        <v>51.79</v>
       </c>
       <c r="D26" s="6">
-        <v>51.79</v>
-      </c>
-      <c r="E26" s="8">
-        <v>3.14</v>
+        <v>49.49</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-2.3</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1813,13 +1812,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="6">
-        <v>47.42</v>
+        <v>47.07</v>
       </c>
       <c r="D27" s="6">
-        <v>47.07</v>
+        <v>46.32</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.35</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1830,13 +1829,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="6">
-        <v>-3.81</v>
+        <v>-29.51</v>
       </c>
       <c r="D28" s="6">
-        <v>-29.51</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-25.7</v>
+        <v>2.45</v>
+      </c>
+      <c r="E28" s="8">
+        <v>31.96</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1847,13 +1846,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="6">
-        <v>33.32</v>
+        <v>-31.47</v>
       </c>
       <c r="D29" s="6">
-        <v>-31.47</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-64.79000000000001</v>
+        <v>-27.73</v>
+      </c>
+      <c r="E29" s="8">
+        <v>3.74</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1864,13 +1863,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="6">
-        <v>-62.58</v>
+        <v>-58.05</v>
       </c>
       <c r="D30" s="6">
-        <v>-58.05</v>
+        <v>-50.27</v>
       </c>
       <c r="E30" s="8">
-        <v>4.53</v>
+        <v>7.78</v>
       </c>
     </row>
   </sheetData>
@@ -1935,16 +1934,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="11">
-        <v>47.5</v>
+        <v>46.1</v>
       </c>
       <c r="E2" s="11">
         <v>70</v>
       </c>
       <c r="F2" s="11">
-        <v>-1.5</v>
+        <v>-1.7</v>
       </c>
       <c r="G2" s="11">
-        <v>9.199999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="H2" s="11">
         <v>66.3</v>
@@ -2063,13 +2062,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="14">
-        <v>0.3193</v>
+        <v>0.3175</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1985</v>
+        <v>0.1977</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0305</v>
+        <v>-0.0312</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="60">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,34 +160,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>51.8 → 49.5</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.8</t>
-  </si>
-  <si>
-    <t>49.5</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +246,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -389,15 +362,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -911,10 +883,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3964.1</v>
+        <v>3999</v>
       </c>
       <c r="D2">
-        <v>-0.27</v>
+        <v>0.88</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -923,46 +895,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-9.4</v>
+        <v>-8.6</v>
       </c>
       <c r="H2">
-        <v>19.76</v>
+        <v>20.81</v>
       </c>
       <c r="I2">
-        <v>-2.02</v>
+        <v>-1.13</v>
       </c>
       <c r="J2">
-        <v>-2.41</v>
+        <v>-1.41</v>
       </c>
       <c r="K2">
-        <v>2.29</v>
+        <v>2.52</v>
       </c>
       <c r="L2">
-        <v>11.97</v>
+        <v>12.14</v>
       </c>
       <c r="M2">
-        <v>19.77</v>
+        <v>20.14</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P2">
-        <v>3989.02</v>
+        <v>3979.84</v>
       </c>
       <c r="Q2">
-        <v>4044.82</v>
+        <v>4040.77</v>
       </c>
       <c r="R2">
-        <v>3980.16</v>
+        <v>3976.84</v>
       </c>
       <c r="S2">
-        <v>3959.29</v>
+        <v>3959.39</v>
       </c>
       <c r="T2">
-        <v>0.12</v>
+        <v>1</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -977,34 +949,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>42.4</v>
+        <v>47.88</v>
       </c>
       <c r="Z2">
-        <v>-0.57</v>
+        <v>-1.77</v>
       </c>
       <c r="AA2">
-        <v>15.58</v>
+        <v>12.11</v>
       </c>
       <c r="AB2">
-        <v>-16.15</v>
+        <v>-13.88</v>
       </c>
       <c r="AC2">
-        <v>0.23</v>
+        <v>8.94</v>
       </c>
       <c r="AD2">
-        <v>2.1</v>
+        <v>3.13</v>
       </c>
       <c r="AE2">
-        <v>53.89</v>
+        <v>53.18</v>
       </c>
       <c r="AF2">
-        <v>2.45</v>
+        <v>-2.09</v>
       </c>
       <c r="AG2">
-        <v>4131.95</v>
+        <v>4128.55</v>
       </c>
       <c r="AH2">
-        <v>3957.69</v>
+        <v>3952.99</v>
       </c>
       <c r="AI2">
         <v>3931.27</v>
@@ -1013,7 +985,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>25.58</v>
+        <v>24.06</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1024,37 +996,37 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>314</v>
+        <v>312.5</v>
       </c>
       <c r="D3">
-        <v>-0.92</v>
+        <v>-0.48</v>
       </c>
       <c r="E3">
         <v>335.6</v>
       </c>
       <c r="F3">
-        <v>224.84</v>
+        <v>225.53</v>
       </c>
       <c r="G3">
-        <v>-6.44</v>
+        <v>-6.88</v>
       </c>
       <c r="H3">
-        <v>39.65</v>
+        <v>38.56</v>
       </c>
       <c r="I3">
-        <v>-0.1</v>
+        <v>-2.65</v>
       </c>
       <c r="J3">
-        <v>-0.84</v>
+        <v>1.46</v>
       </c>
       <c r="K3">
-        <v>19.98</v>
+        <v>17.68</v>
       </c>
       <c r="L3">
-        <v>42.94</v>
+        <v>38.99</v>
       </c>
       <c r="M3">
-        <v>31.75</v>
+        <v>31.59</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1063,19 +1035,19 @@
         <v>82</v>
       </c>
       <c r="P3">
-        <v>314.75</v>
+        <v>313.05</v>
       </c>
       <c r="Q3">
-        <v>316.1</v>
+        <v>316.08</v>
       </c>
       <c r="R3">
-        <v>314.8</v>
+        <v>315.07</v>
       </c>
       <c r="S3">
-        <v>291.81</v>
+        <v>291.9</v>
       </c>
       <c r="T3">
-        <v>7.6</v>
+        <v>7.06</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1090,34 +1062,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>49.49</v>
+        <v>48.29</v>
       </c>
       <c r="Z3">
-        <v>0.97</v>
+        <v>0.64</v>
       </c>
       <c r="AA3">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AB3">
-        <v>-0.79</v>
+        <v>-0.89</v>
       </c>
       <c r="AC3">
-        <v>29.01</v>
+        <v>29.79</v>
       </c>
       <c r="AD3">
-        <v>25.79</v>
+        <v>26.41</v>
       </c>
       <c r="AE3">
-        <v>9.1</v>
+        <v>8.77</v>
       </c>
       <c r="AF3">
-        <v>-27.73</v>
+        <v>-55.22</v>
       </c>
       <c r="AG3">
-        <v>324.92</v>
+        <v>324.94</v>
       </c>
       <c r="AH3">
-        <v>307.28</v>
+        <v>307.23</v>
       </c>
       <c r="AI3">
         <v>329.06</v>
@@ -1126,7 +1098,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>19.32</v>
+        <v>17.76</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1137,10 +1109,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3493.3</v>
+        <v>3414.2</v>
       </c>
       <c r="D4">
-        <v>-0.23</v>
+        <v>-2.26</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1149,46 +1121,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-24.78</v>
+        <v>-26.48</v>
       </c>
       <c r="H4">
-        <v>14.86</v>
+        <v>12.26</v>
       </c>
       <c r="I4">
-        <v>-2.11</v>
+        <v>-5.38</v>
       </c>
       <c r="J4">
-        <v>-1.75</v>
+        <v>-5.13</v>
       </c>
       <c r="K4">
-        <v>10.37</v>
+        <v>-0.1</v>
       </c>
       <c r="L4">
-        <v>-15.66</v>
+        <v>-17.35</v>
       </c>
       <c r="M4">
-        <v>-3.12</v>
+        <v>-3.42</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P4">
-        <v>3539.14</v>
+        <v>3500.3</v>
       </c>
       <c r="Q4">
-        <v>3555.3</v>
+        <v>3546.84</v>
       </c>
       <c r="R4">
-        <v>3443.73</v>
+        <v>3449.42</v>
       </c>
       <c r="S4">
-        <v>3648.62</v>
+        <v>3643.74</v>
       </c>
       <c r="T4">
-        <v>-4.26</v>
+        <v>-6.3</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1203,34 +1175,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>46.32</v>
+        <v>39.49</v>
       </c>
       <c r="Z4">
-        <v>11.84</v>
+        <v>0.89</v>
       </c>
       <c r="AA4">
-        <v>26.56</v>
+        <v>21.43</v>
       </c>
       <c r="AB4">
-        <v>-14.72</v>
+        <v>-20.54</v>
       </c>
       <c r="AC4">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>24.79</v>
+        <v>7.39</v>
       </c>
       <c r="AE4">
-        <v>97.31999999999999</v>
+        <v>97.03</v>
       </c>
       <c r="AF4">
-        <v>-50.27</v>
+        <v>-36.92</v>
       </c>
       <c r="AG4">
-        <v>3653.39</v>
+        <v>3662.36</v>
       </c>
       <c r="AH4">
-        <v>3457.22</v>
+        <v>3431.33</v>
       </c>
       <c r="AI4">
         <v>3316.13</v>
@@ -1239,7 +1211,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>22.3</v>
+        <v>22.49</v>
       </c>
     </row>
   </sheetData>
@@ -1400,47 +1372,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1448,428 +1385,428 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>60</v>
+      <c r="B6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
+        <v>-2.41</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-1.41</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-0.84</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1.46</v>
+      </c>
+      <c r="E8" s="6">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-1.75</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-5.13</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-3.38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5">
         <v>-2.02</v>
       </c>
-      <c r="D7" s="6">
-        <v>-2.41</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D10" s="5">
+        <v>-1.13</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-0.47</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-0.84</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-0.1</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-2.65</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-2.55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-2.07</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-1.75</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-2.11</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-5.38</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-3.27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-1.29</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-2.02</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5">
+        <v>11.97</v>
+      </c>
+      <c r="D13" s="5">
+        <v>12.14</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-1.55</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="B14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5">
+        <v>42.94</v>
+      </c>
+      <c r="D14" s="5">
+        <v>38.99</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-3.95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-15.66</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-17.35</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-1.69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>2.29</v>
+      </c>
+      <c r="D16" s="5">
+        <v>2.52</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="5">
+        <v>19.98</v>
+      </c>
+      <c r="D17" s="5">
+        <v>17.68</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-2.3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5">
+        <v>10.37</v>
+      </c>
+      <c r="D18" s="5">
         <v>-0.1</v>
       </c>
-      <c r="E11" s="8">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="E18" s="7">
+        <v>-10.47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-9.4</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-8.6</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-6.44</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-6.88</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-1.04</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-2.11</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-1.07</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-24.78</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-26.48</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="6">
-        <v>11.54</v>
-      </c>
-      <c r="D13" s="6">
-        <v>11.97</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="5">
+        <v>3964.1</v>
+      </c>
+      <c r="D22" s="5">
+        <v>3999</v>
+      </c>
+      <c r="E22" s="6">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="6">
-        <v>43.84</v>
-      </c>
-      <c r="D14" s="6">
-        <v>42.94</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="5">
+        <v>314</v>
+      </c>
+      <c r="D23" s="5">
+        <v>312.5</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-16.21</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-15.66</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="5">
+        <v>3493.3</v>
+      </c>
+      <c r="D24" s="5">
+        <v>3414.2</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-79.09999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.55</v>
-      </c>
-      <c r="D16" s="6">
-        <v>2.29</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="5">
+        <v>42.4</v>
+      </c>
+      <c r="D25" s="5">
+        <v>47.88</v>
+      </c>
+      <c r="E25" s="6">
+        <v>5.48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="6">
-        <v>17.98</v>
-      </c>
-      <c r="D17" s="6">
-        <v>19.98</v>
-      </c>
-      <c r="E17" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="5">
+        <v>49.49</v>
+      </c>
+      <c r="D26" s="5">
+        <v>48.29</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="6">
-        <v>8.98</v>
-      </c>
-      <c r="D18" s="6">
-        <v>10.37</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1.39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
+        <v>46.32</v>
+      </c>
+      <c r="D27" s="5">
+        <v>39.49</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-6.83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-9.15</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-9.4</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="5">
+        <v>2.45</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-2.09</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-4.54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-5.57</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-6.44</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.87</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-27.73</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-55.22</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-27.49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-24.61</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-24.78</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="6">
-        <v>3975</v>
-      </c>
-      <c r="D22" s="6">
-        <v>3964.1</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-10.9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6">
-        <v>316.9</v>
-      </c>
-      <c r="D23" s="6">
-        <v>314</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="6">
-        <v>3501.2</v>
-      </c>
-      <c r="D24" s="6">
-        <v>3493.3</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-7.9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="6">
-        <v>43.73</v>
-      </c>
-      <c r="D25" s="6">
-        <v>42.4</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.33</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="6">
-        <v>51.79</v>
-      </c>
-      <c r="D26" s="6">
-        <v>49.49</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-2.3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="6">
-        <v>47.07</v>
-      </c>
-      <c r="D27" s="6">
-        <v>46.32</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6">
-        <v>-29.51</v>
-      </c>
-      <c r="D28" s="6">
-        <v>2.45</v>
-      </c>
-      <c r="E28" s="8">
-        <v>31.96</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-31.47</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-27.73</v>
-      </c>
-      <c r="E29" s="8">
-        <v>3.74</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-58.05</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C30" s="5">
         <v>-50.27</v>
       </c>
-      <c r="E30" s="8">
-        <v>7.78</v>
+      <c r="D30" s="5">
+        <v>-36.92</v>
+      </c>
+      <c r="E30" s="6">
+        <v>13.35</v>
       </c>
     </row>
   </sheetData>
@@ -1895,60 +1832,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>68</v>
+      <c r="B1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>64.52</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="11">
-        <v>46.1</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>45.2</v>
+      </c>
+      <c r="E2" s="10">
         <v>70</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="10">
         <v>-1.7</v>
       </c>
-      <c r="G2" s="11">
-        <v>10.9</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="G2" s="10">
+        <v>6.7</v>
+      </c>
+      <c r="H2" s="10">
         <v>66.3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>70</v>
       </c>
     </row>
@@ -2050,25 +1987,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="14">
-        <v>0.3175</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1977</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0312</v>
+      <c r="A2" s="13">
+        <v>0.3159</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.2014</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0342</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -246,14 +246,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,13 +286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -750,7 +750,8 @@
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="6.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -883,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3999</v>
+        <v>3946.1</v>
       </c>
       <c r="D2">
-        <v>0.88</v>
+        <v>-1.32</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -895,46 +896,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-8.6</v>
+        <v>-9.81</v>
       </c>
       <c r="H2">
-        <v>20.81</v>
+        <v>19.22</v>
       </c>
       <c r="I2">
-        <v>-1.13</v>
+        <v>-0.85</v>
       </c>
       <c r="J2">
-        <v>-1.41</v>
+        <v>-3.28</v>
       </c>
       <c r="K2">
-        <v>2.52</v>
+        <v>0.73</v>
       </c>
       <c r="L2">
-        <v>12.14</v>
+        <v>10.91</v>
       </c>
       <c r="M2">
-        <v>20.14</v>
+        <v>20.03</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P2">
-        <v>3979.84</v>
+        <v>3973.04</v>
       </c>
       <c r="Q2">
-        <v>4040.77</v>
+        <v>4036.21</v>
       </c>
       <c r="R2">
-        <v>3976.84</v>
+        <v>3972.89</v>
       </c>
       <c r="S2">
-        <v>3959.39</v>
+        <v>3959.12</v>
       </c>
       <c r="T2">
-        <v>1</v>
+        <v>-0.33</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -946,37 +947,37 @@
         <v>41</v>
       </c>
       <c r="X2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>47.88</v>
+        <v>41.44</v>
       </c>
       <c r="Z2">
-        <v>-1.77</v>
+        <v>-6.9</v>
       </c>
       <c r="AA2">
-        <v>12.11</v>
+        <v>8.31</v>
       </c>
       <c r="AB2">
-        <v>-13.88</v>
+        <v>-15.21</v>
       </c>
       <c r="AC2">
         <v>8.94</v>
       </c>
       <c r="AD2">
-        <v>3.13</v>
+        <v>6.04</v>
       </c>
       <c r="AE2">
-        <v>53.18</v>
+        <v>53.16</v>
       </c>
       <c r="AF2">
-        <v>-2.09</v>
+        <v>-7.68</v>
       </c>
       <c r="AG2">
-        <v>4128.55</v>
+        <v>4133.68</v>
       </c>
       <c r="AH2">
-        <v>3952.99</v>
+        <v>3938.73</v>
       </c>
       <c r="AI2">
         <v>3931.27</v>
@@ -985,7 +986,7 @@
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>24.06</v>
+        <v>24.11</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -996,58 +997,58 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>312.5</v>
+        <v>308.3</v>
       </c>
       <c r="D3">
-        <v>-0.48</v>
+        <v>-1.34</v>
       </c>
       <c r="E3">
         <v>335.6</v>
       </c>
       <c r="F3">
-        <v>225.53</v>
+        <v>228.16</v>
       </c>
       <c r="G3">
-        <v>-6.88</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="H3">
-        <v>38.56</v>
+        <v>35.12</v>
       </c>
       <c r="I3">
-        <v>-2.65</v>
+        <v>-0.24</v>
       </c>
       <c r="J3">
-        <v>1.46</v>
+        <v>-1.45</v>
       </c>
       <c r="K3">
-        <v>17.68</v>
+        <v>18.42</v>
       </c>
       <c r="L3">
-        <v>38.99</v>
+        <v>36.7</v>
       </c>
       <c r="M3">
-        <v>31.59</v>
+        <v>31.12</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P3">
-        <v>313.05</v>
+        <v>312.9</v>
       </c>
       <c r="Q3">
-        <v>316.08</v>
+        <v>315.73</v>
       </c>
       <c r="R3">
-        <v>315.07</v>
+        <v>315.02</v>
       </c>
       <c r="S3">
-        <v>291.9</v>
+        <v>292</v>
       </c>
       <c r="T3">
-        <v>7.06</v>
+        <v>5.58</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1062,34 +1063,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>48.29</v>
+        <v>45</v>
       </c>
       <c r="Z3">
-        <v>0.64</v>
+        <v>0.04</v>
       </c>
       <c r="AA3">
-        <v>1.53</v>
+        <v>1.23</v>
       </c>
       <c r="AB3">
-        <v>-0.89</v>
+        <v>-1.19</v>
       </c>
       <c r="AC3">
-        <v>29.79</v>
+        <v>16.07</v>
       </c>
       <c r="AD3">
-        <v>26.41</v>
+        <v>24.95</v>
       </c>
       <c r="AE3">
-        <v>8.77</v>
+        <v>8.44</v>
       </c>
       <c r="AF3">
-        <v>-55.22</v>
+        <v>-66.64</v>
       </c>
       <c r="AG3">
-        <v>324.94</v>
+        <v>325.24</v>
       </c>
       <c r="AH3">
-        <v>307.23</v>
+        <v>306.21</v>
       </c>
       <c r="AI3">
         <v>329.06</v>
@@ -1098,7 +1099,7 @@
         <v>44</v>
       </c>
       <c r="AK3">
-        <v>17.76</v>
+        <v>17.74</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1109,10 +1110,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3414.2</v>
+        <v>3389.1</v>
       </c>
       <c r="D4">
-        <v>-2.26</v>
+        <v>-0.74</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1121,25 +1122,25 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-26.48</v>
+        <v>-27.02</v>
       </c>
       <c r="H4">
-        <v>12.26</v>
+        <v>11.44</v>
       </c>
       <c r="I4">
-        <v>-5.38</v>
+        <v>-5.54</v>
       </c>
       <c r="J4">
-        <v>-5.13</v>
+        <v>-5.42</v>
       </c>
       <c r="K4">
-        <v>-0.1</v>
+        <v>1.84</v>
       </c>
       <c r="L4">
-        <v>-17.35</v>
+        <v>-17.51</v>
       </c>
       <c r="M4">
-        <v>-3.42</v>
+        <v>-3.67</v>
       </c>
       <c r="N4">
         <v>34</v>
@@ -1148,19 +1149,19 @@
         <v>38</v>
       </c>
       <c r="P4">
-        <v>3500.3</v>
+        <v>3460.56</v>
       </c>
       <c r="Q4">
-        <v>3546.84</v>
+        <v>3533.66</v>
       </c>
       <c r="R4">
-        <v>3449.42</v>
+        <v>3454.41</v>
       </c>
       <c r="S4">
-        <v>3643.74</v>
+        <v>3639.27</v>
       </c>
       <c r="T4">
-        <v>-6.3</v>
+        <v>-6.87</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1175,34 +1176,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>39.49</v>
+        <v>37.6</v>
       </c>
       <c r="Z4">
-        <v>0.89</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="AA4">
-        <v>21.43</v>
+        <v>15.2</v>
       </c>
       <c r="AB4">
-        <v>-20.54</v>
+        <v>-24.9</v>
       </c>
       <c r="AC4">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>7.39</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>97.03</v>
+        <v>94.38</v>
       </c>
       <c r="AF4">
-        <v>-36.92</v>
+        <v>-44.6</v>
       </c>
       <c r="AG4">
-        <v>3662.36</v>
+        <v>3658.13</v>
       </c>
       <c r="AH4">
-        <v>3431.33</v>
+        <v>3409.2</v>
       </c>
       <c r="AI4">
         <v>3316.13</v>
@@ -1211,7 +1212,7 @@
         <v>43</v>
       </c>
       <c r="AK4">
-        <v>22.49</v>
+        <v>23.54</v>
       </c>
     </row>
   </sheetData>
@@ -1409,13 +1410,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-2.41</v>
+        <v>-1.41</v>
       </c>
       <c r="D7" s="5">
-        <v>-1.41</v>
+        <v>-3.28</v>
       </c>
       <c r="E7" s="6">
-        <v>1</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1426,13 +1427,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-0.84</v>
+        <v>1.46</v>
       </c>
       <c r="D8" s="5">
-        <v>1.46</v>
+        <v>-1.45</v>
       </c>
       <c r="E8" s="6">
-        <v>2.3</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1443,13 +1444,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-1.75</v>
+        <v>-5.13</v>
       </c>
       <c r="D9" s="5">
-        <v>-5.13</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-3.38</v>
+        <v>-5.42</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1460,13 +1461,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-2.02</v>
+        <v>-1.13</v>
       </c>
       <c r="D10" s="5">
-        <v>-1.13</v>
-      </c>
-      <c r="E10" s="6">
-        <v>0.89</v>
+        <v>-0.85</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.28</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1477,13 +1478,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-0.1</v>
+        <v>-2.65</v>
       </c>
       <c r="D11" s="5">
-        <v>-2.65</v>
+        <v>-0.24</v>
       </c>
       <c r="E11" s="7">
-        <v>-2.55</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1494,13 +1495,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-2.11</v>
+        <v>-5.38</v>
       </c>
       <c r="D12" s="5">
-        <v>-5.38</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-3.27</v>
+        <v>-5.54</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1511,13 +1512,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>11.97</v>
+        <v>12.14</v>
       </c>
       <c r="D13" s="5">
-        <v>12.14</v>
+        <v>10.91</v>
       </c>
       <c r="E13" s="6">
-        <v>0.17</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1528,13 +1529,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>42.94</v>
+        <v>38.99</v>
       </c>
       <c r="D14" s="5">
-        <v>38.99</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-3.95</v>
+        <v>36.7</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-2.29</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1545,13 +1546,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-15.66</v>
+        <v>-17.35</v>
       </c>
       <c r="D15" s="5">
-        <v>-17.35</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-1.69</v>
+        <v>-17.51</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1562,13 +1563,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>2.29</v>
+        <v>2.52</v>
       </c>
       <c r="D16" s="5">
-        <v>2.52</v>
+        <v>0.73</v>
       </c>
       <c r="E16" s="6">
-        <v>0.23</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1579,13 +1580,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>19.98</v>
+        <v>17.68</v>
       </c>
       <c r="D17" s="5">
-        <v>17.68</v>
+        <v>18.42</v>
       </c>
       <c r="E17" s="7">
-        <v>-2.3</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1596,13 +1597,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>10.37</v>
+        <v>-0.1</v>
       </c>
       <c r="D18" s="5">
-        <v>-0.1</v>
+        <v>1.84</v>
       </c>
       <c r="E18" s="7">
-        <v>-10.47</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1613,13 +1614,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-9.4</v>
+        <v>-8.6</v>
       </c>
       <c r="D19" s="5">
-        <v>-8.6</v>
+        <v>-9.81</v>
       </c>
       <c r="E19" s="6">
-        <v>0.8</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1630,13 +1631,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-6.44</v>
+        <v>-6.88</v>
       </c>
       <c r="D20" s="5">
-        <v>-6.88</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.44</v>
+        <v>-8.130000000000001</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1647,13 +1648,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-24.78</v>
+        <v>-26.48</v>
       </c>
       <c r="D21" s="5">
-        <v>-26.48</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-1.7</v>
+        <v>-27.02</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1664,13 +1665,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>3964.1</v>
+        <v>3999</v>
       </c>
       <c r="D22" s="5">
-        <v>3999</v>
+        <v>3946.1</v>
       </c>
       <c r="E22" s="6">
-        <v>34.9</v>
+        <v>-52.9</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1681,13 +1682,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>314</v>
+        <v>312.5</v>
       </c>
       <c r="D23" s="5">
-        <v>312.5</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-1.5</v>
+        <v>308.3</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-4.2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1698,13 +1699,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>3493.3</v>
+        <v>3414.2</v>
       </c>
       <c r="D24" s="5">
-        <v>3414.2</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-79.09999999999999</v>
+        <v>3389.1</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-25.1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1715,13 +1716,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>42.4</v>
+        <v>47.88</v>
       </c>
       <c r="D25" s="5">
-        <v>47.88</v>
+        <v>41.44</v>
       </c>
       <c r="E25" s="6">
-        <v>5.48</v>
+        <v>-6.44</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1732,13 +1733,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>49.49</v>
+        <v>48.29</v>
       </c>
       <c r="D26" s="5">
-        <v>48.29</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.2</v>
+        <v>45</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-3.29</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1749,13 +1750,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>46.32</v>
+        <v>39.49</v>
       </c>
       <c r="D27" s="5">
-        <v>39.49</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-6.83</v>
+        <v>37.6</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-1.89</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1766,13 +1767,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>2.45</v>
+        <v>-2.09</v>
       </c>
       <c r="D28" s="5">
-        <v>-2.09</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-4.54</v>
+        <v>-7.68</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-5.59</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1783,13 +1784,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-27.73</v>
+        <v>-55.22</v>
       </c>
       <c r="D29" s="5">
-        <v>-55.22</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-27.49</v>
+        <v>-66.64</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-11.42</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1800,13 +1801,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-50.27</v>
+        <v>-36.92</v>
       </c>
       <c r="D30" s="5">
-        <v>-36.92</v>
+        <v>-44.6</v>
       </c>
       <c r="E30" s="6">
-        <v>13.35</v>
+        <v>-7.68</v>
       </c>
     </row>
   </sheetData>
@@ -1865,22 +1866,22 @@
         <v>40</v>
       </c>
       <c r="B2" s="10">
-        <v>64.52</v>
+        <v>48.52</v>
       </c>
       <c r="C2" s="11">
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>45.2</v>
+        <v>41.3</v>
       </c>
       <c r="E2" s="10">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="F2" s="10">
-        <v>-1.7</v>
+        <v>-3.4</v>
       </c>
       <c r="G2" s="10">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -1999,13 +2000,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.3159</v>
+        <v>0.3112</v>
       </c>
       <c r="B2" s="13">
-        <v>0.2014</v>
+        <v>0.2003</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0342</v>
+        <v>-0.0367</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -151,10 +151,10 @@
     <t>No</t>
   </si>
   <si>
+    <t>DOWN</t>
+  </si>
+  <si>
     <t>UP</t>
-  </si>
-  <si>
-    <t>DOWN</t>
   </si>
   <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
@@ -246,14 +246,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,13 +286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -751,7 +751,7 @@
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
     <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="6.7109375" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -884,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3946.1</v>
+        <v>3922.6</v>
       </c>
       <c r="D2">
-        <v>-1.32</v>
+        <v>-0.6</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -896,46 +896,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-9.81</v>
+        <v>-10.35</v>
       </c>
       <c r="H2">
-        <v>19.22</v>
+        <v>18.51</v>
       </c>
       <c r="I2">
-        <v>-0.85</v>
+        <v>-1.47</v>
       </c>
       <c r="J2">
-        <v>-3.28</v>
+        <v>-2.84</v>
       </c>
       <c r="K2">
-        <v>0.73</v>
+        <v>1.57</v>
       </c>
       <c r="L2">
-        <v>10.91</v>
+        <v>11.46</v>
       </c>
       <c r="M2">
-        <v>20.03</v>
+        <v>19.84</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="P2">
-        <v>3973.04</v>
+        <v>3961.36</v>
       </c>
       <c r="Q2">
-        <v>4036.21</v>
+        <v>4031.34</v>
       </c>
       <c r="R2">
-        <v>3972.89</v>
+        <v>3969.49</v>
       </c>
       <c r="S2">
-        <v>3959.12</v>
+        <v>3958.81</v>
       </c>
       <c r="T2">
-        <v>-0.33</v>
+        <v>-0.91</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -950,43 +950,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>41.44</v>
+        <v>38.93</v>
       </c>
       <c r="Z2">
-        <v>-6.9</v>
+        <v>-12.72</v>
       </c>
       <c r="AA2">
-        <v>8.31</v>
+        <v>4.1</v>
       </c>
       <c r="AB2">
-        <v>-15.21</v>
+        <v>-16.82</v>
       </c>
       <c r="AC2">
         <v>8.94</v>
       </c>
       <c r="AD2">
-        <v>6.04</v>
+        <v>8.94</v>
       </c>
       <c r="AE2">
-        <v>53.16</v>
+        <v>56.33</v>
       </c>
       <c r="AF2">
-        <v>-7.68</v>
+        <v>126.22</v>
       </c>
       <c r="AG2">
-        <v>4133.68</v>
+        <v>4141.17</v>
       </c>
       <c r="AH2">
-        <v>3938.73</v>
+        <v>3921.5</v>
       </c>
       <c r="AI2">
-        <v>3931.27</v>
+        <v>4126.88</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>24.11</v>
+        <v>21.39</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,58 +997,58 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>308.3</v>
+        <v>310.4</v>
       </c>
       <c r="D3">
-        <v>-1.34</v>
+        <v>0.68</v>
       </c>
       <c r="E3">
         <v>335.6</v>
       </c>
       <c r="F3">
-        <v>228.16</v>
+        <v>230.35</v>
       </c>
       <c r="G3">
-        <v>-8.130000000000001</v>
+        <v>-7.51</v>
       </c>
       <c r="H3">
-        <v>35.12</v>
+        <v>34.75</v>
       </c>
       <c r="I3">
-        <v>-0.24</v>
+        <v>-0.77</v>
       </c>
       <c r="J3">
-        <v>-1.45</v>
+        <v>-1.59</v>
       </c>
       <c r="K3">
-        <v>18.42</v>
+        <v>20.83</v>
       </c>
       <c r="L3">
-        <v>36.7</v>
+        <v>36.04</v>
       </c>
       <c r="M3">
-        <v>31.12</v>
+        <v>31.3</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="P3">
-        <v>312.9</v>
+        <v>312.42</v>
       </c>
       <c r="Q3">
-        <v>315.73</v>
+        <v>315.39</v>
       </c>
       <c r="R3">
-        <v>315.02</v>
+        <v>314.97</v>
       </c>
       <c r="S3">
-        <v>292</v>
+        <v>292.12</v>
       </c>
       <c r="T3">
-        <v>5.58</v>
+        <v>6.26</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1063,43 +1063,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>45</v>
+        <v>46.95</v>
       </c>
       <c r="Z3">
-        <v>0.04</v>
+        <v>-0.26</v>
       </c>
       <c r="AA3">
-        <v>1.23</v>
+        <v>0.93</v>
       </c>
       <c r="AB3">
-        <v>-1.19</v>
+        <v>-1.2</v>
       </c>
       <c r="AC3">
-        <v>16.07</v>
+        <v>12.71</v>
       </c>
       <c r="AD3">
-        <v>24.95</v>
+        <v>19.52</v>
       </c>
       <c r="AE3">
-        <v>8.44</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="AF3">
-        <v>-66.64</v>
+        <v>-32.5</v>
       </c>
       <c r="AG3">
-        <v>325.24</v>
+        <v>325.16</v>
       </c>
       <c r="AH3">
-        <v>306.21</v>
+        <v>305.61</v>
       </c>
       <c r="AI3">
         <v>329.06</v>
       </c>
       <c r="AJ3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AK3">
-        <v>17.74</v>
+        <v>16.04</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1110,7 +1110,7 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3389.1</v>
+        <v>3364</v>
       </c>
       <c r="D4">
         <v>-0.74</v>
@@ -1122,46 +1122,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-27.02</v>
+        <v>-27.56</v>
       </c>
       <c r="H4">
-        <v>11.44</v>
+        <v>10.61</v>
       </c>
       <c r="I4">
-        <v>-5.54</v>
+        <v>-4.02</v>
       </c>
       <c r="J4">
-        <v>-5.42</v>
+        <v>-7.9</v>
       </c>
       <c r="K4">
-        <v>1.84</v>
+        <v>2.22</v>
       </c>
       <c r="L4">
-        <v>-17.51</v>
+        <v>-17.08</v>
       </c>
       <c r="M4">
-        <v>-3.67</v>
+        <v>-3.72</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P4">
-        <v>3460.56</v>
+        <v>3432.36</v>
       </c>
       <c r="Q4">
-        <v>3533.66</v>
+        <v>3522.92</v>
       </c>
       <c r="R4">
-        <v>3454.41</v>
+        <v>3460.73</v>
       </c>
       <c r="S4">
-        <v>3639.27</v>
+        <v>3635</v>
       </c>
       <c r="T4">
-        <v>-6.87</v>
+        <v>-7.46</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1176,16 +1176,16 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>37.6</v>
+        <v>35.75</v>
       </c>
       <c r="Z4">
-        <v>-9.699999999999999</v>
+        <v>-19.9</v>
       </c>
       <c r="AA4">
-        <v>15.2</v>
+        <v>8.18</v>
       </c>
       <c r="AB4">
-        <v>-24.9</v>
+        <v>-28.08</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -1194,25 +1194,25 @@
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>94.38</v>
+        <v>92.14</v>
       </c>
       <c r="AF4">
-        <v>-44.6</v>
+        <v>-47.98</v>
       </c>
       <c r="AG4">
-        <v>3658.13</v>
+        <v>3666.57</v>
       </c>
       <c r="AH4">
-        <v>3409.2</v>
+        <v>3379.27</v>
       </c>
       <c r="AI4">
         <v>3316.13</v>
       </c>
       <c r="AJ4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AK4">
-        <v>23.54</v>
+        <v>26.43</v>
       </c>
     </row>
   </sheetData>
@@ -1410,13 +1410,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-1.41</v>
+        <v>-3.28</v>
       </c>
       <c r="D7" s="5">
-        <v>-3.28</v>
+        <v>-2.84</v>
       </c>
       <c r="E7" s="6">
-        <v>-1.87</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1427,13 +1427,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>1.46</v>
+        <v>-1.45</v>
       </c>
       <c r="D8" s="5">
-        <v>-1.45</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-2.91</v>
+        <v>-1.59</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1444,13 +1444,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-5.13</v>
+        <v>-5.42</v>
       </c>
       <c r="D9" s="5">
-        <v>-5.42</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-0.29</v>
+        <v>-7.9</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-2.48</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1461,13 +1461,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-1.13</v>
+        <v>-0.85</v>
       </c>
       <c r="D10" s="5">
-        <v>-0.85</v>
+        <v>-1.47</v>
       </c>
       <c r="E10" s="7">
-        <v>0.28</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1478,13 +1478,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-2.65</v>
+        <v>-0.24</v>
       </c>
       <c r="D11" s="5">
-        <v>-0.24</v>
+        <v>-0.77</v>
       </c>
       <c r="E11" s="7">
-        <v>2.41</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1495,13 +1495,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-5.38</v>
+        <v>-5.54</v>
       </c>
       <c r="D12" s="5">
-        <v>-5.54</v>
+        <v>-4.02</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.16</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1512,13 +1512,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>12.14</v>
+        <v>10.91</v>
       </c>
       <c r="D13" s="5">
-        <v>10.91</v>
+        <v>11.46</v>
       </c>
       <c r="E13" s="6">
-        <v>-1.23</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1529,13 +1529,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>38.99</v>
+        <v>36.7</v>
       </c>
       <c r="D14" s="5">
-        <v>36.7</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-2.29</v>
+        <v>36.04</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1546,13 +1546,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-17.35</v>
+        <v>-17.51</v>
       </c>
       <c r="D15" s="5">
-        <v>-17.51</v>
+        <v>-17.08</v>
       </c>
       <c r="E15" s="6">
-        <v>-0.16</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1563,13 +1563,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>2.52</v>
+        <v>0.73</v>
       </c>
       <c r="D16" s="5">
-        <v>0.73</v>
+        <v>1.57</v>
       </c>
       <c r="E16" s="6">
-        <v>-1.79</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1580,13 +1580,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>17.68</v>
+        <v>18.42</v>
       </c>
       <c r="D17" s="5">
-        <v>18.42</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.74</v>
+        <v>20.83</v>
+      </c>
+      <c r="E17" s="6">
+        <v>2.41</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1597,13 +1597,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>-0.1</v>
+        <v>1.84</v>
       </c>
       <c r="D18" s="5">
-        <v>1.84</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.94</v>
+        <v>2.22</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.38</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1614,13 +1614,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-8.6</v>
+        <v>-9.81</v>
       </c>
       <c r="D19" s="5">
-        <v>-9.81</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-1.21</v>
+        <v>-10.35</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1631,13 +1631,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-6.88</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="D20" s="5">
-        <v>-8.130000000000001</v>
+        <v>-7.51</v>
       </c>
       <c r="E20" s="6">
-        <v>-1.25</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1648,12 +1648,12 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-26.48</v>
+        <v>-27.02</v>
       </c>
       <c r="D21" s="5">
-        <v>-27.02</v>
-      </c>
-      <c r="E21" s="6">
+        <v>-27.56</v>
+      </c>
+      <c r="E21" s="7">
         <v>-0.54</v>
       </c>
     </row>
@@ -1665,13 +1665,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>3999</v>
+        <v>3946.1</v>
       </c>
       <c r="D22" s="5">
-        <v>3946.1</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-52.9</v>
+        <v>3922.6</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-23.5</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1682,13 +1682,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>312.5</v>
+        <v>308.3</v>
       </c>
       <c r="D23" s="5">
-        <v>308.3</v>
+        <v>310.4</v>
       </c>
       <c r="E23" s="6">
-        <v>-4.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1699,12 +1699,12 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>3414.2</v>
+        <v>3389.1</v>
       </c>
       <c r="D24" s="5">
-        <v>3389.1</v>
-      </c>
-      <c r="E24" s="6">
+        <v>3364</v>
+      </c>
+      <c r="E24" s="7">
         <v>-25.1</v>
       </c>
     </row>
@@ -1716,13 +1716,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>47.88</v>
+        <v>41.44</v>
       </c>
       <c r="D25" s="5">
-        <v>41.44</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-6.44</v>
+        <v>38.93</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-2.51</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1733,13 +1733,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>48.29</v>
+        <v>45</v>
       </c>
       <c r="D26" s="5">
-        <v>45</v>
+        <v>46.95</v>
       </c>
       <c r="E26" s="6">
-        <v>-3.29</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1750,13 +1750,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>39.49</v>
+        <v>37.6</v>
       </c>
       <c r="D27" s="5">
-        <v>37.6</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-1.89</v>
+        <v>35.75</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.85</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1767,13 +1767,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>-2.09</v>
+        <v>-7.68</v>
       </c>
       <c r="D28" s="5">
-        <v>-7.68</v>
+        <v>126.22</v>
       </c>
       <c r="E28" s="6">
-        <v>-5.59</v>
+        <v>133.9</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1784,13 +1784,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-55.22</v>
+        <v>-66.64</v>
       </c>
       <c r="D29" s="5">
-        <v>-66.64</v>
+        <v>-32.5</v>
       </c>
       <c r="E29" s="6">
-        <v>-11.42</v>
+        <v>34.14</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1801,13 +1801,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-36.92</v>
+        <v>-44.6</v>
       </c>
       <c r="D30" s="5">
-        <v>-44.6</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-7.68</v>
+        <v>-47.98</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-3.38</v>
       </c>
     </row>
   </sheetData>
@@ -1872,16 +1872,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>41.3</v>
+        <v>40.5</v>
       </c>
       <c r="E2" s="10">
         <v>30</v>
       </c>
       <c r="F2" s="10">
-        <v>-3.4</v>
+        <v>-4.1</v>
       </c>
       <c r="G2" s="10">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -2000,13 +2000,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.3112</v>
+        <v>0.313</v>
       </c>
       <c r="B2" s="13">
-        <v>0.2003</v>
+        <v>0.1984</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0367</v>
+        <v>-0.0372</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -884,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3922.6</v>
+        <v>3955</v>
       </c>
       <c r="D2">
-        <v>-0.6</v>
+        <v>0.83</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -896,46 +896,46 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-10.35</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="H2">
-        <v>18.51</v>
+        <v>19.48</v>
       </c>
       <c r="I2">
-        <v>-1.47</v>
+        <v>-0.5</v>
       </c>
       <c r="J2">
-        <v>-2.84</v>
+        <v>-1.62</v>
       </c>
       <c r="K2">
-        <v>1.57</v>
+        <v>-2.33</v>
       </c>
       <c r="L2">
-        <v>11.46</v>
+        <v>13.15</v>
       </c>
       <c r="M2">
-        <v>19.84</v>
+        <v>20.05</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P2">
-        <v>3961.36</v>
+        <v>3957.36</v>
       </c>
       <c r="Q2">
-        <v>4031.34</v>
+        <v>4025.55</v>
       </c>
       <c r="R2">
-        <v>3969.49</v>
+        <v>3967.41</v>
       </c>
       <c r="S2">
-        <v>3958.81</v>
+        <v>3958.71</v>
       </c>
       <c r="T2">
-        <v>-0.91</v>
+        <v>-0.09</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -950,43 +950,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>38.93</v>
+        <v>43.97</v>
       </c>
       <c r="Z2">
-        <v>-12.72</v>
+        <v>-14.55</v>
       </c>
       <c r="AA2">
-        <v>4.1</v>
+        <v>0.37</v>
       </c>
       <c r="AB2">
-        <v>-16.82</v>
+        <v>-14.92</v>
       </c>
       <c r="AC2">
-        <v>8.94</v>
+        <v>7.01</v>
       </c>
       <c r="AD2">
-        <v>8.94</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AE2">
-        <v>56.33</v>
+        <v>56.27</v>
       </c>
       <c r="AF2">
-        <v>126.22</v>
+        <v>-0.28</v>
       </c>
       <c r="AG2">
-        <v>4141.17</v>
+        <v>4138.79</v>
       </c>
       <c r="AH2">
-        <v>3921.5</v>
+        <v>3912.31</v>
       </c>
       <c r="AI2">
-        <v>4126.88</v>
+        <v>4106.57</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>21.39</v>
+        <v>19.35</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>310.4</v>
+        <v>311.3</v>
       </c>
       <c r="D3">
-        <v>0.68</v>
+        <v>0.29</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1009,46 +1009,46 @@
         <v>230.35</v>
       </c>
       <c r="G3">
-        <v>-7.51</v>
+        <v>-7.24</v>
       </c>
       <c r="H3">
-        <v>34.75</v>
+        <v>35.14</v>
       </c>
       <c r="I3">
-        <v>-0.77</v>
+        <v>-1.77</v>
       </c>
       <c r="J3">
-        <v>-1.59</v>
+        <v>-1.86</v>
       </c>
       <c r="K3">
-        <v>20.83</v>
+        <v>12.81</v>
       </c>
       <c r="L3">
-        <v>36.04</v>
+        <v>34.65</v>
       </c>
       <c r="M3">
-        <v>31.3</v>
+        <v>31.28</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P3">
-        <v>312.42</v>
+        <v>311.3</v>
       </c>
       <c r="Q3">
-        <v>315.39</v>
+        <v>315.18</v>
       </c>
       <c r="R3">
-        <v>314.97</v>
+        <v>314.89</v>
       </c>
       <c r="S3">
-        <v>292.12</v>
+        <v>292.23</v>
       </c>
       <c r="T3">
-        <v>6.26</v>
+        <v>6.53</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1063,34 +1063,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>46.95</v>
+        <v>47.8</v>
       </c>
       <c r="Z3">
-        <v>-0.26</v>
+        <v>-0.43</v>
       </c>
       <c r="AA3">
-        <v>0.93</v>
+        <v>0.66</v>
       </c>
       <c r="AB3">
-        <v>-1.2</v>
+        <v>-1.09</v>
       </c>
       <c r="AC3">
-        <v>12.71</v>
+        <v>12.72</v>
       </c>
       <c r="AD3">
-        <v>19.52</v>
+        <v>13.83</v>
       </c>
       <c r="AE3">
-        <v>8.369999999999999</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="AF3">
-        <v>-32.5</v>
+        <v>1.02</v>
       </c>
       <c r="AG3">
-        <v>325.16</v>
+        <v>325.13</v>
       </c>
       <c r="AH3">
-        <v>305.61</v>
+        <v>305.24</v>
       </c>
       <c r="AI3">
         <v>329.06</v>
@@ -1099,7 +1099,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>16.04</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1110,10 +1110,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3364</v>
+        <v>3377.9</v>
       </c>
       <c r="D4">
-        <v>-0.74</v>
+        <v>0.41</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1122,46 +1122,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-27.56</v>
+        <v>-27.26</v>
       </c>
       <c r="H4">
-        <v>10.61</v>
+        <v>11.07</v>
       </c>
       <c r="I4">
-        <v>-4.02</v>
+        <v>-3.52</v>
       </c>
       <c r="J4">
-        <v>-7.9</v>
+        <v>-5.62</v>
       </c>
       <c r="K4">
-        <v>2.22</v>
+        <v>0.8</v>
       </c>
       <c r="L4">
-        <v>-17.08</v>
+        <v>-16.33</v>
       </c>
       <c r="M4">
-        <v>-3.72</v>
+        <v>-3.9</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="P4">
-        <v>3432.36</v>
+        <v>3407.7</v>
       </c>
       <c r="Q4">
-        <v>3522.92</v>
+        <v>3511.58</v>
       </c>
       <c r="R4">
-        <v>3460.73</v>
+        <v>3464.95</v>
       </c>
       <c r="S4">
-        <v>3635</v>
+        <v>3630.52</v>
       </c>
       <c r="T4">
-        <v>-7.46</v>
+        <v>-6.96</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1176,34 +1176,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>35.75</v>
+        <v>37.58</v>
       </c>
       <c r="Z4">
-        <v>-19.9</v>
+        <v>-26.55</v>
       </c>
       <c r="AA4">
-        <v>8.18</v>
+        <v>1.24</v>
       </c>
       <c r="AB4">
-        <v>-28.08</v>
+        <v>-27.78</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AE4">
-        <v>92.14</v>
+        <v>89.75</v>
       </c>
       <c r="AF4">
-        <v>-47.98</v>
+        <v>-50.18</v>
       </c>
       <c r="AG4">
-        <v>3666.57</v>
+        <v>3663.61</v>
       </c>
       <c r="AH4">
-        <v>3379.27</v>
+        <v>3359.55</v>
       </c>
       <c r="AI4">
         <v>3316.13</v>
@@ -1212,7 +1212,7 @@
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>26.43</v>
+        <v>26.19</v>
       </c>
     </row>
   </sheetData>
@@ -1410,13 +1410,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-3.28</v>
+        <v>-2.84</v>
       </c>
       <c r="D7" s="5">
-        <v>-2.84</v>
+        <v>-1.62</v>
       </c>
       <c r="E7" s="6">
-        <v>0.44</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1427,13 +1427,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-1.45</v>
+        <v>-1.59</v>
       </c>
       <c r="D8" s="5">
-        <v>-1.59</v>
+        <v>-1.86</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.14</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1444,13 +1444,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-5.42</v>
+        <v>-7.9</v>
       </c>
       <c r="D9" s="5">
-        <v>-7.9</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-2.48</v>
+        <v>-5.62</v>
+      </c>
+      <c r="E9" s="6">
+        <v>2.28</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1461,13 +1461,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-0.85</v>
+        <v>-1.47</v>
       </c>
       <c r="D10" s="5">
-        <v>-1.47</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.62</v>
+        <v>-0.5</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.97</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1478,13 +1478,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-0.24</v>
+        <v>-0.77</v>
       </c>
       <c r="D11" s="5">
-        <v>-0.77</v>
+        <v>-1.77</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.53</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1495,13 +1495,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-5.54</v>
+        <v>-4.02</v>
       </c>
       <c r="D12" s="5">
-        <v>-4.02</v>
+        <v>-3.52</v>
       </c>
       <c r="E12" s="6">
-        <v>1.52</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1512,13 +1512,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>10.91</v>
+        <v>11.46</v>
       </c>
       <c r="D13" s="5">
-        <v>11.46</v>
+        <v>13.15</v>
       </c>
       <c r="E13" s="6">
-        <v>0.55</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1529,13 +1529,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>36.7</v>
+        <v>36.04</v>
       </c>
       <c r="D14" s="5">
-        <v>36.04</v>
+        <v>34.65</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.66</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1546,13 +1546,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-17.51</v>
+        <v>-17.08</v>
       </c>
       <c r="D15" s="5">
-        <v>-17.08</v>
+        <v>-16.33</v>
       </c>
       <c r="E15" s="6">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1563,13 +1563,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>0.73</v>
+        <v>1.57</v>
       </c>
       <c r="D16" s="5">
-        <v>1.57</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0.84</v>
+        <v>-2.33</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-3.9</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1580,13 +1580,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>18.42</v>
+        <v>20.83</v>
       </c>
       <c r="D17" s="5">
-        <v>20.83</v>
-      </c>
-      <c r="E17" s="6">
-        <v>2.41</v>
+        <v>12.81</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-8.02</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1597,13 +1597,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>1.84</v>
+        <v>2.22</v>
       </c>
       <c r="D18" s="5">
-        <v>2.22</v>
-      </c>
-      <c r="E18" s="6">
-        <v>0.38</v>
+        <v>0.8</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1.42</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1614,13 +1614,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-9.81</v>
+        <v>-10.35</v>
       </c>
       <c r="D19" s="5">
-        <v>-10.35</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.54</v>
+        <v>-9.609999999999999</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.74</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1631,13 +1631,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-8.130000000000001</v>
+        <v>-7.51</v>
       </c>
       <c r="D20" s="5">
-        <v>-7.51</v>
+        <v>-7.24</v>
       </c>
       <c r="E20" s="6">
-        <v>0.62</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1648,13 +1648,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-27.02</v>
+        <v>-27.56</v>
       </c>
       <c r="D21" s="5">
-        <v>-27.56</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.54</v>
+        <v>-27.26</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.3</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1665,13 +1665,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>3946.1</v>
+        <v>3922.6</v>
       </c>
       <c r="D22" s="5">
-        <v>3922.6</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-23.5</v>
+        <v>3955</v>
+      </c>
+      <c r="E22" s="6">
+        <v>32.4</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1682,13 +1682,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>308.3</v>
+        <v>310.4</v>
       </c>
       <c r="D23" s="5">
-        <v>310.4</v>
+        <v>311.3</v>
       </c>
       <c r="E23" s="6">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1699,13 +1699,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>3389.1</v>
+        <v>3364</v>
       </c>
       <c r="D24" s="5">
-        <v>3364</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-25.1</v>
+        <v>3377.9</v>
+      </c>
+      <c r="E24" s="6">
+        <v>13.9</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1716,13 +1716,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>41.44</v>
+        <v>38.93</v>
       </c>
       <c r="D25" s="5">
-        <v>38.93</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-2.51</v>
+        <v>43.97</v>
+      </c>
+      <c r="E25" s="6">
+        <v>5.04</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1733,13 +1733,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>45</v>
+        <v>46.95</v>
       </c>
       <c r="D26" s="5">
-        <v>46.95</v>
+        <v>47.8</v>
       </c>
       <c r="E26" s="6">
-        <v>1.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1750,13 +1750,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>37.6</v>
+        <v>35.75</v>
       </c>
       <c r="D27" s="5">
-        <v>35.75</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-1.85</v>
+        <v>37.58</v>
+      </c>
+      <c r="E27" s="6">
+        <v>1.83</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1767,13 +1767,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>-7.68</v>
+        <v>126.22</v>
       </c>
       <c r="D28" s="5">
-        <v>126.22</v>
-      </c>
-      <c r="E28" s="6">
-        <v>133.9</v>
+        <v>-0.28</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-126.5</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1784,13 +1784,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-66.64</v>
+        <v>-32.5</v>
       </c>
       <c r="D29" s="5">
-        <v>-32.5</v>
+        <v>1.02</v>
       </c>
       <c r="E29" s="6">
-        <v>34.14</v>
+        <v>33.52</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1801,13 +1801,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-44.6</v>
+        <v>-47.98</v>
       </c>
       <c r="D30" s="5">
-        <v>-47.98</v>
+        <v>-50.18</v>
       </c>
       <c r="E30" s="7">
-        <v>-3.38</v>
+        <v>-2.2</v>
       </c>
     </row>
   </sheetData>
@@ -1872,16 +1872,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>40.5</v>
+        <v>43.1</v>
       </c>
       <c r="E2" s="10">
         <v>30</v>
       </c>
       <c r="F2" s="10">
-        <v>-4.1</v>
+        <v>-3</v>
       </c>
       <c r="G2" s="10">
-        <v>8.199999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -2000,13 +2000,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.313</v>
+        <v>0.3128</v>
       </c>
       <c r="B2" s="13">
-        <v>0.1984</v>
+        <v>0.2005</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0372</v>
+        <v>-0.039</v>
       </c>
     </row>
   </sheetData>

--- a/LNT_GROUP_Technical_Metrics.xlsx
+++ b/LNT_GROUP_Technical_Metrics.xlsx
@@ -246,14 +246,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,13 +286,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -884,10 +884,10 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>3955</v>
+        <v>3930.7</v>
       </c>
       <c r="D2">
-        <v>0.83</v>
+        <v>-0.61</v>
       </c>
       <c r="E2">
         <v>4375.36</v>
@@ -896,25 +896,25 @@
         <v>3310.07</v>
       </c>
       <c r="G2">
-        <v>-9.609999999999999</v>
+        <v>-10.16</v>
       </c>
       <c r="H2">
-        <v>19.48</v>
+        <v>18.75</v>
       </c>
       <c r="I2">
-        <v>-0.5</v>
+        <v>-0.84</v>
       </c>
       <c r="J2">
-        <v>-1.62</v>
+        <v>-3.44</v>
       </c>
       <c r="K2">
-        <v>-2.33</v>
+        <v>-5.73</v>
       </c>
       <c r="L2">
-        <v>13.15</v>
+        <v>12.6</v>
       </c>
       <c r="M2">
-        <v>20.05</v>
+        <v>19.89</v>
       </c>
       <c r="N2">
         <v>66</v>
@@ -923,19 +923,19 @@
         <v>59</v>
       </c>
       <c r="P2">
-        <v>3957.36</v>
+        <v>3950.68</v>
       </c>
       <c r="Q2">
-        <v>4025.55</v>
+        <v>4019.24</v>
       </c>
       <c r="R2">
-        <v>3967.41</v>
+        <v>3965.49</v>
       </c>
       <c r="S2">
-        <v>3958.71</v>
+        <v>3958.57</v>
       </c>
       <c r="T2">
-        <v>-0.09</v>
+        <v>-0.7</v>
       </c>
       <c r="U2" t="s">
         <v>41</v>
@@ -950,43 +950,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>43.97</v>
+        <v>41.22</v>
       </c>
       <c r="Z2">
-        <v>-14.55</v>
+        <v>-17.76</v>
       </c>
       <c r="AA2">
-        <v>0.37</v>
+        <v>-3.25</v>
       </c>
       <c r="AB2">
-        <v>-14.92</v>
+        <v>-14.5</v>
       </c>
       <c r="AC2">
-        <v>7.01</v>
+        <v>10.2</v>
       </c>
       <c r="AD2">
-        <v>8.300000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="AE2">
-        <v>56.27</v>
+        <v>57.56</v>
       </c>
       <c r="AF2">
-        <v>-0.28</v>
+        <v>-10.76</v>
       </c>
       <c r="AG2">
-        <v>4138.79</v>
+        <v>4138.99</v>
       </c>
       <c r="AH2">
-        <v>3912.31</v>
+        <v>3899.48</v>
       </c>
       <c r="AI2">
-        <v>4106.57</v>
+        <v>4087.04</v>
       </c>
       <c r="AJ2" t="s">
         <v>43</v>
       </c>
       <c r="AK2">
-        <v>19.35</v>
+        <v>20.11</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -997,10 +997,10 @@
         <v>40</v>
       </c>
       <c r="C3">
-        <v>311.3</v>
+        <v>309.1</v>
       </c>
       <c r="D3">
-        <v>0.29</v>
+        <v>-0.71</v>
       </c>
       <c r="E3">
         <v>335.6</v>
@@ -1009,25 +1009,25 @@
         <v>230.35</v>
       </c>
       <c r="G3">
-        <v>-7.24</v>
+        <v>-7.9</v>
       </c>
       <c r="H3">
-        <v>35.14</v>
+        <v>34.19</v>
       </c>
       <c r="I3">
-        <v>-1.77</v>
+        <v>-1.56</v>
       </c>
       <c r="J3">
-        <v>-1.86</v>
+        <v>-1.98</v>
       </c>
       <c r="K3">
-        <v>12.81</v>
+        <v>5.4</v>
       </c>
       <c r="L3">
-        <v>34.65</v>
+        <v>33.47</v>
       </c>
       <c r="M3">
-        <v>31.28</v>
+        <v>31.08</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1036,19 +1036,19 @@
         <v>77</v>
       </c>
       <c r="P3">
-        <v>311.3</v>
+        <v>310.32</v>
       </c>
       <c r="Q3">
-        <v>315.18</v>
+        <v>315.32</v>
       </c>
       <c r="R3">
-        <v>314.89</v>
+        <v>314.54</v>
       </c>
       <c r="S3">
-        <v>292.23</v>
+        <v>292.3</v>
       </c>
       <c r="T3">
-        <v>6.53</v>
+        <v>5.75</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
@@ -1063,34 +1063,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>47.8</v>
+        <v>45.86</v>
       </c>
       <c r="Z3">
-        <v>-0.43</v>
+        <v>-0.72</v>
       </c>
       <c r="AA3">
-        <v>0.66</v>
+        <v>0.38</v>
       </c>
       <c r="AB3">
-        <v>-1.09</v>
+        <v>-1.11</v>
       </c>
       <c r="AC3">
-        <v>12.72</v>
+        <v>15.03</v>
       </c>
       <c r="AD3">
-        <v>13.83</v>
+        <v>13.49</v>
       </c>
       <c r="AE3">
-        <v>8.130000000000001</v>
+        <v>8.19</v>
       </c>
       <c r="AF3">
-        <v>1.02</v>
+        <v>-11.1</v>
       </c>
       <c r="AG3">
-        <v>325.13</v>
+        <v>324.81</v>
       </c>
       <c r="AH3">
-        <v>305.24</v>
+        <v>305.84</v>
       </c>
       <c r="AI3">
         <v>329.06</v>
@@ -1099,7 +1099,7 @@
         <v>43</v>
       </c>
       <c r="AK3">
-        <v>14.99</v>
+        <v>16.11</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1110,10 +1110,10 @@
         <v>40</v>
       </c>
       <c r="C4">
-        <v>3377.9</v>
+        <v>3337.4</v>
       </c>
       <c r="D4">
-        <v>0.41</v>
+        <v>-1.2</v>
       </c>
       <c r="E4">
         <v>4643.84</v>
@@ -1122,46 +1122,46 @@
         <v>3041.31</v>
       </c>
       <c r="G4">
-        <v>-27.26</v>
+        <v>-28.13</v>
       </c>
       <c r="H4">
-        <v>11.07</v>
+        <v>9.74</v>
       </c>
       <c r="I4">
-        <v>-3.52</v>
+        <v>-4.46</v>
       </c>
       <c r="J4">
-        <v>-5.62</v>
+        <v>-7.42</v>
       </c>
       <c r="K4">
-        <v>0.8</v>
+        <v>-1.71</v>
       </c>
       <c r="L4">
-        <v>-16.33</v>
+        <v>-17.28</v>
       </c>
       <c r="M4">
-        <v>-3.9</v>
+        <v>-4.13</v>
       </c>
       <c r="N4">
         <v>34</v>
       </c>
       <c r="O4">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P4">
-        <v>3407.7</v>
+        <v>3376.52</v>
       </c>
       <c r="Q4">
-        <v>3511.58</v>
+        <v>3504.61</v>
       </c>
       <c r="R4">
-        <v>3464.95</v>
+        <v>3467.58</v>
       </c>
       <c r="S4">
-        <v>3630.52</v>
+        <v>3626.13</v>
       </c>
       <c r="T4">
-        <v>-6.96</v>
+        <v>-7.96</v>
       </c>
       <c r="U4" t="s">
         <v>41</v>
@@ -1176,34 +1176,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>37.58</v>
+        <v>34.5</v>
       </c>
       <c r="Z4">
-        <v>-26.55</v>
+        <v>-34.68</v>
       </c>
       <c r="AA4">
-        <v>1.24</v>
+        <v>-5.95</v>
       </c>
       <c r="AB4">
-        <v>-27.78</v>
+        <v>-28.74</v>
       </c>
       <c r="AC4">
         <v>2.74</v>
       </c>
       <c r="AD4">
-        <v>0.91</v>
+        <v>1.82</v>
       </c>
       <c r="AE4">
-        <v>89.75</v>
+        <v>87.33</v>
       </c>
       <c r="AF4">
-        <v>-50.18</v>
+        <v>-66.23</v>
       </c>
       <c r="AG4">
-        <v>3663.61</v>
+        <v>3675.03</v>
       </c>
       <c r="AH4">
-        <v>3359.55</v>
+        <v>3334.19</v>
       </c>
       <c r="AI4">
         <v>3316.13</v>
@@ -1212,7 +1212,7 @@
         <v>44</v>
       </c>
       <c r="AK4">
-        <v>26.19</v>
+        <v>27.2</v>
       </c>
     </row>
   </sheetData>
@@ -1410,13 +1410,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-2.84</v>
+        <v>-1.62</v>
       </c>
       <c r="D7" s="5">
-        <v>-1.62</v>
+        <v>-3.44</v>
       </c>
       <c r="E7" s="6">
-        <v>1.22</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1427,13 +1427,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-1.59</v>
+        <v>-1.86</v>
       </c>
       <c r="D8" s="5">
-        <v>-1.86</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.27</v>
+        <v>-1.98</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1444,13 +1444,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-7.9</v>
+        <v>-5.62</v>
       </c>
       <c r="D9" s="5">
-        <v>-5.62</v>
+        <v>-7.42</v>
       </c>
       <c r="E9" s="6">
-        <v>2.28</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1461,13 +1461,13 @@
         <v>8</v>
       </c>
       <c r="C10" s="5">
-        <v>-1.47</v>
+        <v>-0.5</v>
       </c>
       <c r="D10" s="5">
-        <v>-0.5</v>
+        <v>-0.84</v>
       </c>
       <c r="E10" s="6">
-        <v>0.97</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1478,13 +1478,13 @@
         <v>8</v>
       </c>
       <c r="C11" s="5">
-        <v>-0.77</v>
+        <v>-1.77</v>
       </c>
       <c r="D11" s="5">
-        <v>-1.77</v>
+        <v>-1.56</v>
       </c>
       <c r="E11" s="7">
-        <v>-1</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1495,13 +1495,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-4.02</v>
+        <v>-3.52</v>
       </c>
       <c r="D12" s="5">
-        <v>-3.52</v>
+        <v>-4.46</v>
       </c>
       <c r="E12" s="6">
-        <v>0.5</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1512,13 +1512,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="5">
-        <v>11.46</v>
+        <v>13.15</v>
       </c>
       <c r="D13" s="5">
-        <v>13.15</v>
+        <v>12.6</v>
       </c>
       <c r="E13" s="6">
-        <v>1.69</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1529,13 +1529,13 @@
         <v>11</v>
       </c>
       <c r="C14" s="5">
-        <v>36.04</v>
+        <v>34.65</v>
       </c>
       <c r="D14" s="5">
-        <v>34.65</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.39</v>
+        <v>33.47</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-1.18</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1546,13 +1546,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="5">
-        <v>-17.08</v>
+        <v>-16.33</v>
       </c>
       <c r="D15" s="5">
-        <v>-16.33</v>
+        <v>-17.28</v>
       </c>
       <c r="E15" s="6">
-        <v>0.75</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1563,13 +1563,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="5">
-        <v>1.57</v>
+        <v>-2.33</v>
       </c>
       <c r="D16" s="5">
-        <v>-2.33</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-3.9</v>
+        <v>-5.73</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-3.4</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1580,13 +1580,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="5">
-        <v>20.83</v>
+        <v>12.81</v>
       </c>
       <c r="D17" s="5">
-        <v>12.81</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-8.02</v>
+        <v>5.4</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-7.41</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1597,13 +1597,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="5">
-        <v>2.22</v>
+        <v>0.8</v>
       </c>
       <c r="D18" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-1.42</v>
+        <v>-1.71</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-2.51</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1614,13 +1614,13 @@
         <v>6</v>
       </c>
       <c r="C19" s="5">
-        <v>-10.35</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="D19" s="5">
-        <v>-9.609999999999999</v>
+        <v>-10.16</v>
       </c>
       <c r="E19" s="6">
-        <v>0.74</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1631,13 +1631,13 @@
         <v>6</v>
       </c>
       <c r="C20" s="5">
-        <v>-7.51</v>
+        <v>-7.24</v>
       </c>
       <c r="D20" s="5">
-        <v>-7.24</v>
+        <v>-7.9</v>
       </c>
       <c r="E20" s="6">
-        <v>0.27</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1648,13 +1648,13 @@
         <v>6</v>
       </c>
       <c r="C21" s="5">
-        <v>-27.56</v>
+        <v>-27.26</v>
       </c>
       <c r="D21" s="5">
-        <v>-27.26</v>
+        <v>-28.13</v>
       </c>
       <c r="E21" s="6">
-        <v>0.3</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1665,13 +1665,13 @@
         <v>2</v>
       </c>
       <c r="C22" s="5">
-        <v>3922.6</v>
+        <v>3955</v>
       </c>
       <c r="D22" s="5">
-        <v>3955</v>
+        <v>3930.7</v>
       </c>
       <c r="E22" s="6">
-        <v>32.4</v>
+        <v>-24.3</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1682,13 +1682,13 @@
         <v>2</v>
       </c>
       <c r="C23" s="5">
-        <v>310.4</v>
+        <v>311.3</v>
       </c>
       <c r="D23" s="5">
-        <v>311.3</v>
+        <v>309.1</v>
       </c>
       <c r="E23" s="6">
-        <v>0.9</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1699,13 +1699,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="5">
-        <v>3364</v>
+        <v>3377.9</v>
       </c>
       <c r="D24" s="5">
-        <v>3377.9</v>
+        <v>3337.4</v>
       </c>
       <c r="E24" s="6">
-        <v>13.9</v>
+        <v>-40.5</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1716,13 +1716,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="5">
-        <v>38.93</v>
+        <v>43.97</v>
       </c>
       <c r="D25" s="5">
-        <v>43.97</v>
+        <v>41.22</v>
       </c>
       <c r="E25" s="6">
-        <v>5.04</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1733,13 +1733,13 @@
         <v>24</v>
       </c>
       <c r="C26" s="5">
-        <v>46.95</v>
+        <v>47.8</v>
       </c>
       <c r="D26" s="5">
-        <v>47.8</v>
+        <v>45.86</v>
       </c>
       <c r="E26" s="6">
-        <v>0.85</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1750,13 +1750,13 @@
         <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>35.75</v>
+        <v>37.58</v>
       </c>
       <c r="D27" s="5">
-        <v>37.58</v>
+        <v>34.5</v>
       </c>
       <c r="E27" s="6">
-        <v>1.83</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1767,13 +1767,13 @@
         <v>31</v>
       </c>
       <c r="C28" s="5">
-        <v>126.22</v>
+        <v>-0.28</v>
       </c>
       <c r="D28" s="5">
-        <v>-0.28</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-126.5</v>
+        <v>-10.76</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-10.48</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1784,13 +1784,13 @@
         <v>31</v>
       </c>
       <c r="C29" s="5">
-        <v>-32.5</v>
+        <v>1.02</v>
       </c>
       <c r="D29" s="5">
-        <v>1.02</v>
+        <v>-11.1</v>
       </c>
       <c r="E29" s="6">
-        <v>33.52</v>
+        <v>-12.12</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1801,13 +1801,13 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>-47.98</v>
+        <v>-50.18</v>
       </c>
       <c r="D30" s="5">
-        <v>-50.18</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-2.2</v>
+        <v>-66.23</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-16.05</v>
       </c>
     </row>
   </sheetData>
@@ -1872,16 +1872,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="10">
-        <v>43.1</v>
+        <v>40.5</v>
       </c>
       <c r="E2" s="10">
         <v>30</v>
       </c>
       <c r="F2" s="10">
-        <v>-3</v>
+        <v>-4.3</v>
       </c>
       <c r="G2" s="10">
-        <v>3.8</v>
+        <v>-0.7</v>
       </c>
       <c r="H2" s="10">
         <v>66.3</v>
@@ -2000,13 +2000,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13">
-        <v>0.3128</v>
+        <v>0.3108</v>
       </c>
       <c r="B2" s="13">
-        <v>0.2005</v>
+        <v>0.1989</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.039</v>
+        <v>-0.0413</v>
       </c>
     </row>
   </sheetData>
